--- a/config/鸿合_配置_v2.0.xlsx
+++ b/config/鸿合_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="105">
   <si>
     <t>key</t>
   </si>
@@ -80,7 +81,7 @@
     <t>mqtt_host</t>
   </si>
   <si>
-    <t>60.204.207.155</t>
+    <t>127.0.0.1</t>
   </si>
   <si>
     <t>MQTT服务器地址</t>
@@ -197,6 +198,15 @@
     <t>bcu4</t>
   </si>
   <si>
+    <t>crd</t>
+  </si>
+  <si>
+    <t>CRD</t>
+  </si>
+  <si>
+    <t>测控柜</t>
+  </si>
+  <si>
     <t>comType</t>
   </si>
   <si>
@@ -236,70 +246,43 @@
     <t>interface</t>
   </si>
   <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>./config/BCU_GOLD.xlsx</t>
-  </si>
-  <si>
-    <t>vcan0</t>
-  </si>
-  <si>
-    <t>pcs</t>
-  </si>
-  <si>
     <t>ModbusTCP</t>
   </si>
   <si>
-    <t>./config/PCS_125_英博.xlsx</t>
-  </si>
-  <si>
-    <t>127.0.0.1</t>
-  </si>
-  <si>
-    <t>liquidcool1</t>
-  </si>
-  <si>
-    <t>LiquidCool</t>
-  </si>
-  <si>
-    <t>ModbusRTU</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB2</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>liquidcool2</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB3</t>
-  </si>
-  <si>
-    <t>liquidcool3</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB1</t>
-  </si>
-  <si>
-    <t>firefighting</t>
-  </si>
-  <si>
-    <t>Firefighting</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB4</t>
-  </si>
-  <si>
-    <t>dehumidifier</t>
-  </si>
-  <si>
-    <t>Dehumidifier</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB5</t>
+    <t>./config/PCS_英博_大机.xlsx</t>
+  </si>
+  <si>
+    <t>192.168.0.1</t>
+  </si>
+  <si>
+    <t>192.168.0.2</t>
+  </si>
+  <si>
+    <t>192.168.0.3</t>
+  </si>
+  <si>
+    <t>192.168.0.4</t>
+  </si>
+  <si>
+    <t>192.168.1.104</t>
+  </si>
+  <si>
+    <t>192.168.1.105</t>
+  </si>
+  <si>
+    <t>192.168.1.106</t>
+  </si>
+  <si>
+    <t>192.168.1.107</t>
+  </si>
+  <si>
+    <t>IEC104</t>
+  </si>
+  <si>
+    <t>./config/测控柜_鸿合.xlsx</t>
+  </si>
+  <si>
+    <t>192.168.1.108</t>
   </si>
   <si>
     <t>device_id</t>
@@ -314,9 +297,6 @@
     <t>enable</t>
   </si>
   <si>
-    <t>pcs0</t>
-  </si>
-  <si>
     <t>/pcs/0/yx</t>
   </si>
   <si>
@@ -324,6 +304,51 @@
   </si>
   <si>
     <t>/pcs/0/yt</t>
+  </si>
+  <si>
+    <t>/pcs/1/yx</t>
+  </si>
+  <si>
+    <t>58,59,60,61,62,63,64,65,66,67,68,69,70,71</t>
+  </si>
+  <si>
+    <t>/pcs/1/yc</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57</t>
+  </si>
+  <si>
+    <t>/pcs/1/yt</t>
+  </si>
+  <si>
+    <t>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029</t>
+  </si>
+  <si>
+    <t>/pcs/2/yx</t>
+  </si>
+  <si>
+    <t>/pcs/2/yc</t>
+  </si>
+  <si>
+    <t>/pcs/2/yt</t>
+  </si>
+  <si>
+    <t>/pcs/3/yx</t>
+  </si>
+  <si>
+    <t>/pcs/3/yc</t>
+  </si>
+  <si>
+    <t>/pcs/3/yt</t>
+  </si>
+  <si>
+    <t>/crd/0/yx</t>
+  </si>
+  <si>
+    <t>/crd/0/yc</t>
+  </si>
+  <si>
+    <t>/crd/0/yk</t>
   </si>
 </sst>
 </file>
@@ -336,7 +361,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,15 +384,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -851,137 +883,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -997,11 +1029,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1566,6 +1604,855 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="遥测"/>
+      <sheetName val="遥信"/>
+      <sheetName val="遥控"/>
+      <sheetName val="遥脉"/>
+      <sheetName val="遥调"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>35</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>37</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>39</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>41</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>42</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>46</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>47</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>49</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>51</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>52</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>53</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>54</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>57</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>58</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>59</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>61</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>62</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>63</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>64</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>65</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>66</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>67</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>68</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>69</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>70</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>71</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>73</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>74</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>75</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>76</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>77</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>78</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>79</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>80</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>81</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>82</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>83</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>84</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>85</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>86</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>87</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>88</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>89</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>90</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>91</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>92</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>93</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>94</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>96</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>97</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>99</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>101</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>102</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>104</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>106</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>107</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>108</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>109</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>112</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>113</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>114</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>116</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>117</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="A2">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>1001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>1002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>1003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>1004</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>1005</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>1006</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>1007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>1008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>1009</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>1010</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>1011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>1012</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>1013</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1014</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1015</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>1016</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>1017</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>1018</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>1019</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>1020</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>1021</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>1022</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>1023</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>1024</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>1025</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>1026</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>1027</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>1028</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>1029</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>1030</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>1031</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>1032</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>1033</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>1034</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>1035</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>1036</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>1037</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>1038</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>1039</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>1040</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>1041</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>1042</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>1043</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="A2">
+            <v>3000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>3001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>3003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1830,13 +2717,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1900,7 +2787,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="3">
-        <v>9131</v>
+        <v>1883</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>18</v>
@@ -1993,7 +2880,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
@@ -2003,24 +2890,24 @@
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:5">
+      <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -2034,7 +2921,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>45</v>
@@ -2042,13 +2929,13 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>46</v>
@@ -2056,13 +2943,13 @@
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>47</v>
@@ -2070,13 +2957,13 @@
       <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>48</v>
@@ -2090,7 +2977,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>51</v>
@@ -2104,7 +2991,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>52</v>
@@ -2118,7 +3005,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>53</v>
@@ -2128,6 +3015,20 @@
       </c>
       <c r="D9" s="3" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2140,89 +3041,91 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="7"/>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.5982905982906" style="3" customWidth="1"/>
     <col min="3" max="3" width="13.4615384615385" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.9316239316239" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.8034188034188" style="3" customWidth="1"/>
     <col min="5" max="5" width="44.5299145299145" style="3" customWidth="1"/>
-    <col min="6" max="10" width="12.1965811965812" style="3" customWidth="1"/>
+    <col min="6" max="7" width="12.1965811965812" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.6068376068376" style="3" customWidth="1"/>
+    <col min="9" max="10" width="12.1965811965812" style="3" customWidth="1"/>
     <col min="11" max="11" width="16.6666666666667" style="3" customWidth="1"/>
     <col min="12" max="16" width="12.1965811965812" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9.06837606837607" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:17">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:17">
+      <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="M1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="N1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="3">
         <f>devices!A2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>67</v>
+        <v>43</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3">
         <v>1000</v>
@@ -2230,29 +3133,32 @@
       <c r="G2" s="3">
         <v>500</v>
       </c>
-      <c r="L2" s="3">
-        <v>500000</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>69</v>
+      <c r="H2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="3">
+        <v>502</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="3">
         <f>devices!A3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="F3" s="3">
         <v>1000</v>
@@ -2264,7 +3170,7 @@
         <v>73</v>
       </c>
       <c r="I3" s="3">
-        <v>33434</v>
+        <v>502</v>
       </c>
       <c r="J3" s="3">
         <v>1</v>
@@ -2273,16 +3179,19 @@
     <row r="4" spans="1:17">
       <c r="A4" s="3">
         <f>devices!A4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>43</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="F4" s="3">
         <v>1000</v>
@@ -2290,38 +3199,32 @@
       <c r="G4" s="3">
         <v>500</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="3">
+        <v>502</v>
+      </c>
       <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M4" s="3">
-        <v>8</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3">
         <f>devices!A5</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>76</v>
+        <v>43</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="F5" s="3">
         <v>1000</v>
@@ -2329,38 +3232,29 @@
       <c r="G5" s="3">
         <v>500</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="3">
+        <v>502</v>
+      </c>
       <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="L5" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M5" s="3">
-        <v>8</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="3">
         <f>devices!A6</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F6" s="3">
         <v>1000</v>
@@ -2368,38 +3262,29 @@
       <c r="G6" s="3">
         <v>500</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="3">
+        <v>502</v>
+      </c>
       <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M6" s="3">
-        <v>8</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="3">
         <f>devices!A7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F7" s="3">
         <v>1000</v>
@@ -2407,38 +3292,29 @@
       <c r="G7" s="3">
         <v>500</v>
       </c>
+      <c r="H7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="3">
+        <v>502</v>
+      </c>
       <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L7" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M7" s="3">
-        <v>8</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="3">
         <f>devices!A8</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F8" s="3">
         <v>1000</v>
@@ -2446,23 +3322,67 @@
       <c r="G8" s="3">
         <v>500</v>
       </c>
+      <c r="H8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="3">
+        <v>502</v>
+      </c>
       <c r="J8" s="3">
         <v>1</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="L8" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M8" s="3">
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="3">
+        <f>devices!A9</f>
         <v>8</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="B9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>500</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="3">
+        <v>502</v>
+      </c>
+      <c r="J9" s="3">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="3">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -2475,12 +3395,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.7606837606838" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.6752136752137" style="2" customWidth="1"/>
-    <col min="3" max="3" width="144.854700854701" style="2" customWidth="1"/>
+    <col min="3" max="3" width="237.846153846154" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.3931623931624" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.2905982905983" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.4358974358974" style="2" customWidth="1"/>
@@ -2489,27 +3409,27 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>93</v>
+      <c r="A2" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)</f>
@@ -2520,11 +3440,11 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>93</v>
+      <c r="A3" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
@@ -2535,17 +3455,188 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>93</v>
+      <c r="A4" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
         <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029</v>
       </c>
       <c r="D4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$120)</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$120)</f>
+        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥控!$A$2:$A$120)</f>
+        <v>3000,3001,3002,3003</v>
+      </c>
+      <c r="D16" s="2">
         <v>1</v>
       </c>
     </row>

--- a/config/鸿合_配置_v2.0.xlsx
+++ b/config/鸿合_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="199">
   <si>
     <t>key</t>
   </si>
@@ -264,6 +265,9 @@
     <t>192.168.0.4</t>
   </si>
   <si>
+    <t>./config/BMS_鸿合国轩.xlsx</t>
+  </si>
+  <si>
     <t>192.168.1.104</t>
   </si>
   <si>
@@ -297,58 +301,337 @@
     <t>enable</t>
   </si>
   <si>
-    <t>/pcs/0/yx</t>
-  </si>
-  <si>
-    <t>/pcs/0/yc</t>
-  </si>
-  <si>
-    <t>/pcs/0/yt</t>
-  </si>
-  <si>
-    <t>/pcs/1/yx</t>
+    <t>/pds/pcs/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/pcs/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/pcs/0/yt</t>
+  </si>
+  <si>
+    <t>/pds/pcs/1/yx</t>
   </si>
   <si>
     <t>58,59,60,61,62,63,64,65,66,67,68,69,70,71</t>
   </si>
   <si>
-    <t>/pcs/1/yc</t>
+    <t>/pds/pcs/1/yc</t>
   </si>
   <si>
     <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57</t>
   </si>
   <si>
-    <t>/pcs/1/yt</t>
+    <t>/pds/pcs/1/yt</t>
   </si>
   <si>
     <t>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029</t>
   </si>
   <si>
-    <t>/pcs/2/yx</t>
-  </si>
-  <si>
-    <t>/pcs/2/yc</t>
-  </si>
-  <si>
-    <t>/pcs/2/yt</t>
-  </si>
-  <si>
-    <t>/pcs/3/yx</t>
-  </si>
-  <si>
-    <t>/pcs/3/yc</t>
-  </si>
-  <si>
-    <t>/pcs/3/yt</t>
-  </si>
-  <si>
-    <t>/crd/0/yx</t>
-  </si>
-  <si>
-    <t>/crd/0/yc</t>
-  </si>
-  <si>
-    <t>/crd/0/yk</t>
+    <t>/pds/pcs/2/yx</t>
+  </si>
+  <si>
+    <t>/pds/pcs/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/pcs/2/yt</t>
+  </si>
+  <si>
+    <t>/pds/pcs/3/yx</t>
+  </si>
+  <si>
+    <t>/pds/pcs/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/pcs/3/yt</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/yt</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/yt</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/yx</t>
+  </si>
+  <si>
+    <t>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/yc</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/yt</t>
+  </si>
+  <si>
+    <t>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/yt</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/4/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/5/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/0/yc</t>
+  </si>
+  <si>
+    <t>100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/1/yc</t>
+  </si>
+  <si>
+    <t>139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/2/yc</t>
+  </si>
+  <si>
+    <t>178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/3/yc</t>
+  </si>
+  <si>
+    <t>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,249,250,251,252,253,254,255</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/4/yc</t>
+  </si>
+  <si>
+    <t>256,257,258,259,260,261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,281,282,283,284,285,286,287,288,289,290,291,292,293,294</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/5/yc</t>
+  </si>
+  <si>
+    <t>295,296,297,298,299,300,301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/4/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/5/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/4/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/5/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/cell/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/cell/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/cell/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/cell/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/cell/4/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/cell/5/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/cell/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/cell/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/cell/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/cell/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/cell/4/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/cell/5/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/cell/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/cell/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/cell/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/cell/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/cell/4/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/cell/5/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/cell/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/cell/1/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/cell/2/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/cell/3/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/cell/4/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/cell/5/yc</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/1/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/2/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/3/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/4/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/0/rack/5/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/1/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/2/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/3/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/4/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/1/rack/5/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/1/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/2/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/3/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/4/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/2/rack/5/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/1/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/2/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/3/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/4/yx</t>
+  </si>
+  <si>
+    <t>/pds/bank/3/rack/5/yx</t>
+  </si>
+  <si>
+    <t>/pds/crd/0/yx</t>
+  </si>
+  <si>
+    <t>/pds/crd/0/yc</t>
+  </si>
+  <si>
+    <t>/pds/crd/0/yk</t>
   </si>
 </sst>
 </file>
@@ -386,15 +669,15 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1013,7 +1296,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1030,6 +1313,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2186,26 +2478,6 @@
             <v>113</v>
           </cell>
         </row>
-        <row r="115">
-          <cell r="A115">
-            <v>114</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116">
-            <v>115</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117">
-            <v>116</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118">
-            <v>117</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="2">
@@ -2453,6 +2725,5791 @@
       </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="遥测"/>
+      <sheetName val="遥调"/>
+      <sheetName val="遥信"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>34</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>35</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>37</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>39</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>41</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>42</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>43</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>45</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>46</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>47</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>49</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>51</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>52</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>101</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>102</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>104</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>106</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>107</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>108</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>109</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>112</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>113</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>114</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>116</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>117</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>118</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>119</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>121</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>122</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>123</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>124</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>125</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>126</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>127</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>128</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>129</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>130</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>131</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>132</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>133</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>134</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>136</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>137</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>138</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>139</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>140</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>141</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>142</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>143</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>144</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>146</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>147</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>148</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>149</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>150</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>151</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>152</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>153</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>154</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>155</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>156</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>157</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>158</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>159</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>160</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>161</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>162</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>163</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>164</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119">
+            <v>165</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120">
+            <v>166</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121">
+            <v>167</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122">
+            <v>168</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123">
+            <v>169</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
+            <v>170</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125">
+            <v>171</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126">
+            <v>172</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127">
+            <v>173</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128">
+            <v>174</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129">
+            <v>175</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130">
+            <v>176</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131">
+            <v>177</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132">
+            <v>178</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133">
+            <v>179</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134">
+            <v>180</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135">
+            <v>181</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136">
+            <v>182</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137">
+            <v>183</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138">
+            <v>184</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139">
+            <v>185</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140">
+            <v>186</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141">
+            <v>187</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142">
+            <v>188</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143">
+            <v>189</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144">
+            <v>190</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145">
+            <v>191</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146">
+            <v>192</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147">
+            <v>193</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148">
+            <v>194</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149">
+            <v>195</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150">
+            <v>196</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151">
+            <v>197</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152">
+            <v>198</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153">
+            <v>199</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155">
+            <v>201</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156">
+            <v>202</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157">
+            <v>203</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158">
+            <v>204</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159">
+            <v>205</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160">
+            <v>206</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161">
+            <v>207</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162">
+            <v>208</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163">
+            <v>209</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164">
+            <v>210</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165">
+            <v>211</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166">
+            <v>212</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167">
+            <v>213</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>214</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>215</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>216</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171">
+            <v>217</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172">
+            <v>218</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173">
+            <v>219</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174">
+            <v>220</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="A175">
+            <v>221</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="A176">
+            <v>222</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="A177">
+            <v>223</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="A178">
+            <v>224</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="A179">
+            <v>225</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="A180">
+            <v>226</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="A181">
+            <v>227</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="A182">
+            <v>228</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="A183">
+            <v>229</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="A184">
+            <v>230</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="A185">
+            <v>231</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="A186">
+            <v>232</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="A187">
+            <v>233</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="A188">
+            <v>234</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="A189">
+            <v>235</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="A190">
+            <v>236</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="A191">
+            <v>237</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="A192">
+            <v>238</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="A193">
+            <v>239</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="A194">
+            <v>240</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="A195">
+            <v>241</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="A196">
+            <v>242</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="A197">
+            <v>243</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="A198">
+            <v>244</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="A199">
+            <v>245</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="A200">
+            <v>246</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="A201">
+            <v>247</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="A202">
+            <v>248</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="A203">
+            <v>249</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="A204">
+            <v>250</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="A205">
+            <v>251</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="A206">
+            <v>252</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="A207">
+            <v>253</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="A208">
+            <v>254</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="A209">
+            <v>255</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="A210">
+            <v>256</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="A211">
+            <v>257</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="A212">
+            <v>258</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="A213">
+            <v>259</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="A214">
+            <v>260</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="A215">
+            <v>261</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="A216">
+            <v>262</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="A217">
+            <v>263</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="A218">
+            <v>264</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="A219">
+            <v>265</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="A220">
+            <v>266</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="A221">
+            <v>267</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="A222">
+            <v>268</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="A223">
+            <v>269</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="A224">
+            <v>270</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="A225">
+            <v>271</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="A226">
+            <v>272</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="A227">
+            <v>273</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="A228">
+            <v>274</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="A229">
+            <v>275</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="A230">
+            <v>276</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="A231">
+            <v>277</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="A232">
+            <v>278</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="A233">
+            <v>279</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="A234">
+            <v>280</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="A235">
+            <v>281</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="A236">
+            <v>282</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="A237">
+            <v>283</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="A238">
+            <v>284</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="A239">
+            <v>285</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="A240">
+            <v>286</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="A241">
+            <v>287</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="A242">
+            <v>288</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="A243">
+            <v>289</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="A244">
+            <v>290</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="A245">
+            <v>291</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="A246">
+            <v>292</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="A247">
+            <v>293</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="A248">
+            <v>294</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="A249">
+            <v>295</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="A250">
+            <v>296</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="A251">
+            <v>297</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="A252">
+            <v>298</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="A253">
+            <v>299</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="A254">
+            <v>300</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="A255">
+            <v>301</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="A256">
+            <v>302</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="A257">
+            <v>303</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="A258">
+            <v>304</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="A259">
+            <v>305</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="A260">
+            <v>306</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="A261">
+            <v>307</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="A262">
+            <v>308</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="A263">
+            <v>309</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="A264">
+            <v>310</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="A265">
+            <v>311</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="A266">
+            <v>312</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="A267">
+            <v>313</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="A268">
+            <v>314</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="A269">
+            <v>315</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="A270">
+            <v>316</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="A271">
+            <v>317</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="A272">
+            <v>318</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="A273">
+            <v>319</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="A274">
+            <v>320</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="A275">
+            <v>321</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="A276">
+            <v>322</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="A277">
+            <v>323</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="A278">
+            <v>324</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="A279">
+            <v>325</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="A280">
+            <v>326</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="A281">
+            <v>327</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="A282">
+            <v>328</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="A283">
+            <v>329</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="A284">
+            <v>330</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="A285">
+            <v>331</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="A286">
+            <v>332</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="A287">
+            <v>333</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="A300">
+            <v>600</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="A301">
+            <v>601</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="A302">
+            <v>602</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="A303">
+            <v>603</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="A304">
+            <v>604</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="A305">
+            <v>605</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="A306">
+            <v>606</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="A307">
+            <v>607</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="A308">
+            <v>608</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="A309">
+            <v>609</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="A310">
+            <v>610</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="A311">
+            <v>611</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="A312">
+            <v>612</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="A313">
+            <v>613</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="A314">
+            <v>614</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="A315">
+            <v>615</v>
+          </cell>
+        </row>
+        <row r="316">
+          <cell r="A316">
+            <v>616</v>
+          </cell>
+        </row>
+        <row r="317">
+          <cell r="A317">
+            <v>617</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="A2">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>2002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>2003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>2004</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>2006</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>2007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>2008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>2009</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>2011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>2012</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>2013</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>2014</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>2015</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>2016</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>2017</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>2018</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="A2">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>1001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>1002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>1003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>1004</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>1005</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>1006</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>1007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>1008</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>1009</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>1010</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>1011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>1012</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>1013</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1014</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1015</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>1016</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>1017</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>1018</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>1019</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>1020</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>1021</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>1022</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>1023</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>1024</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>1025</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>1026</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>1027</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>1028</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>1029</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>1030</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>1031</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>1032</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>1033</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>1034</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>1035</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>1036</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>1037</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>1038</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>1039</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>1040</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>1041</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>1042</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>1043</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>1044</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>1045</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>1046</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>1047</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>1048</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>1049</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>1050</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>1051</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>1052</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>1053</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>1054</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>1055</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>1056</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>1057</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>1058</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>1059</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>1060</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>1061</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>1062</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>1063</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>1064</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>1065</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>1066</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>1067</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>1068</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>1069</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>1070</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>1071</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>1072</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>1073</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>1074</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>1075</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>1076</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>1077</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>1078</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>1079</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>1080</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>1081</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>1082</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>1083</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>1084</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>1085</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>1086</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>1087</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>1088</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>1089</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>1090</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>1091</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>1092</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>1093</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>1094</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>1095</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>1096</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>1097</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>1098</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>1099</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>1100</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>1101</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>1102</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>1103</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>1104</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>1105</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>1106</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>1107</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>1108</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>1109</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>1110</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>1111</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>1112</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>1113</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>1114</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>1115</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>1116</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119">
+            <v>1117</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120">
+            <v>1118</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121">
+            <v>1119</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122">
+            <v>1120</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123">
+            <v>1121</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
+            <v>1122</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125">
+            <v>1123</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126">
+            <v>1124</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127">
+            <v>1125</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128">
+            <v>1126</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129">
+            <v>1127</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130">
+            <v>1128</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131">
+            <v>1129</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132">
+            <v>1130</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133">
+            <v>1131</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134">
+            <v>1132</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135">
+            <v>1133</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136">
+            <v>1134</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137">
+            <v>1135</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138">
+            <v>1136</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139">
+            <v>1137</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140">
+            <v>1138</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141">
+            <v>1139</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142">
+            <v>1500</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143">
+            <v>1501</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144">
+            <v>1502</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145">
+            <v>1503</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146">
+            <v>1504</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147">
+            <v>1505</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148">
+            <v>1506</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149">
+            <v>1507</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150">
+            <v>1508</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151">
+            <v>1509</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152">
+            <v>1510</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153">
+            <v>1511</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154">
+            <v>1512</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155">
+            <v>1513</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156">
+            <v>1514</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157">
+            <v>1515</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158">
+            <v>1516</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159">
+            <v>1517</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160">
+            <v>1518</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161">
+            <v>1519</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162">
+            <v>1520</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163">
+            <v>1521</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164">
+            <v>1522</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165">
+            <v>1523</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166">
+            <v>1524</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167">
+            <v>1525</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>1526</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>1527</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>1528</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171">
+            <v>1529</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172">
+            <v>1530</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173">
+            <v>1531</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174">
+            <v>1532</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="A175">
+            <v>1533</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="A176">
+            <v>1534</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="A177">
+            <v>1535</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="A178">
+            <v>1536</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="A179">
+            <v>1537</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="A180">
+            <v>1538</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="A181">
+            <v>1539</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="A182">
+            <v>1540</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="A183">
+            <v>1541</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="A184">
+            <v>1542</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="A185">
+            <v>1543</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="A186">
+            <v>1544</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="A187">
+            <v>1545</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="A188">
+            <v>1546</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="A189">
+            <v>1547</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="A190">
+            <v>1548</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="A191">
+            <v>1549</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="A192">
+            <v>1550</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="A193">
+            <v>1551</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="A194">
+            <v>1552</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="A195">
+            <v>1553</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="A196">
+            <v>1554</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="A197">
+            <v>1555</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="A198">
+            <v>1556</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="A199">
+            <v>1557</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="A200">
+            <v>1558</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="A201">
+            <v>1559</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="A202">
+            <v>1560</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="A203">
+            <v>1561</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="A204">
+            <v>1562</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="A205">
+            <v>1563</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="A206">
+            <v>1564</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="A207">
+            <v>1565</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="A208">
+            <v>1566</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="A209">
+            <v>1567</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="A210">
+            <v>1568</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="A211">
+            <v>1569</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="A212">
+            <v>1570</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="A213">
+            <v>1571</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="A214">
+            <v>1572</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="A215">
+            <v>1573</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="A216">
+            <v>1574</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="A217">
+            <v>1575</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="A218">
+            <v>1576</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="A219">
+            <v>1577</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="A220">
+            <v>1578</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="A221">
+            <v>1579</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="A222">
+            <v>1580</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="A223">
+            <v>1581</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="A224">
+            <v>1582</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="A225">
+            <v>1583</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="A226">
+            <v>1584</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="A227">
+            <v>1585</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="A228">
+            <v>1586</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="A229">
+            <v>1587</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="A230">
+            <v>1588</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="A231">
+            <v>1589</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="A232">
+            <v>1590</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="A233">
+            <v>1591</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="A234">
+            <v>1592</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="A235">
+            <v>1593</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="A236">
+            <v>1594</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="A237">
+            <v>1595</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="A238">
+            <v>1596</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="A239">
+            <v>1597</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="A240">
+            <v>1598</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="A241">
+            <v>1599</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="A242">
+            <v>1600</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="A243">
+            <v>1601</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="A244">
+            <v>1602</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="A245">
+            <v>1603</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="A246">
+            <v>1604</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="A247">
+            <v>1605</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="A248">
+            <v>1606</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="A249">
+            <v>1607</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="A250">
+            <v>1608</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="A251">
+            <v>1609</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="A252">
+            <v>1610</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="A253">
+            <v>1611</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="A254">
+            <v>1612</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="A255">
+            <v>1613</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="A256">
+            <v>1614</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="A257">
+            <v>1615</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="A258">
+            <v>1616</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="A259">
+            <v>1617</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="A260">
+            <v>1618</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="A261">
+            <v>1619</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="A262">
+            <v>1620</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="A263">
+            <v>1621</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="A264">
+            <v>1622</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="A265">
+            <v>1623</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="A266">
+            <v>1624</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="A267">
+            <v>1625</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="A268">
+            <v>1626</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="A269">
+            <v>1627</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="A270">
+            <v>1628</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="A271">
+            <v>1629</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="A272">
+            <v>1630</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="A273">
+            <v>1631</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="A274">
+            <v>1632</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="A275">
+            <v>1633</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="A276">
+            <v>1634</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="A277">
+            <v>1635</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="A278">
+            <v>1636</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="A279">
+            <v>1637</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="A280">
+            <v>1638</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="A281">
+            <v>1639</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="A282">
+            <v>1640</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="A283">
+            <v>1641</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="A284">
+            <v>1642</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="A285">
+            <v>1643</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="A286">
+            <v>1644</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="A287">
+            <v>1645</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="A288">
+            <v>1646</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="A289">
+            <v>1647</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="A290">
+            <v>1648</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="A291">
+            <v>1649</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="A292">
+            <v>1650</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="A293">
+            <v>1651</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="A294">
+            <v>1652</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="A295">
+            <v>1653</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="A296">
+            <v>1654</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="A297">
+            <v>1655</v>
+          </cell>
+        </row>
+        <row r="298">
+          <cell r="A298">
+            <v>1656</v>
+          </cell>
+        </row>
+        <row r="299">
+          <cell r="A299">
+            <v>1657</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="A300">
+            <v>1658</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="A301">
+            <v>1659</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="A302">
+            <v>1660</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="A303">
+            <v>1661</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="A304">
+            <v>1662</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="A305">
+            <v>1663</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="A306">
+            <v>1664</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="A307">
+            <v>1665</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="A308">
+            <v>1666</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="A309">
+            <v>1667</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="A310">
+            <v>1668</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="A311">
+            <v>1669</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="A312">
+            <v>1670</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="A313">
+            <v>1671</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="A314">
+            <v>1672</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="A315">
+            <v>1673</v>
+          </cell>
+        </row>
+        <row r="316">
+          <cell r="A316">
+            <v>1674</v>
+          </cell>
+        </row>
+        <row r="317">
+          <cell r="A317">
+            <v>1675</v>
+          </cell>
+        </row>
+        <row r="318">
+          <cell r="A318">
+            <v>1676</v>
+          </cell>
+        </row>
+        <row r="319">
+          <cell r="A319">
+            <v>1677</v>
+          </cell>
+        </row>
+        <row r="320">
+          <cell r="A320">
+            <v>1678</v>
+          </cell>
+        </row>
+        <row r="321">
+          <cell r="A321">
+            <v>1679</v>
+          </cell>
+        </row>
+        <row r="322">
+          <cell r="A322">
+            <v>1680</v>
+          </cell>
+        </row>
+        <row r="323">
+          <cell r="A323">
+            <v>1681</v>
+          </cell>
+        </row>
+        <row r="324">
+          <cell r="A324">
+            <v>1682</v>
+          </cell>
+        </row>
+        <row r="325">
+          <cell r="A325">
+            <v>1683</v>
+          </cell>
+        </row>
+        <row r="326">
+          <cell r="A326">
+            <v>1684</v>
+          </cell>
+        </row>
+        <row r="327">
+          <cell r="A327">
+            <v>1685</v>
+          </cell>
+        </row>
+        <row r="328">
+          <cell r="A328">
+            <v>1686</v>
+          </cell>
+        </row>
+        <row r="329">
+          <cell r="A329">
+            <v>1687</v>
+          </cell>
+        </row>
+        <row r="330">
+          <cell r="A330">
+            <v>1688</v>
+          </cell>
+        </row>
+        <row r="331">
+          <cell r="A331">
+            <v>1689</v>
+          </cell>
+        </row>
+        <row r="332">
+          <cell r="A332">
+            <v>1690</v>
+          </cell>
+        </row>
+        <row r="333">
+          <cell r="A333">
+            <v>1691</v>
+          </cell>
+        </row>
+        <row r="334">
+          <cell r="A334">
+            <v>1692</v>
+          </cell>
+        </row>
+        <row r="335">
+          <cell r="A335">
+            <v>1693</v>
+          </cell>
+        </row>
+        <row r="336">
+          <cell r="A336">
+            <v>1694</v>
+          </cell>
+        </row>
+        <row r="337">
+          <cell r="A337">
+            <v>1695</v>
+          </cell>
+        </row>
+        <row r="338">
+          <cell r="A338">
+            <v>1696</v>
+          </cell>
+        </row>
+        <row r="339">
+          <cell r="A339">
+            <v>1697</v>
+          </cell>
+        </row>
+        <row r="340">
+          <cell r="A340">
+            <v>1698</v>
+          </cell>
+        </row>
+        <row r="341">
+          <cell r="A341">
+            <v>1699</v>
+          </cell>
+        </row>
+        <row r="342">
+          <cell r="A342">
+            <v>1700</v>
+          </cell>
+        </row>
+        <row r="343">
+          <cell r="A343">
+            <v>1701</v>
+          </cell>
+        </row>
+        <row r="344">
+          <cell r="A344">
+            <v>1702</v>
+          </cell>
+        </row>
+        <row r="345">
+          <cell r="A345">
+            <v>1703</v>
+          </cell>
+        </row>
+        <row r="346">
+          <cell r="A346">
+            <v>1704</v>
+          </cell>
+        </row>
+        <row r="347">
+          <cell r="A347">
+            <v>1705</v>
+          </cell>
+        </row>
+        <row r="348">
+          <cell r="A348">
+            <v>1706</v>
+          </cell>
+        </row>
+        <row r="349">
+          <cell r="A349">
+            <v>1707</v>
+          </cell>
+        </row>
+        <row r="350">
+          <cell r="A350">
+            <v>1708</v>
+          </cell>
+        </row>
+        <row r="351">
+          <cell r="A351">
+            <v>1709</v>
+          </cell>
+        </row>
+        <row r="352">
+          <cell r="A352">
+            <v>1710</v>
+          </cell>
+        </row>
+        <row r="353">
+          <cell r="A353">
+            <v>1711</v>
+          </cell>
+        </row>
+        <row r="354">
+          <cell r="A354">
+            <v>1712</v>
+          </cell>
+        </row>
+        <row r="355">
+          <cell r="A355">
+            <v>1713</v>
+          </cell>
+        </row>
+        <row r="356">
+          <cell r="A356">
+            <v>1714</v>
+          </cell>
+        </row>
+        <row r="357">
+          <cell r="A357">
+            <v>1715</v>
+          </cell>
+        </row>
+        <row r="358">
+          <cell r="A358">
+            <v>1716</v>
+          </cell>
+        </row>
+        <row r="359">
+          <cell r="A359">
+            <v>1717</v>
+          </cell>
+        </row>
+        <row r="360">
+          <cell r="A360">
+            <v>1718</v>
+          </cell>
+        </row>
+        <row r="361">
+          <cell r="A361">
+            <v>1719</v>
+          </cell>
+        </row>
+        <row r="362">
+          <cell r="A362">
+            <v>1720</v>
+          </cell>
+        </row>
+        <row r="363">
+          <cell r="A363">
+            <v>1721</v>
+          </cell>
+        </row>
+        <row r="364">
+          <cell r="A364">
+            <v>1722</v>
+          </cell>
+        </row>
+        <row r="365">
+          <cell r="A365">
+            <v>1723</v>
+          </cell>
+        </row>
+        <row r="366">
+          <cell r="A366">
+            <v>1724</v>
+          </cell>
+        </row>
+        <row r="367">
+          <cell r="A367">
+            <v>1725</v>
+          </cell>
+        </row>
+        <row r="368">
+          <cell r="A368">
+            <v>1726</v>
+          </cell>
+        </row>
+        <row r="369">
+          <cell r="A369">
+            <v>1727</v>
+          </cell>
+        </row>
+        <row r="370">
+          <cell r="A370">
+            <v>1728</v>
+          </cell>
+        </row>
+        <row r="371">
+          <cell r="A371">
+            <v>1729</v>
+          </cell>
+        </row>
+        <row r="372">
+          <cell r="A372">
+            <v>1730</v>
+          </cell>
+        </row>
+        <row r="373">
+          <cell r="A373">
+            <v>1731</v>
+          </cell>
+        </row>
+        <row r="374">
+          <cell r="A374">
+            <v>1732</v>
+          </cell>
+        </row>
+        <row r="375">
+          <cell r="A375">
+            <v>1733</v>
+          </cell>
+        </row>
+        <row r="376">
+          <cell r="A376">
+            <v>1734</v>
+          </cell>
+        </row>
+        <row r="377">
+          <cell r="A377">
+            <v>1735</v>
+          </cell>
+        </row>
+        <row r="378">
+          <cell r="A378">
+            <v>1736</v>
+          </cell>
+        </row>
+        <row r="379">
+          <cell r="A379">
+            <v>1737</v>
+          </cell>
+        </row>
+        <row r="380">
+          <cell r="A380">
+            <v>1738</v>
+          </cell>
+        </row>
+        <row r="381">
+          <cell r="A381">
+            <v>1739</v>
+          </cell>
+        </row>
+        <row r="382">
+          <cell r="A382">
+            <v>1740</v>
+          </cell>
+        </row>
+        <row r="383">
+          <cell r="A383">
+            <v>1741</v>
+          </cell>
+        </row>
+        <row r="384">
+          <cell r="A384">
+            <v>1742</v>
+          </cell>
+        </row>
+        <row r="385">
+          <cell r="A385">
+            <v>1743</v>
+          </cell>
+        </row>
+        <row r="386">
+          <cell r="A386">
+            <v>1744</v>
+          </cell>
+        </row>
+        <row r="387">
+          <cell r="A387">
+            <v>1745</v>
+          </cell>
+        </row>
+        <row r="388">
+          <cell r="A388">
+            <v>1746</v>
+          </cell>
+        </row>
+        <row r="389">
+          <cell r="A389">
+            <v>1747</v>
+          </cell>
+        </row>
+        <row r="390">
+          <cell r="A390">
+            <v>1748</v>
+          </cell>
+        </row>
+        <row r="391">
+          <cell r="A391">
+            <v>1749</v>
+          </cell>
+        </row>
+        <row r="392">
+          <cell r="A392">
+            <v>1750</v>
+          </cell>
+        </row>
+        <row r="393">
+          <cell r="A393">
+            <v>1751</v>
+          </cell>
+        </row>
+        <row r="394">
+          <cell r="A394">
+            <v>1752</v>
+          </cell>
+        </row>
+        <row r="395">
+          <cell r="A395">
+            <v>1753</v>
+          </cell>
+        </row>
+        <row r="396">
+          <cell r="A396">
+            <v>1754</v>
+          </cell>
+        </row>
+        <row r="397">
+          <cell r="A397">
+            <v>1755</v>
+          </cell>
+        </row>
+        <row r="398">
+          <cell r="A398">
+            <v>1756</v>
+          </cell>
+        </row>
+        <row r="399">
+          <cell r="A399">
+            <v>1757</v>
+          </cell>
+        </row>
+        <row r="400">
+          <cell r="A400">
+            <v>1758</v>
+          </cell>
+        </row>
+        <row r="401">
+          <cell r="A401">
+            <v>1759</v>
+          </cell>
+        </row>
+        <row r="402">
+          <cell r="A402">
+            <v>1760</v>
+          </cell>
+        </row>
+        <row r="403">
+          <cell r="A403">
+            <v>1761</v>
+          </cell>
+        </row>
+        <row r="404">
+          <cell r="A404">
+            <v>1762</v>
+          </cell>
+        </row>
+        <row r="405">
+          <cell r="A405">
+            <v>1763</v>
+          </cell>
+        </row>
+        <row r="406">
+          <cell r="A406">
+            <v>1764</v>
+          </cell>
+        </row>
+        <row r="407">
+          <cell r="A407">
+            <v>1765</v>
+          </cell>
+        </row>
+        <row r="408">
+          <cell r="A408">
+            <v>1766</v>
+          </cell>
+        </row>
+        <row r="409">
+          <cell r="A409">
+            <v>1767</v>
+          </cell>
+        </row>
+        <row r="410">
+          <cell r="A410">
+            <v>1768</v>
+          </cell>
+        </row>
+        <row r="411">
+          <cell r="A411">
+            <v>1769</v>
+          </cell>
+        </row>
+        <row r="412">
+          <cell r="A412">
+            <v>1770</v>
+          </cell>
+        </row>
+        <row r="413">
+          <cell r="A413">
+            <v>1771</v>
+          </cell>
+        </row>
+        <row r="414">
+          <cell r="A414">
+            <v>1772</v>
+          </cell>
+        </row>
+        <row r="415">
+          <cell r="A415">
+            <v>1773</v>
+          </cell>
+        </row>
+        <row r="416">
+          <cell r="A416">
+            <v>1774</v>
+          </cell>
+        </row>
+        <row r="417">
+          <cell r="A417">
+            <v>1775</v>
+          </cell>
+        </row>
+        <row r="418">
+          <cell r="A418">
+            <v>1776</v>
+          </cell>
+        </row>
+        <row r="419">
+          <cell r="A419">
+            <v>1777</v>
+          </cell>
+        </row>
+        <row r="420">
+          <cell r="A420">
+            <v>1778</v>
+          </cell>
+        </row>
+        <row r="421">
+          <cell r="A421">
+            <v>1779</v>
+          </cell>
+        </row>
+        <row r="422">
+          <cell r="A422">
+            <v>1780</v>
+          </cell>
+        </row>
+        <row r="423">
+          <cell r="A423">
+            <v>1781</v>
+          </cell>
+        </row>
+        <row r="424">
+          <cell r="A424">
+            <v>1782</v>
+          </cell>
+        </row>
+        <row r="425">
+          <cell r="A425">
+            <v>1783</v>
+          </cell>
+        </row>
+        <row r="426">
+          <cell r="A426">
+            <v>1784</v>
+          </cell>
+        </row>
+        <row r="427">
+          <cell r="A427">
+            <v>1785</v>
+          </cell>
+        </row>
+        <row r="428">
+          <cell r="A428">
+            <v>1786</v>
+          </cell>
+        </row>
+        <row r="429">
+          <cell r="A429">
+            <v>1787</v>
+          </cell>
+        </row>
+        <row r="430">
+          <cell r="A430">
+            <v>1788</v>
+          </cell>
+        </row>
+        <row r="431">
+          <cell r="A431">
+            <v>1789</v>
+          </cell>
+        </row>
+        <row r="432">
+          <cell r="A432">
+            <v>1790</v>
+          </cell>
+        </row>
+        <row r="433">
+          <cell r="A433">
+            <v>1791</v>
+          </cell>
+        </row>
+        <row r="434">
+          <cell r="A434">
+            <v>1792</v>
+          </cell>
+        </row>
+        <row r="435">
+          <cell r="A435">
+            <v>1793</v>
+          </cell>
+        </row>
+        <row r="436">
+          <cell r="A436">
+            <v>1794</v>
+          </cell>
+        </row>
+        <row r="437">
+          <cell r="A437">
+            <v>1795</v>
+          </cell>
+        </row>
+        <row r="438">
+          <cell r="A438">
+            <v>1796</v>
+          </cell>
+        </row>
+        <row r="439">
+          <cell r="A439">
+            <v>1797</v>
+          </cell>
+        </row>
+        <row r="440">
+          <cell r="A440">
+            <v>1798</v>
+          </cell>
+        </row>
+        <row r="441">
+          <cell r="A441">
+            <v>1799</v>
+          </cell>
+        </row>
+        <row r="442">
+          <cell r="A442">
+            <v>1800</v>
+          </cell>
+        </row>
+        <row r="443">
+          <cell r="A443">
+            <v>1801</v>
+          </cell>
+        </row>
+        <row r="444">
+          <cell r="A444">
+            <v>1802</v>
+          </cell>
+        </row>
+        <row r="445">
+          <cell r="A445">
+            <v>1803</v>
+          </cell>
+        </row>
+        <row r="446">
+          <cell r="A446">
+            <v>1804</v>
+          </cell>
+        </row>
+        <row r="447">
+          <cell r="A447">
+            <v>1805</v>
+          </cell>
+        </row>
+        <row r="448">
+          <cell r="A448">
+            <v>1806</v>
+          </cell>
+        </row>
+        <row r="449">
+          <cell r="A449">
+            <v>1807</v>
+          </cell>
+        </row>
+        <row r="450">
+          <cell r="A450">
+            <v>1808</v>
+          </cell>
+        </row>
+        <row r="451">
+          <cell r="A451">
+            <v>1809</v>
+          </cell>
+        </row>
+        <row r="452">
+          <cell r="A452">
+            <v>1810</v>
+          </cell>
+        </row>
+        <row r="453">
+          <cell r="A453">
+            <v>1811</v>
+          </cell>
+        </row>
+        <row r="454">
+          <cell r="A454">
+            <v>1812</v>
+          </cell>
+        </row>
+        <row r="455">
+          <cell r="A455">
+            <v>1813</v>
+          </cell>
+        </row>
+        <row r="456">
+          <cell r="A456">
+            <v>1814</v>
+          </cell>
+        </row>
+        <row r="457">
+          <cell r="A457">
+            <v>1815</v>
+          </cell>
+        </row>
+        <row r="458">
+          <cell r="A458">
+            <v>1816</v>
+          </cell>
+        </row>
+        <row r="459">
+          <cell r="A459">
+            <v>1817</v>
+          </cell>
+        </row>
+        <row r="460">
+          <cell r="A460">
+            <v>1818</v>
+          </cell>
+        </row>
+        <row r="461">
+          <cell r="A461">
+            <v>1819</v>
+          </cell>
+        </row>
+        <row r="462">
+          <cell r="A462">
+            <v>1820</v>
+          </cell>
+        </row>
+        <row r="463">
+          <cell r="A463">
+            <v>1821</v>
+          </cell>
+        </row>
+        <row r="464">
+          <cell r="A464">
+            <v>1822</v>
+          </cell>
+        </row>
+        <row r="465">
+          <cell r="A465">
+            <v>1823</v>
+          </cell>
+        </row>
+        <row r="466">
+          <cell r="A466">
+            <v>1824</v>
+          </cell>
+        </row>
+        <row r="467">
+          <cell r="A467">
+            <v>1825</v>
+          </cell>
+        </row>
+        <row r="468">
+          <cell r="A468">
+            <v>1826</v>
+          </cell>
+        </row>
+        <row r="469">
+          <cell r="A469">
+            <v>1827</v>
+          </cell>
+        </row>
+        <row r="470">
+          <cell r="A470">
+            <v>1828</v>
+          </cell>
+        </row>
+        <row r="471">
+          <cell r="A471">
+            <v>1829</v>
+          </cell>
+        </row>
+        <row r="472">
+          <cell r="A472">
+            <v>1830</v>
+          </cell>
+        </row>
+        <row r="473">
+          <cell r="A473">
+            <v>1831</v>
+          </cell>
+        </row>
+        <row r="474">
+          <cell r="A474">
+            <v>1832</v>
+          </cell>
+        </row>
+        <row r="475">
+          <cell r="A475">
+            <v>1833</v>
+          </cell>
+        </row>
+        <row r="476">
+          <cell r="A476">
+            <v>1834</v>
+          </cell>
+        </row>
+        <row r="477">
+          <cell r="A477">
+            <v>1835</v>
+          </cell>
+        </row>
+        <row r="478">
+          <cell r="A478">
+            <v>1836</v>
+          </cell>
+        </row>
+        <row r="479">
+          <cell r="A479">
+            <v>1837</v>
+          </cell>
+        </row>
+        <row r="480">
+          <cell r="A480">
+            <v>1838</v>
+          </cell>
+        </row>
+        <row r="481">
+          <cell r="A481">
+            <v>1839</v>
+          </cell>
+        </row>
+        <row r="482">
+          <cell r="A482">
+            <v>1840</v>
+          </cell>
+        </row>
+        <row r="483">
+          <cell r="A483">
+            <v>1841</v>
+          </cell>
+        </row>
+        <row r="484">
+          <cell r="A484">
+            <v>1842</v>
+          </cell>
+        </row>
+        <row r="485">
+          <cell r="A485">
+            <v>1843</v>
+          </cell>
+        </row>
+        <row r="486">
+          <cell r="A486">
+            <v>1844</v>
+          </cell>
+        </row>
+        <row r="487">
+          <cell r="A487">
+            <v>1845</v>
+          </cell>
+        </row>
+        <row r="488">
+          <cell r="A488">
+            <v>1846</v>
+          </cell>
+        </row>
+        <row r="489">
+          <cell r="A489">
+            <v>1847</v>
+          </cell>
+        </row>
+        <row r="490">
+          <cell r="A490">
+            <v>1848</v>
+          </cell>
+        </row>
+        <row r="491">
+          <cell r="A491">
+            <v>1849</v>
+          </cell>
+        </row>
+        <row r="492">
+          <cell r="A492">
+            <v>1850</v>
+          </cell>
+        </row>
+        <row r="493">
+          <cell r="A493">
+            <v>1851</v>
+          </cell>
+        </row>
+        <row r="494">
+          <cell r="A494">
+            <v>1852</v>
+          </cell>
+        </row>
+        <row r="495">
+          <cell r="A495">
+            <v>1853</v>
+          </cell>
+        </row>
+        <row r="496">
+          <cell r="A496">
+            <v>1854</v>
+          </cell>
+        </row>
+        <row r="497">
+          <cell r="A497">
+            <v>1855</v>
+          </cell>
+        </row>
+        <row r="498">
+          <cell r="A498">
+            <v>1856</v>
+          </cell>
+        </row>
+        <row r="499">
+          <cell r="A499">
+            <v>1857</v>
+          </cell>
+        </row>
+        <row r="500">
+          <cell r="A500">
+            <v>1858</v>
+          </cell>
+        </row>
+        <row r="501">
+          <cell r="A501">
+            <v>1859</v>
+          </cell>
+        </row>
+        <row r="502">
+          <cell r="A502">
+            <v>1860</v>
+          </cell>
+        </row>
+        <row r="503">
+          <cell r="A503">
+            <v>1861</v>
+          </cell>
+        </row>
+        <row r="504">
+          <cell r="A504">
+            <v>1862</v>
+          </cell>
+        </row>
+        <row r="505">
+          <cell r="A505">
+            <v>1863</v>
+          </cell>
+        </row>
+        <row r="506">
+          <cell r="A506">
+            <v>1864</v>
+          </cell>
+        </row>
+        <row r="507">
+          <cell r="A507">
+            <v>1865</v>
+          </cell>
+        </row>
+        <row r="508">
+          <cell r="A508">
+            <v>1866</v>
+          </cell>
+        </row>
+        <row r="509">
+          <cell r="A509">
+            <v>1867</v>
+          </cell>
+        </row>
+        <row r="510">
+          <cell r="A510">
+            <v>1868</v>
+          </cell>
+        </row>
+        <row r="511">
+          <cell r="A511">
+            <v>1869</v>
+          </cell>
+        </row>
+        <row r="512">
+          <cell r="A512">
+            <v>1870</v>
+          </cell>
+        </row>
+        <row r="513">
+          <cell r="A513">
+            <v>1871</v>
+          </cell>
+        </row>
+        <row r="514">
+          <cell r="A514">
+            <v>1872</v>
+          </cell>
+        </row>
+        <row r="515">
+          <cell r="A515">
+            <v>1873</v>
+          </cell>
+        </row>
+        <row r="516">
+          <cell r="A516">
+            <v>1874</v>
+          </cell>
+        </row>
+        <row r="517">
+          <cell r="A517">
+            <v>1875</v>
+          </cell>
+        </row>
+        <row r="518">
+          <cell r="A518">
+            <v>1876</v>
+          </cell>
+        </row>
+        <row r="519">
+          <cell r="A519">
+            <v>1877</v>
+          </cell>
+        </row>
+        <row r="520">
+          <cell r="A520">
+            <v>1878</v>
+          </cell>
+        </row>
+        <row r="521">
+          <cell r="A521">
+            <v>1879</v>
+          </cell>
+        </row>
+        <row r="522">
+          <cell r="A522">
+            <v>1880</v>
+          </cell>
+        </row>
+        <row r="523">
+          <cell r="A523">
+            <v>1881</v>
+          </cell>
+        </row>
+        <row r="524">
+          <cell r="A524">
+            <v>1882</v>
+          </cell>
+        </row>
+        <row r="525">
+          <cell r="A525">
+            <v>1883</v>
+          </cell>
+        </row>
+        <row r="526">
+          <cell r="A526">
+            <v>1884</v>
+          </cell>
+        </row>
+        <row r="527">
+          <cell r="A527">
+            <v>1885</v>
+          </cell>
+        </row>
+        <row r="528">
+          <cell r="A528">
+            <v>1886</v>
+          </cell>
+        </row>
+        <row r="529">
+          <cell r="A529">
+            <v>1887</v>
+          </cell>
+        </row>
+        <row r="530">
+          <cell r="A530">
+            <v>1888</v>
+          </cell>
+        </row>
+        <row r="531">
+          <cell r="A531">
+            <v>1889</v>
+          </cell>
+        </row>
+        <row r="532">
+          <cell r="A532">
+            <v>1890</v>
+          </cell>
+        </row>
+        <row r="533">
+          <cell r="A533">
+            <v>1891</v>
+          </cell>
+        </row>
+        <row r="534">
+          <cell r="A534">
+            <v>1892</v>
+          </cell>
+        </row>
+        <row r="535">
+          <cell r="A535">
+            <v>1893</v>
+          </cell>
+        </row>
+        <row r="536">
+          <cell r="A536">
+            <v>1894</v>
+          </cell>
+        </row>
+        <row r="537">
+          <cell r="A537">
+            <v>1895</v>
+          </cell>
+        </row>
+        <row r="538">
+          <cell r="A538">
+            <v>1896</v>
+          </cell>
+        </row>
+        <row r="539">
+          <cell r="A539">
+            <v>1897</v>
+          </cell>
+        </row>
+        <row r="540">
+          <cell r="A540">
+            <v>1898</v>
+          </cell>
+        </row>
+        <row r="541">
+          <cell r="A541">
+            <v>1899</v>
+          </cell>
+        </row>
+        <row r="542">
+          <cell r="A542">
+            <v>1900</v>
+          </cell>
+        </row>
+        <row r="543">
+          <cell r="A543">
+            <v>1901</v>
+          </cell>
+        </row>
+        <row r="544">
+          <cell r="A544">
+            <v>1902</v>
+          </cell>
+        </row>
+        <row r="545">
+          <cell r="A545">
+            <v>1903</v>
+          </cell>
+        </row>
+        <row r="546">
+          <cell r="A546">
+            <v>1904</v>
+          </cell>
+        </row>
+        <row r="547">
+          <cell r="A547">
+            <v>1905</v>
+          </cell>
+        </row>
+        <row r="548">
+          <cell r="A548">
+            <v>1906</v>
+          </cell>
+        </row>
+        <row r="549">
+          <cell r="A549">
+            <v>1907</v>
+          </cell>
+        </row>
+        <row r="550">
+          <cell r="A550">
+            <v>1908</v>
+          </cell>
+        </row>
+        <row r="551">
+          <cell r="A551">
+            <v>1909</v>
+          </cell>
+        </row>
+        <row r="552">
+          <cell r="A552">
+            <v>1910</v>
+          </cell>
+        </row>
+        <row r="553">
+          <cell r="A553">
+            <v>1911</v>
+          </cell>
+        </row>
+        <row r="554">
+          <cell r="A554">
+            <v>1912</v>
+          </cell>
+        </row>
+        <row r="555">
+          <cell r="A555">
+            <v>1913</v>
+          </cell>
+        </row>
+        <row r="556">
+          <cell r="A556">
+            <v>1914</v>
+          </cell>
+        </row>
+        <row r="557">
+          <cell r="A557">
+            <v>1915</v>
+          </cell>
+        </row>
+        <row r="558">
+          <cell r="A558">
+            <v>1916</v>
+          </cell>
+        </row>
+        <row r="559">
+          <cell r="A559">
+            <v>1917</v>
+          </cell>
+        </row>
+        <row r="560">
+          <cell r="A560">
+            <v>1918</v>
+          </cell>
+        </row>
+        <row r="561">
+          <cell r="A561">
+            <v>1919</v>
+          </cell>
+        </row>
+        <row r="562">
+          <cell r="A562">
+            <v>1920</v>
+          </cell>
+        </row>
+        <row r="563">
+          <cell r="A563">
+            <v>1921</v>
+          </cell>
+        </row>
+        <row r="564">
+          <cell r="A564">
+            <v>1922</v>
+          </cell>
+        </row>
+        <row r="565">
+          <cell r="A565">
+            <v>1923</v>
+          </cell>
+        </row>
+        <row r="566">
+          <cell r="A566">
+            <v>1924</v>
+          </cell>
+        </row>
+        <row r="567">
+          <cell r="A567">
+            <v>1925</v>
+          </cell>
+        </row>
+        <row r="568">
+          <cell r="A568">
+            <v>1926</v>
+          </cell>
+        </row>
+        <row r="569">
+          <cell r="A569">
+            <v>1927</v>
+          </cell>
+        </row>
+        <row r="570">
+          <cell r="A570">
+            <v>1928</v>
+          </cell>
+        </row>
+        <row r="571">
+          <cell r="A571">
+            <v>1929</v>
+          </cell>
+        </row>
+        <row r="572">
+          <cell r="A572">
+            <v>1930</v>
+          </cell>
+        </row>
+        <row r="573">
+          <cell r="A573">
+            <v>1931</v>
+          </cell>
+        </row>
+        <row r="574">
+          <cell r="A574">
+            <v>1932</v>
+          </cell>
+        </row>
+        <row r="575">
+          <cell r="A575">
+            <v>1933</v>
+          </cell>
+        </row>
+        <row r="576">
+          <cell r="A576">
+            <v>1934</v>
+          </cell>
+        </row>
+        <row r="577">
+          <cell r="A577">
+            <v>1935</v>
+          </cell>
+        </row>
+        <row r="578">
+          <cell r="A578">
+            <v>1936</v>
+          </cell>
+        </row>
+        <row r="579">
+          <cell r="A579">
+            <v>1937</v>
+          </cell>
+        </row>
+        <row r="580">
+          <cell r="A580">
+            <v>1938</v>
+          </cell>
+        </row>
+        <row r="581">
+          <cell r="A581">
+            <v>1939</v>
+          </cell>
+        </row>
+        <row r="582">
+          <cell r="A582">
+            <v>1940</v>
+          </cell>
+        </row>
+        <row r="583">
+          <cell r="A583">
+            <v>1941</v>
+          </cell>
+        </row>
+        <row r="584">
+          <cell r="A584">
+            <v>1942</v>
+          </cell>
+        </row>
+        <row r="585">
+          <cell r="A585">
+            <v>1943</v>
+          </cell>
+        </row>
+        <row r="586">
+          <cell r="A586">
+            <v>1944</v>
+          </cell>
+        </row>
+        <row r="587">
+          <cell r="A587">
+            <v>1945</v>
+          </cell>
+        </row>
+        <row r="588">
+          <cell r="A588">
+            <v>1946</v>
+          </cell>
+        </row>
+        <row r="589">
+          <cell r="A589">
+            <v>1947</v>
+          </cell>
+        </row>
+        <row r="590">
+          <cell r="A590">
+            <v>1948</v>
+          </cell>
+        </row>
+        <row r="591">
+          <cell r="A591">
+            <v>1949</v>
+          </cell>
+        </row>
+        <row r="592">
+          <cell r="A592">
+            <v>1950</v>
+          </cell>
+        </row>
+        <row r="593">
+          <cell r="A593">
+            <v>1951</v>
+          </cell>
+        </row>
+        <row r="594">
+          <cell r="A594">
+            <v>1952</v>
+          </cell>
+        </row>
+        <row r="595">
+          <cell r="A595">
+            <v>1953</v>
+          </cell>
+        </row>
+        <row r="596">
+          <cell r="A596">
+            <v>1954</v>
+          </cell>
+        </row>
+        <row r="597">
+          <cell r="A597">
+            <v>1955</v>
+          </cell>
+        </row>
+        <row r="598">
+          <cell r="A598">
+            <v>1956</v>
+          </cell>
+        </row>
+        <row r="599">
+          <cell r="A599">
+            <v>1957</v>
+          </cell>
+        </row>
+        <row r="600">
+          <cell r="A600">
+            <v>1958</v>
+          </cell>
+        </row>
+        <row r="601">
+          <cell r="A601">
+            <v>1959</v>
+          </cell>
+        </row>
+        <row r="602">
+          <cell r="A602">
+            <v>1960</v>
+          </cell>
+        </row>
+        <row r="603">
+          <cell r="A603">
+            <v>1961</v>
+          </cell>
+        </row>
+        <row r="604">
+          <cell r="A604">
+            <v>1962</v>
+          </cell>
+        </row>
+        <row r="605">
+          <cell r="A605">
+            <v>1963</v>
+          </cell>
+        </row>
+        <row r="606">
+          <cell r="A606">
+            <v>1964</v>
+          </cell>
+        </row>
+        <row r="607">
+          <cell r="A607">
+            <v>1965</v>
+          </cell>
+        </row>
+        <row r="608">
+          <cell r="A608">
+            <v>1966</v>
+          </cell>
+        </row>
+        <row r="609">
+          <cell r="A609">
+            <v>1967</v>
+          </cell>
+        </row>
+        <row r="610">
+          <cell r="A610">
+            <v>1968</v>
+          </cell>
+        </row>
+        <row r="611">
+          <cell r="A611">
+            <v>1969</v>
+          </cell>
+        </row>
+        <row r="612">
+          <cell r="A612">
+            <v>1970</v>
+          </cell>
+        </row>
+        <row r="613">
+          <cell r="A613">
+            <v>1971</v>
+          </cell>
+        </row>
+        <row r="614">
+          <cell r="A614">
+            <v>1972</v>
+          </cell>
+        </row>
+        <row r="615">
+          <cell r="A615">
+            <v>1973</v>
+          </cell>
+        </row>
+        <row r="616">
+          <cell r="A616">
+            <v>1974</v>
+          </cell>
+        </row>
+        <row r="617">
+          <cell r="A617">
+            <v>1975</v>
+          </cell>
+        </row>
+        <row r="618">
+          <cell r="A618">
+            <v>1976</v>
+          </cell>
+        </row>
+        <row r="619">
+          <cell r="A619">
+            <v>1977</v>
+          </cell>
+        </row>
+        <row r="620">
+          <cell r="A620">
+            <v>1978</v>
+          </cell>
+        </row>
+        <row r="621">
+          <cell r="A621">
+            <v>1979</v>
+          </cell>
+        </row>
+        <row r="622">
+          <cell r="A622">
+            <v>1980</v>
+          </cell>
+        </row>
+        <row r="623">
+          <cell r="A623">
+            <v>1981</v>
+          </cell>
+        </row>
+        <row r="624">
+          <cell r="A624">
+            <v>1982</v>
+          </cell>
+        </row>
+        <row r="625">
+          <cell r="A625">
+            <v>1983</v>
+          </cell>
+        </row>
+        <row r="626">
+          <cell r="A626">
+            <v>1984</v>
+          </cell>
+        </row>
+        <row r="627">
+          <cell r="A627">
+            <v>1985</v>
+          </cell>
+        </row>
+        <row r="628">
+          <cell r="A628">
+            <v>1986</v>
+          </cell>
+        </row>
+        <row r="629">
+          <cell r="A629">
+            <v>1987</v>
+          </cell>
+        </row>
+        <row r="630">
+          <cell r="A630">
+            <v>1988</v>
+          </cell>
+        </row>
+        <row r="631">
+          <cell r="A631">
+            <v>1989</v>
+          </cell>
+        </row>
+        <row r="632">
+          <cell r="A632">
+            <v>1990</v>
+          </cell>
+        </row>
+        <row r="633">
+          <cell r="A633">
+            <v>1991</v>
+          </cell>
+        </row>
+        <row r="634">
+          <cell r="A634">
+            <v>1992</v>
+          </cell>
+        </row>
+        <row r="635">
+          <cell r="A635">
+            <v>1993</v>
+          </cell>
+        </row>
+        <row r="636">
+          <cell r="A636">
+            <v>1994</v>
+          </cell>
+        </row>
+        <row r="637">
+          <cell r="A637">
+            <v>1995</v>
+          </cell>
+        </row>
+        <row r="638">
+          <cell r="A638">
+            <v>1996</v>
+          </cell>
+        </row>
+        <row r="639">
+          <cell r="A639">
+            <v>1997</v>
+          </cell>
+        </row>
+        <row r="640">
+          <cell r="A640">
+            <v>1998</v>
+          </cell>
+        </row>
+        <row r="641">
+          <cell r="A641">
+            <v>1999</v>
+          </cell>
+        </row>
+        <row r="642">
+          <cell r="A642">
+            <v>2000</v>
+          </cell>
+        </row>
+        <row r="643">
+          <cell r="A643">
+            <v>2001</v>
+          </cell>
+        </row>
+        <row r="644">
+          <cell r="A644">
+            <v>2002</v>
+          </cell>
+        </row>
+        <row r="645">
+          <cell r="A645">
+            <v>2003</v>
+          </cell>
+        </row>
+        <row r="646">
+          <cell r="A646">
+            <v>2004</v>
+          </cell>
+        </row>
+        <row r="647">
+          <cell r="A647">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="648">
+          <cell r="A648">
+            <v>2006</v>
+          </cell>
+        </row>
+        <row r="649">
+          <cell r="A649">
+            <v>2007</v>
+          </cell>
+        </row>
+        <row r="650">
+          <cell r="A650">
+            <v>2008</v>
+          </cell>
+        </row>
+        <row r="651">
+          <cell r="A651">
+            <v>2009</v>
+          </cell>
+        </row>
+        <row r="652">
+          <cell r="A652">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="653">
+          <cell r="A653">
+            <v>2011</v>
+          </cell>
+        </row>
+        <row r="654">
+          <cell r="A654">
+            <v>2012</v>
+          </cell>
+        </row>
+        <row r="655">
+          <cell r="A655">
+            <v>2013</v>
+          </cell>
+        </row>
+        <row r="656">
+          <cell r="A656">
+            <v>2014</v>
+          </cell>
+        </row>
+        <row r="657">
+          <cell r="A657">
+            <v>2015</v>
+          </cell>
+        </row>
+        <row r="658">
+          <cell r="A658">
+            <v>2016</v>
+          </cell>
+        </row>
+        <row r="659">
+          <cell r="A659">
+            <v>2017</v>
+          </cell>
+        </row>
+        <row r="660">
+          <cell r="A660">
+            <v>2018</v>
+          </cell>
+        </row>
+        <row r="661">
+          <cell r="A661">
+            <v>2019</v>
+          </cell>
+        </row>
+        <row r="662">
+          <cell r="A662">
+            <v>2020</v>
+          </cell>
+        </row>
+        <row r="663">
+          <cell r="A663">
+            <v>2021</v>
+          </cell>
+        </row>
+        <row r="664">
+          <cell r="A664">
+            <v>2022</v>
+          </cell>
+        </row>
+        <row r="665">
+          <cell r="A665">
+            <v>2023</v>
+          </cell>
+        </row>
+        <row r="666">
+          <cell r="A666">
+            <v>2024</v>
+          </cell>
+        </row>
+        <row r="667">
+          <cell r="A667">
+            <v>2025</v>
+          </cell>
+        </row>
+        <row r="668">
+          <cell r="A668">
+            <v>2026</v>
+          </cell>
+        </row>
+        <row r="669">
+          <cell r="A669">
+            <v>2027</v>
+          </cell>
+        </row>
+        <row r="670">
+          <cell r="A670">
+            <v>2028</v>
+          </cell>
+        </row>
+        <row r="671">
+          <cell r="A671">
+            <v>2029</v>
+          </cell>
+        </row>
+        <row r="672">
+          <cell r="A672">
+            <v>2030</v>
+          </cell>
+        </row>
+        <row r="673">
+          <cell r="A673">
+            <v>2031</v>
+          </cell>
+        </row>
+        <row r="674">
+          <cell r="A674">
+            <v>2032</v>
+          </cell>
+        </row>
+        <row r="675">
+          <cell r="A675">
+            <v>2033</v>
+          </cell>
+        </row>
+        <row r="676">
+          <cell r="A676">
+            <v>2034</v>
+          </cell>
+        </row>
+        <row r="677">
+          <cell r="A677">
+            <v>2035</v>
+          </cell>
+        </row>
+        <row r="678">
+          <cell r="A678">
+            <v>2036</v>
+          </cell>
+        </row>
+        <row r="679">
+          <cell r="A679">
+            <v>2037</v>
+          </cell>
+        </row>
+        <row r="680">
+          <cell r="A680">
+            <v>2038</v>
+          </cell>
+        </row>
+        <row r="681">
+          <cell r="A681">
+            <v>2039</v>
+          </cell>
+        </row>
+        <row r="682">
+          <cell r="A682">
+            <v>2040</v>
+          </cell>
+        </row>
+        <row r="683">
+          <cell r="A683">
+            <v>2041</v>
+          </cell>
+        </row>
+        <row r="684">
+          <cell r="A684">
+            <v>2042</v>
+          </cell>
+        </row>
+        <row r="685">
+          <cell r="A685">
+            <v>2043</v>
+          </cell>
+        </row>
+        <row r="686">
+          <cell r="A686">
+            <v>2044</v>
+          </cell>
+        </row>
+        <row r="687">
+          <cell r="A687">
+            <v>2045</v>
+          </cell>
+        </row>
+        <row r="688">
+          <cell r="A688">
+            <v>2046</v>
+          </cell>
+        </row>
+        <row r="689">
+          <cell r="A689">
+            <v>2047</v>
+          </cell>
+        </row>
+        <row r="690">
+          <cell r="A690">
+            <v>2048</v>
+          </cell>
+        </row>
+        <row r="691">
+          <cell r="A691">
+            <v>2049</v>
+          </cell>
+        </row>
+        <row r="692">
+          <cell r="A692">
+            <v>2050</v>
+          </cell>
+        </row>
+        <row r="693">
+          <cell r="A693">
+            <v>2051</v>
+          </cell>
+        </row>
+        <row r="694">
+          <cell r="A694">
+            <v>2052</v>
+          </cell>
+        </row>
+        <row r="695">
+          <cell r="A695">
+            <v>2053</v>
+          </cell>
+        </row>
+        <row r="696">
+          <cell r="A696">
+            <v>2054</v>
+          </cell>
+        </row>
+        <row r="697">
+          <cell r="A697">
+            <v>2055</v>
+          </cell>
+        </row>
+        <row r="698">
+          <cell r="A698">
+            <v>2056</v>
+          </cell>
+        </row>
+        <row r="699">
+          <cell r="A699">
+            <v>2057</v>
+          </cell>
+        </row>
+        <row r="700">
+          <cell r="A700">
+            <v>2058</v>
+          </cell>
+        </row>
+        <row r="701">
+          <cell r="A701">
+            <v>2059</v>
+          </cell>
+        </row>
+        <row r="702">
+          <cell r="A702">
+            <v>2060</v>
+          </cell>
+        </row>
+        <row r="703">
+          <cell r="A703">
+            <v>2061</v>
+          </cell>
+        </row>
+        <row r="704">
+          <cell r="A704">
+            <v>2062</v>
+          </cell>
+        </row>
+        <row r="705">
+          <cell r="A705">
+            <v>2063</v>
+          </cell>
+        </row>
+        <row r="706">
+          <cell r="A706">
+            <v>2064</v>
+          </cell>
+        </row>
+        <row r="707">
+          <cell r="A707">
+            <v>2065</v>
+          </cell>
+        </row>
+        <row r="708">
+          <cell r="A708">
+            <v>2066</v>
+          </cell>
+        </row>
+        <row r="709">
+          <cell r="A709">
+            <v>2067</v>
+          </cell>
+        </row>
+        <row r="710">
+          <cell r="A710">
+            <v>2068</v>
+          </cell>
+        </row>
+        <row r="711">
+          <cell r="A711">
+            <v>2069</v>
+          </cell>
+        </row>
+        <row r="712">
+          <cell r="A712">
+            <v>2070</v>
+          </cell>
+        </row>
+        <row r="713">
+          <cell r="A713">
+            <v>2071</v>
+          </cell>
+        </row>
+        <row r="714">
+          <cell r="A714">
+            <v>2072</v>
+          </cell>
+        </row>
+        <row r="715">
+          <cell r="A715">
+            <v>2073</v>
+          </cell>
+        </row>
+        <row r="716">
+          <cell r="A716">
+            <v>2074</v>
+          </cell>
+        </row>
+        <row r="717">
+          <cell r="A717">
+            <v>2075</v>
+          </cell>
+        </row>
+        <row r="718">
+          <cell r="A718">
+            <v>2076</v>
+          </cell>
+        </row>
+        <row r="719">
+          <cell r="A719">
+            <v>2077</v>
+          </cell>
+        </row>
+        <row r="720">
+          <cell r="A720">
+            <v>2078</v>
+          </cell>
+        </row>
+        <row r="721">
+          <cell r="A721">
+            <v>2079</v>
+          </cell>
+        </row>
+        <row r="722">
+          <cell r="A722">
+            <v>2080</v>
+          </cell>
+        </row>
+        <row r="723">
+          <cell r="A723">
+            <v>2081</v>
+          </cell>
+        </row>
+        <row r="724">
+          <cell r="A724">
+            <v>2082</v>
+          </cell>
+        </row>
+        <row r="725">
+          <cell r="A725">
+            <v>2083</v>
+          </cell>
+        </row>
+        <row r="726">
+          <cell r="A726">
+            <v>2084</v>
+          </cell>
+        </row>
+        <row r="727">
+          <cell r="A727">
+            <v>2085</v>
+          </cell>
+        </row>
+        <row r="728">
+          <cell r="A728">
+            <v>2086</v>
+          </cell>
+        </row>
+        <row r="729">
+          <cell r="A729">
+            <v>2087</v>
+          </cell>
+        </row>
+        <row r="730">
+          <cell r="A730">
+            <v>2088</v>
+          </cell>
+        </row>
+        <row r="731">
+          <cell r="A731">
+            <v>2089</v>
+          </cell>
+        </row>
+        <row r="732">
+          <cell r="A732">
+            <v>2090</v>
+          </cell>
+        </row>
+        <row r="733">
+          <cell r="A733">
+            <v>2091</v>
+          </cell>
+        </row>
+        <row r="734">
+          <cell r="A734">
+            <v>2092</v>
+          </cell>
+        </row>
+        <row r="735">
+          <cell r="A735">
+            <v>2093</v>
+          </cell>
+        </row>
+        <row r="736">
+          <cell r="A736">
+            <v>2094</v>
+          </cell>
+        </row>
+        <row r="737">
+          <cell r="A737">
+            <v>2095</v>
+          </cell>
+        </row>
+        <row r="738">
+          <cell r="A738">
+            <v>2096</v>
+          </cell>
+        </row>
+        <row r="739">
+          <cell r="A739">
+            <v>2097</v>
+          </cell>
+        </row>
+        <row r="740">
+          <cell r="A740">
+            <v>2098</v>
+          </cell>
+        </row>
+        <row r="741">
+          <cell r="A741">
+            <v>2099</v>
+          </cell>
+        </row>
+        <row r="742">
+          <cell r="A742">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="743">
+          <cell r="A743">
+            <v>2101</v>
+          </cell>
+        </row>
+        <row r="744">
+          <cell r="A744">
+            <v>2102</v>
+          </cell>
+        </row>
+        <row r="745">
+          <cell r="A745">
+            <v>2103</v>
+          </cell>
+        </row>
+        <row r="746">
+          <cell r="A746">
+            <v>2104</v>
+          </cell>
+        </row>
+        <row r="747">
+          <cell r="A747">
+            <v>2105</v>
+          </cell>
+        </row>
+        <row r="748">
+          <cell r="A748">
+            <v>2106</v>
+          </cell>
+        </row>
+        <row r="749">
+          <cell r="A749">
+            <v>2107</v>
+          </cell>
+        </row>
+        <row r="750">
+          <cell r="A750">
+            <v>2108</v>
+          </cell>
+        </row>
+        <row r="751">
+          <cell r="A751">
+            <v>2109</v>
+          </cell>
+        </row>
+        <row r="752">
+          <cell r="A752">
+            <v>2110</v>
+          </cell>
+        </row>
+        <row r="753">
+          <cell r="A753">
+            <v>2111</v>
+          </cell>
+        </row>
+        <row r="754">
+          <cell r="A754">
+            <v>2112</v>
+          </cell>
+        </row>
+        <row r="755">
+          <cell r="A755">
+            <v>2113</v>
+          </cell>
+        </row>
+        <row r="756">
+          <cell r="A756">
+            <v>2114</v>
+          </cell>
+        </row>
+        <row r="757">
+          <cell r="A757">
+            <v>2115</v>
+          </cell>
+        </row>
+        <row r="758">
+          <cell r="A758">
+            <v>2116</v>
+          </cell>
+        </row>
+        <row r="759">
+          <cell r="A759">
+            <v>2117</v>
+          </cell>
+        </row>
+        <row r="760">
+          <cell r="A760">
+            <v>2118</v>
+          </cell>
+        </row>
+        <row r="761">
+          <cell r="A761">
+            <v>2119</v>
+          </cell>
+        </row>
+        <row r="762">
+          <cell r="A762">
+            <v>2120</v>
+          </cell>
+        </row>
+        <row r="763">
+          <cell r="A763">
+            <v>2121</v>
+          </cell>
+        </row>
+        <row r="764">
+          <cell r="A764">
+            <v>2122</v>
+          </cell>
+        </row>
+        <row r="765">
+          <cell r="A765">
+            <v>2123</v>
+          </cell>
+        </row>
+        <row r="766">
+          <cell r="A766">
+            <v>2124</v>
+          </cell>
+        </row>
+        <row r="767">
+          <cell r="A767">
+            <v>2125</v>
+          </cell>
+        </row>
+        <row r="768">
+          <cell r="A768">
+            <v>2126</v>
+          </cell>
+        </row>
+        <row r="769">
+          <cell r="A769">
+            <v>2127</v>
+          </cell>
+        </row>
+        <row r="770">
+          <cell r="A770">
+            <v>2128</v>
+          </cell>
+        </row>
+        <row r="771">
+          <cell r="A771">
+            <v>2129</v>
+          </cell>
+        </row>
+        <row r="772">
+          <cell r="A772">
+            <v>2130</v>
+          </cell>
+        </row>
+        <row r="773">
+          <cell r="A773">
+            <v>2131</v>
+          </cell>
+        </row>
+        <row r="774">
+          <cell r="A774">
+            <v>2132</v>
+          </cell>
+        </row>
+        <row r="775">
+          <cell r="A775">
+            <v>2133</v>
+          </cell>
+        </row>
+        <row r="776">
+          <cell r="A776">
+            <v>2134</v>
+          </cell>
+        </row>
+        <row r="777">
+          <cell r="A777">
+            <v>2135</v>
+          </cell>
+        </row>
+        <row r="778">
+          <cell r="A778">
+            <v>2136</v>
+          </cell>
+        </row>
+        <row r="779">
+          <cell r="A779">
+            <v>2137</v>
+          </cell>
+        </row>
+        <row r="780">
+          <cell r="A780">
+            <v>2138</v>
+          </cell>
+        </row>
+        <row r="781">
+          <cell r="A781">
+            <v>2139</v>
+          </cell>
+        </row>
+        <row r="782">
+          <cell r="A782">
+            <v>2140</v>
+          </cell>
+        </row>
+        <row r="783">
+          <cell r="A783">
+            <v>2141</v>
+          </cell>
+        </row>
+        <row r="784">
+          <cell r="A784">
+            <v>2142</v>
+          </cell>
+        </row>
+        <row r="785">
+          <cell r="A785">
+            <v>2143</v>
+          </cell>
+        </row>
+        <row r="786">
+          <cell r="A786">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="787">
+          <cell r="A787">
+            <v>2145</v>
+          </cell>
+        </row>
+        <row r="788">
+          <cell r="A788">
+            <v>2146</v>
+          </cell>
+        </row>
+        <row r="789">
+          <cell r="A789">
+            <v>2147</v>
+          </cell>
+        </row>
+        <row r="790">
+          <cell r="A790">
+            <v>2148</v>
+          </cell>
+        </row>
+        <row r="791">
+          <cell r="A791">
+            <v>2149</v>
+          </cell>
+        </row>
+        <row r="792">
+          <cell r="A792">
+            <v>2150</v>
+          </cell>
+        </row>
+        <row r="793">
+          <cell r="A793">
+            <v>2151</v>
+          </cell>
+        </row>
+        <row r="794">
+          <cell r="A794">
+            <v>2152</v>
+          </cell>
+        </row>
+        <row r="795">
+          <cell r="A795">
+            <v>2153</v>
+          </cell>
+        </row>
+        <row r="796">
+          <cell r="A796">
+            <v>2154</v>
+          </cell>
+        </row>
+        <row r="797">
+          <cell r="A797">
+            <v>2155</v>
+          </cell>
+        </row>
+        <row r="798">
+          <cell r="A798">
+            <v>2156</v>
+          </cell>
+        </row>
+        <row r="799">
+          <cell r="A799">
+            <v>2157</v>
+          </cell>
+        </row>
+        <row r="800">
+          <cell r="A800">
+            <v>2158</v>
+          </cell>
+        </row>
+        <row r="801">
+          <cell r="A801">
+            <v>2159</v>
+          </cell>
+        </row>
+        <row r="802">
+          <cell r="A802">
+            <v>2160</v>
+          </cell>
+        </row>
+        <row r="803">
+          <cell r="A803">
+            <v>2161</v>
+          </cell>
+        </row>
+        <row r="804">
+          <cell r="A804">
+            <v>2162</v>
+          </cell>
+        </row>
+        <row r="805">
+          <cell r="A805">
+            <v>2163</v>
+          </cell>
+        </row>
+        <row r="806">
+          <cell r="A806">
+            <v>2164</v>
+          </cell>
+        </row>
+        <row r="807">
+          <cell r="A807">
+            <v>2165</v>
+          </cell>
+        </row>
+        <row r="808">
+          <cell r="A808">
+            <v>2166</v>
+          </cell>
+        </row>
+        <row r="809">
+          <cell r="A809">
+            <v>2167</v>
+          </cell>
+        </row>
+        <row r="810">
+          <cell r="A810">
+            <v>2168</v>
+          </cell>
+        </row>
+        <row r="811">
+          <cell r="A811">
+            <v>2169</v>
+          </cell>
+        </row>
+        <row r="812">
+          <cell r="A812">
+            <v>2170</v>
+          </cell>
+        </row>
+        <row r="813">
+          <cell r="A813">
+            <v>2171</v>
+          </cell>
+        </row>
+        <row r="814">
+          <cell r="A814">
+            <v>2172</v>
+          </cell>
+        </row>
+        <row r="815">
+          <cell r="A815">
+            <v>2173</v>
+          </cell>
+        </row>
+        <row r="816">
+          <cell r="A816">
+            <v>2174</v>
+          </cell>
+        </row>
+        <row r="817">
+          <cell r="A817">
+            <v>2175</v>
+          </cell>
+        </row>
+        <row r="818">
+          <cell r="A818">
+            <v>2176</v>
+          </cell>
+        </row>
+        <row r="819">
+          <cell r="A819">
+            <v>2177</v>
+          </cell>
+        </row>
+        <row r="820">
+          <cell r="A820">
+            <v>2178</v>
+          </cell>
+        </row>
+        <row r="821">
+          <cell r="A821">
+            <v>2179</v>
+          </cell>
+        </row>
+        <row r="822">
+          <cell r="A822">
+            <v>2180</v>
+          </cell>
+        </row>
+        <row r="823">
+          <cell r="A823">
+            <v>2181</v>
+          </cell>
+        </row>
+        <row r="824">
+          <cell r="A824">
+            <v>2182</v>
+          </cell>
+        </row>
+        <row r="825">
+          <cell r="A825">
+            <v>2183</v>
+          </cell>
+        </row>
+        <row r="826">
+          <cell r="A826">
+            <v>2184</v>
+          </cell>
+        </row>
+        <row r="827">
+          <cell r="A827">
+            <v>2185</v>
+          </cell>
+        </row>
+        <row r="828">
+          <cell r="A828">
+            <v>2186</v>
+          </cell>
+        </row>
+        <row r="829">
+          <cell r="A829">
+            <v>2187</v>
+          </cell>
+        </row>
+        <row r="830">
+          <cell r="A830">
+            <v>2188</v>
+          </cell>
+        </row>
+        <row r="831">
+          <cell r="A831">
+            <v>2189</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2717,13 +8774,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2890,17 +8947,17 @@
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="9" customFormat="1" spans="1:5">
+      <c r="A1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="3"/>
@@ -2929,7 +8986,7 @@
       <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2943,7 +9000,7 @@
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2957,7 +9014,7 @@
       <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3057,56 +9114,56 @@
     <col min="17" max="16384" width="9.06837606837607" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" spans="1:17">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="9" customFormat="1" spans="1:17">
+      <c r="A1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="9" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3121,7 +9178,7 @@
       <c r="C2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -3131,7 +9188,7 @@
         <v>1000</v>
       </c>
       <c r="G2" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>72</v>
@@ -3164,7 +9221,7 @@
         <v>1000</v>
       </c>
       <c r="G3" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>73</v>
@@ -3187,7 +9244,7 @@
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -3197,7 +9254,7 @@
         <v>1000</v>
       </c>
       <c r="G4" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>74</v>
@@ -3220,7 +9277,7 @@
       <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -3230,7 +9287,7 @@
         <v>1000</v>
       </c>
       <c r="G5" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>75</v>
@@ -3253,17 +9310,20 @@
       <c r="C6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>70</v>
       </c>
+      <c r="E6" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="F6" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G6" s="3">
         <v>1000</v>
       </c>
-      <c r="G6" s="3">
-        <v>500</v>
-      </c>
       <c r="H6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" s="3">
         <v>502</v>
@@ -3283,17 +9343,20 @@
       <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>70</v>
       </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="F7" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="3">
         <v>1000</v>
       </c>
-      <c r="G7" s="3">
-        <v>500</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I7" s="3">
         <v>502</v>
@@ -3313,17 +9376,20 @@
       <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>70</v>
       </c>
+      <c r="E8" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="F8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
-        <v>500</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="3">
         <v>502</v>
@@ -3343,17 +9409,20 @@
       <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>70</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="F9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3">
         <v>1000</v>
       </c>
-      <c r="G9" s="3">
-        <v>500</v>
-      </c>
       <c r="H9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" s="3">
         <v>502</v>
@@ -3369,17 +9438,17 @@
       <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="11" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I10" s="3">
         <v>502</v>
@@ -3395,12 +9464,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.7606837606838" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.6752136752137" style="2" customWidth="1"/>
-    <col min="3" max="3" width="237.846153846154" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.0940170940171" style="2" customWidth="1"/>
+    <col min="3" max="3" width="212.162393162393" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.3931623931624" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.2905982905983" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.4358974358974" style="2" customWidth="1"/>
@@ -3409,16 +9478,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3429,13 +9498,13 @@
         <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)</f>
         <v>58,59,60,61,62,63,64,65,66,67,68,69,70,71</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
     </row>
@@ -3444,13 +9513,13 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
         <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>1</v>
       </c>
     </row>
@@ -3459,184 +9528,1402 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
         <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="2">
+      <c r="C5" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="D8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="9" spans="1:7">
+      <c r="A9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="D9" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="D10" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="2">
+    <row r="11" spans="1:7">
+      <c r="A11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="2">
+    <row r="12" spans="1:7">
+      <c r="A12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
+    <row r="13" spans="1:7">
+      <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="B13" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
+        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
+        <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
+        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
+        <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
+        <v>100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
+        <v>139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
+        <v>178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
+        <v>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,249,250,251,252,253,254,255</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
+        <v>256,257,258,259,260,261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,281,282,283,284,285,286,287,288,289,290,291,292,293,294</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
+        <v>295,296,297,298,299,300,301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
+        <v>100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
+        <v>139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
+        <v>178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
+        <v>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,249,250,251,252,253,254,255</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
+        <v>256,257,258,259,260,261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,281,282,283,284,285,286,287,288,289,290,291,292,293,294</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
+        <v>295,296,297,298,299,300,301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="8">
+        <v>500506</v>
+      </c>
+      <c r="D50" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="8">
+        <v>501507</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" s="8">
+        <v>502508</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C53" s="8">
+        <v>503509</v>
+      </c>
+      <c r="D53" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="8">
+        <v>504510</v>
+      </c>
+      <c r="D54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" s="8">
+        <v>505511</v>
+      </c>
+      <c r="D55" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" s="8">
+        <v>500506</v>
+      </c>
+      <c r="D56" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C57" s="8">
+        <v>501507</v>
+      </c>
+      <c r="D57" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C58" s="8">
+        <v>502508</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="8">
+        <v>503509</v>
+      </c>
+      <c r="D59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C60" s="8">
+        <v>504510</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" s="8">
+        <v>505511</v>
+      </c>
+      <c r="D61" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C62" s="8">
+        <v>500506</v>
+      </c>
+      <c r="D62" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C63" s="8">
+        <v>501507</v>
+      </c>
+      <c r="D63" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C64" s="8">
+        <v>502508</v>
+      </c>
+      <c r="D64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65" s="8">
+        <v>503509</v>
+      </c>
+      <c r="D65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C66" s="8">
+        <v>504510</v>
+      </c>
+      <c r="D66" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C67" s="8">
+        <v>505511</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C68" s="8">
+        <v>500506</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C69" s="8">
+        <v>501507</v>
+      </c>
+      <c r="D69" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" s="8">
+        <v>502508</v>
+      </c>
+      <c r="D70" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71" s="8">
+        <v>503509</v>
+      </c>
+      <c r="D71" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" s="8">
+        <v>504510</v>
+      </c>
+      <c r="D72" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" s="8">
+        <v>505511</v>
+      </c>
+      <c r="D73" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C74" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
+        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+      </c>
+      <c r="D74" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
+        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+      </c>
+      <c r="D75" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C76" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
+        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C77" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
+        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+      </c>
+      <c r="D77" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
+        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+      </c>
+      <c r="D78" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C79" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
+        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+      </c>
+      <c r="D79" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C80" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
+        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+      </c>
+      <c r="D80" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
+        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+      </c>
+      <c r="D81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
+        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+      </c>
+      <c r="D82" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C83" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
+        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+      </c>
+      <c r="D83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
+        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+      </c>
+      <c r="D84" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
+        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+      </c>
+      <c r="D85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
+        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+      </c>
+      <c r="D86" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
+        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+      </c>
+      <c r="D87" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C88" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
+        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+      </c>
+      <c r="D88" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C89" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
+        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+      </c>
+      <c r="D89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C90" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
+        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+      </c>
+      <c r="D90" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
+        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+      </c>
+      <c r="D91" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
+        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+      </c>
+      <c r="D92" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C93" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
+        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+      </c>
+      <c r="D93" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C94" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
+        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+      </c>
+      <c r="D94" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C95" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
+        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+      </c>
+      <c r="D95" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C96" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
+        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+      </c>
+      <c r="D96" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
+        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+      </c>
+      <c r="D97" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="2" t="str">
+      <c r="B98" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C98" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$120)</f>
         <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D98" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3" t="s">
+    <row r="99" spans="1:4">
+      <c r="A99" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$120)</f>
-        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="B99" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$200)</f>
+        <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113</v>
+      </c>
+      <c r="D99" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3" t="s">
+    <row r="100" spans="1:4">
+      <c r="A100" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="2" t="str">
+      <c r="B100" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥控!$A$2:$A$120)</f>
         <v>3000,3001,3002,3003</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D100" s="4">
         <v>1</v>
       </c>
     </row>

--- a/config/鸿合_配置_v2.0.xlsx
+++ b/config/鸿合_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
+    <workbookView windowWidth="18569" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
     <t>mqtt_yt</t>
   </si>
   <si>
-    <t>/asw/+/+/yt</t>
+    <t>/asw/+/+/setyt</t>
   </si>
   <si>
     <t>MQTT遥调</t>
@@ -124,7 +124,7 @@
     <t>mqtt_yk</t>
   </si>
   <si>
-    <t>/asw/+/+/yk</t>
+    <t>/asw/+/+/setyk</t>
   </si>
   <si>
     <t>MQTT遥控</t>
@@ -1296,7 +1296,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1307,12 +1307,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5061,3452 +5055,3452 @@
         </row>
         <row r="142">
           <cell r="A142">
-            <v>1500</v>
+            <v>1200</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>1501</v>
+            <v>1201</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>1502</v>
+            <v>1202</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>1503</v>
+            <v>1203</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>1504</v>
+            <v>1204</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>1505</v>
+            <v>1205</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>1506</v>
+            <v>1206</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>1507</v>
+            <v>1207</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>1508</v>
+            <v>1208</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>1509</v>
+            <v>1209</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>1510</v>
+            <v>1210</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>1511</v>
+            <v>1211</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>1512</v>
+            <v>1212</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>1513</v>
+            <v>1213</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>1514</v>
+            <v>1214</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>1515</v>
+            <v>1215</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>1516</v>
+            <v>1216</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>1517</v>
+            <v>1217</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>1518</v>
+            <v>1218</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>1519</v>
+            <v>1219</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>1520</v>
+            <v>1220</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>1521</v>
+            <v>1221</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>1522</v>
+            <v>1222</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>1523</v>
+            <v>1223</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>1524</v>
+            <v>1224</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>1525</v>
+            <v>1225</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>1526</v>
+            <v>1226</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>1527</v>
+            <v>1227</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>1528</v>
+            <v>1228</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>1529</v>
+            <v>1229</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>1530</v>
+            <v>1230</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>1531</v>
+            <v>1231</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>1532</v>
+            <v>1232</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>1533</v>
+            <v>1233</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>1534</v>
+            <v>1234</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>1535</v>
+            <v>1235</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>1536</v>
+            <v>1236</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>1537</v>
+            <v>1237</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>1538</v>
+            <v>1238</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>1539</v>
+            <v>1239</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>1540</v>
+            <v>1240</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>1541</v>
+            <v>1241</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>1542</v>
+            <v>1242</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>1543</v>
+            <v>1243</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>1544</v>
+            <v>1244</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>1545</v>
+            <v>1245</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>1546</v>
+            <v>1246</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>1547</v>
+            <v>1247</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>1548</v>
+            <v>1248</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>1549</v>
+            <v>1249</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>1550</v>
+            <v>1250</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>1551</v>
+            <v>1251</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>1552</v>
+            <v>1252</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>1553</v>
+            <v>1253</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>1554</v>
+            <v>1254</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>1555</v>
+            <v>1255</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>1556</v>
+            <v>1256</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>1557</v>
+            <v>1257</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>1558</v>
+            <v>1258</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>1559</v>
+            <v>1259</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>1560</v>
+            <v>1260</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>1561</v>
+            <v>1261</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>1562</v>
+            <v>1262</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>1563</v>
+            <v>1263</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>1564</v>
+            <v>1264</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>1565</v>
+            <v>1265</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>1566</v>
+            <v>1266</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>1567</v>
+            <v>1267</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>1568</v>
+            <v>1268</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>1569</v>
+            <v>1269</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>1570</v>
+            <v>1270</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>1571</v>
+            <v>1271</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
-            <v>1572</v>
+            <v>1272</v>
           </cell>
         </row>
         <row r="215">
           <cell r="A215">
-            <v>1573</v>
+            <v>1273</v>
           </cell>
         </row>
         <row r="216">
           <cell r="A216">
-            <v>1574</v>
+            <v>1274</v>
           </cell>
         </row>
         <row r="217">
           <cell r="A217">
-            <v>1575</v>
+            <v>1275</v>
           </cell>
         </row>
         <row r="218">
           <cell r="A218">
-            <v>1576</v>
+            <v>1276</v>
           </cell>
         </row>
         <row r="219">
           <cell r="A219">
-            <v>1577</v>
+            <v>1277</v>
           </cell>
         </row>
         <row r="220">
           <cell r="A220">
-            <v>1578</v>
+            <v>1278</v>
           </cell>
         </row>
         <row r="221">
           <cell r="A221">
-            <v>1579</v>
+            <v>1279</v>
           </cell>
         </row>
         <row r="222">
           <cell r="A222">
-            <v>1580</v>
+            <v>1280</v>
           </cell>
         </row>
         <row r="223">
           <cell r="A223">
-            <v>1581</v>
+            <v>1281</v>
           </cell>
         </row>
         <row r="224">
           <cell r="A224">
-            <v>1582</v>
+            <v>1282</v>
           </cell>
         </row>
         <row r="225">
           <cell r="A225">
-            <v>1583</v>
+            <v>1283</v>
           </cell>
         </row>
         <row r="226">
           <cell r="A226">
-            <v>1584</v>
+            <v>1284</v>
           </cell>
         </row>
         <row r="227">
           <cell r="A227">
-            <v>1585</v>
+            <v>1285</v>
           </cell>
         </row>
         <row r="228">
           <cell r="A228">
-            <v>1586</v>
+            <v>1286</v>
           </cell>
         </row>
         <row r="229">
           <cell r="A229">
-            <v>1587</v>
+            <v>1287</v>
           </cell>
         </row>
         <row r="230">
           <cell r="A230">
-            <v>1588</v>
+            <v>1288</v>
           </cell>
         </row>
         <row r="231">
           <cell r="A231">
-            <v>1589</v>
+            <v>1289</v>
           </cell>
         </row>
         <row r="232">
           <cell r="A232">
-            <v>1590</v>
+            <v>1290</v>
           </cell>
         </row>
         <row r="233">
           <cell r="A233">
-            <v>1591</v>
+            <v>1291</v>
           </cell>
         </row>
         <row r="234">
           <cell r="A234">
-            <v>1592</v>
+            <v>1292</v>
           </cell>
         </row>
         <row r="235">
           <cell r="A235">
-            <v>1593</v>
+            <v>1293</v>
           </cell>
         </row>
         <row r="236">
           <cell r="A236">
-            <v>1594</v>
+            <v>1294</v>
           </cell>
         </row>
         <row r="237">
           <cell r="A237">
-            <v>1595</v>
+            <v>1295</v>
           </cell>
         </row>
         <row r="238">
           <cell r="A238">
-            <v>1596</v>
+            <v>1296</v>
           </cell>
         </row>
         <row r="239">
           <cell r="A239">
-            <v>1597</v>
+            <v>1297</v>
           </cell>
         </row>
         <row r="240">
           <cell r="A240">
-            <v>1598</v>
+            <v>1298</v>
           </cell>
         </row>
         <row r="241">
           <cell r="A241">
-            <v>1599</v>
+            <v>1299</v>
           </cell>
         </row>
         <row r="242">
           <cell r="A242">
-            <v>1600</v>
+            <v>1300</v>
           </cell>
         </row>
         <row r="243">
           <cell r="A243">
-            <v>1601</v>
+            <v>1301</v>
           </cell>
         </row>
         <row r="244">
           <cell r="A244">
-            <v>1602</v>
+            <v>1302</v>
           </cell>
         </row>
         <row r="245">
           <cell r="A245">
-            <v>1603</v>
+            <v>1303</v>
           </cell>
         </row>
         <row r="246">
           <cell r="A246">
-            <v>1604</v>
+            <v>1304</v>
           </cell>
         </row>
         <row r="247">
           <cell r="A247">
-            <v>1605</v>
+            <v>1305</v>
           </cell>
         </row>
         <row r="248">
           <cell r="A248">
-            <v>1606</v>
+            <v>1306</v>
           </cell>
         </row>
         <row r="249">
           <cell r="A249">
-            <v>1607</v>
+            <v>1307</v>
           </cell>
         </row>
         <row r="250">
           <cell r="A250">
-            <v>1608</v>
+            <v>1308</v>
           </cell>
         </row>
         <row r="251">
           <cell r="A251">
-            <v>1609</v>
+            <v>1309</v>
           </cell>
         </row>
         <row r="252">
           <cell r="A252">
-            <v>1610</v>
+            <v>1310</v>
           </cell>
         </row>
         <row r="253">
           <cell r="A253">
-            <v>1611</v>
+            <v>1311</v>
           </cell>
         </row>
         <row r="254">
           <cell r="A254">
-            <v>1612</v>
+            <v>1312</v>
           </cell>
         </row>
         <row r="255">
           <cell r="A255">
-            <v>1613</v>
+            <v>1313</v>
           </cell>
         </row>
         <row r="256">
           <cell r="A256">
-            <v>1614</v>
+            <v>1314</v>
           </cell>
         </row>
         <row r="257">
           <cell r="A257">
-            <v>1615</v>
+            <v>1315</v>
           </cell>
         </row>
         <row r="258">
           <cell r="A258">
-            <v>1616</v>
+            <v>1316</v>
           </cell>
         </row>
         <row r="259">
           <cell r="A259">
-            <v>1617</v>
+            <v>1317</v>
           </cell>
         </row>
         <row r="260">
           <cell r="A260">
-            <v>1618</v>
+            <v>1318</v>
           </cell>
         </row>
         <row r="261">
           <cell r="A261">
-            <v>1619</v>
+            <v>1319</v>
           </cell>
         </row>
         <row r="262">
           <cell r="A262">
-            <v>1620</v>
+            <v>1320</v>
           </cell>
         </row>
         <row r="263">
           <cell r="A263">
-            <v>1621</v>
+            <v>1321</v>
           </cell>
         </row>
         <row r="264">
           <cell r="A264">
-            <v>1622</v>
+            <v>1322</v>
           </cell>
         </row>
         <row r="265">
           <cell r="A265">
-            <v>1623</v>
+            <v>1323</v>
           </cell>
         </row>
         <row r="266">
           <cell r="A266">
-            <v>1624</v>
+            <v>1324</v>
           </cell>
         </row>
         <row r="267">
           <cell r="A267">
-            <v>1625</v>
+            <v>1325</v>
           </cell>
         </row>
         <row r="268">
           <cell r="A268">
-            <v>1626</v>
+            <v>1326</v>
           </cell>
         </row>
         <row r="269">
           <cell r="A269">
-            <v>1627</v>
+            <v>1327</v>
           </cell>
         </row>
         <row r="270">
           <cell r="A270">
-            <v>1628</v>
+            <v>1328</v>
           </cell>
         </row>
         <row r="271">
           <cell r="A271">
-            <v>1629</v>
+            <v>1329</v>
           </cell>
         </row>
         <row r="272">
           <cell r="A272">
-            <v>1630</v>
+            <v>1330</v>
           </cell>
         </row>
         <row r="273">
           <cell r="A273">
-            <v>1631</v>
+            <v>1331</v>
           </cell>
         </row>
         <row r="274">
           <cell r="A274">
-            <v>1632</v>
+            <v>1332</v>
           </cell>
         </row>
         <row r="275">
           <cell r="A275">
-            <v>1633</v>
+            <v>1333</v>
           </cell>
         </row>
         <row r="276">
           <cell r="A276">
-            <v>1634</v>
+            <v>1334</v>
           </cell>
         </row>
         <row r="277">
           <cell r="A277">
-            <v>1635</v>
+            <v>1335</v>
           </cell>
         </row>
         <row r="278">
           <cell r="A278">
-            <v>1636</v>
+            <v>1336</v>
           </cell>
         </row>
         <row r="279">
           <cell r="A279">
-            <v>1637</v>
+            <v>1337</v>
           </cell>
         </row>
         <row r="280">
           <cell r="A280">
-            <v>1638</v>
+            <v>1338</v>
           </cell>
         </row>
         <row r="281">
           <cell r="A281">
-            <v>1639</v>
+            <v>1339</v>
           </cell>
         </row>
         <row r="282">
           <cell r="A282">
-            <v>1640</v>
+            <v>1340</v>
           </cell>
         </row>
         <row r="283">
           <cell r="A283">
-            <v>1641</v>
+            <v>1341</v>
           </cell>
         </row>
         <row r="284">
           <cell r="A284">
-            <v>1642</v>
+            <v>1342</v>
           </cell>
         </row>
         <row r="285">
           <cell r="A285">
-            <v>1643</v>
+            <v>1343</v>
           </cell>
         </row>
         <row r="286">
           <cell r="A286">
-            <v>1644</v>
+            <v>1344</v>
           </cell>
         </row>
         <row r="287">
           <cell r="A287">
-            <v>1645</v>
+            <v>1345</v>
           </cell>
         </row>
         <row r="288">
           <cell r="A288">
-            <v>1646</v>
+            <v>1346</v>
           </cell>
         </row>
         <row r="289">
           <cell r="A289">
-            <v>1647</v>
+            <v>1347</v>
           </cell>
         </row>
         <row r="290">
           <cell r="A290">
-            <v>1648</v>
+            <v>1348</v>
           </cell>
         </row>
         <row r="291">
           <cell r="A291">
-            <v>1649</v>
+            <v>1349</v>
           </cell>
         </row>
         <row r="292">
           <cell r="A292">
-            <v>1650</v>
+            <v>1350</v>
           </cell>
         </row>
         <row r="293">
           <cell r="A293">
-            <v>1651</v>
+            <v>1351</v>
           </cell>
         </row>
         <row r="294">
           <cell r="A294">
-            <v>1652</v>
+            <v>1352</v>
           </cell>
         </row>
         <row r="295">
           <cell r="A295">
-            <v>1653</v>
+            <v>1353</v>
           </cell>
         </row>
         <row r="296">
           <cell r="A296">
-            <v>1654</v>
+            <v>1354</v>
           </cell>
         </row>
         <row r="297">
           <cell r="A297">
-            <v>1655</v>
+            <v>1355</v>
           </cell>
         </row>
         <row r="298">
           <cell r="A298">
-            <v>1656</v>
+            <v>1356</v>
           </cell>
         </row>
         <row r="299">
           <cell r="A299">
-            <v>1657</v>
+            <v>1357</v>
           </cell>
         </row>
         <row r="300">
           <cell r="A300">
-            <v>1658</v>
+            <v>1358</v>
           </cell>
         </row>
         <row r="301">
           <cell r="A301">
-            <v>1659</v>
+            <v>1359</v>
           </cell>
         </row>
         <row r="302">
           <cell r="A302">
-            <v>1660</v>
+            <v>1360</v>
           </cell>
         </row>
         <row r="303">
           <cell r="A303">
-            <v>1661</v>
+            <v>1361</v>
           </cell>
         </row>
         <row r="304">
           <cell r="A304">
-            <v>1662</v>
+            <v>1362</v>
           </cell>
         </row>
         <row r="305">
           <cell r="A305">
-            <v>1663</v>
+            <v>1363</v>
           </cell>
         </row>
         <row r="306">
           <cell r="A306">
-            <v>1664</v>
+            <v>1364</v>
           </cell>
         </row>
         <row r="307">
           <cell r="A307">
-            <v>1665</v>
+            <v>1365</v>
           </cell>
         </row>
         <row r="308">
           <cell r="A308">
-            <v>1666</v>
+            <v>1366</v>
           </cell>
         </row>
         <row r="309">
           <cell r="A309">
-            <v>1667</v>
+            <v>1367</v>
           </cell>
         </row>
         <row r="310">
           <cell r="A310">
-            <v>1668</v>
+            <v>1368</v>
           </cell>
         </row>
         <row r="311">
           <cell r="A311">
-            <v>1669</v>
+            <v>1369</v>
           </cell>
         </row>
         <row r="312">
           <cell r="A312">
-            <v>1670</v>
+            <v>1370</v>
           </cell>
         </row>
         <row r="313">
           <cell r="A313">
-            <v>1671</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="314">
           <cell r="A314">
-            <v>1672</v>
+            <v>1372</v>
           </cell>
         </row>
         <row r="315">
           <cell r="A315">
-            <v>1673</v>
+            <v>1373</v>
           </cell>
         </row>
         <row r="316">
           <cell r="A316">
-            <v>1674</v>
+            <v>1374</v>
           </cell>
         </row>
         <row r="317">
           <cell r="A317">
-            <v>1675</v>
+            <v>1375</v>
           </cell>
         </row>
         <row r="318">
           <cell r="A318">
-            <v>1676</v>
+            <v>1376</v>
           </cell>
         </row>
         <row r="319">
           <cell r="A319">
-            <v>1677</v>
+            <v>1377</v>
           </cell>
         </row>
         <row r="320">
           <cell r="A320">
-            <v>1678</v>
+            <v>1378</v>
           </cell>
         </row>
         <row r="321">
           <cell r="A321">
-            <v>1679</v>
+            <v>1379</v>
           </cell>
         </row>
         <row r="322">
           <cell r="A322">
-            <v>1680</v>
+            <v>1380</v>
           </cell>
         </row>
         <row r="323">
           <cell r="A323">
-            <v>1681</v>
+            <v>1381</v>
           </cell>
         </row>
         <row r="324">
           <cell r="A324">
-            <v>1682</v>
+            <v>1382</v>
           </cell>
         </row>
         <row r="325">
           <cell r="A325">
-            <v>1683</v>
+            <v>1383</v>
           </cell>
         </row>
         <row r="326">
           <cell r="A326">
-            <v>1684</v>
+            <v>1384</v>
           </cell>
         </row>
         <row r="327">
           <cell r="A327">
-            <v>1685</v>
+            <v>1385</v>
           </cell>
         </row>
         <row r="328">
           <cell r="A328">
-            <v>1686</v>
+            <v>1386</v>
           </cell>
         </row>
         <row r="329">
           <cell r="A329">
-            <v>1687</v>
+            <v>1387</v>
           </cell>
         </row>
         <row r="330">
           <cell r="A330">
-            <v>1688</v>
+            <v>1388</v>
           </cell>
         </row>
         <row r="331">
           <cell r="A331">
-            <v>1689</v>
+            <v>1389</v>
           </cell>
         </row>
         <row r="332">
           <cell r="A332">
-            <v>1690</v>
+            <v>1390</v>
           </cell>
         </row>
         <row r="333">
           <cell r="A333">
-            <v>1691</v>
+            <v>1391</v>
           </cell>
         </row>
         <row r="334">
           <cell r="A334">
-            <v>1692</v>
+            <v>1392</v>
           </cell>
         </row>
         <row r="335">
           <cell r="A335">
-            <v>1693</v>
+            <v>1393</v>
           </cell>
         </row>
         <row r="336">
           <cell r="A336">
-            <v>1694</v>
+            <v>1394</v>
           </cell>
         </row>
         <row r="337">
           <cell r="A337">
-            <v>1695</v>
+            <v>1395</v>
           </cell>
         </row>
         <row r="338">
           <cell r="A338">
-            <v>1696</v>
+            <v>1396</v>
           </cell>
         </row>
         <row r="339">
           <cell r="A339">
-            <v>1697</v>
+            <v>1397</v>
           </cell>
         </row>
         <row r="340">
           <cell r="A340">
-            <v>1698</v>
+            <v>1398</v>
           </cell>
         </row>
         <row r="341">
           <cell r="A341">
-            <v>1699</v>
+            <v>1399</v>
           </cell>
         </row>
         <row r="342">
           <cell r="A342">
-            <v>1700</v>
+            <v>1400</v>
           </cell>
         </row>
         <row r="343">
           <cell r="A343">
-            <v>1701</v>
+            <v>1401</v>
           </cell>
         </row>
         <row r="344">
           <cell r="A344">
-            <v>1702</v>
+            <v>1402</v>
           </cell>
         </row>
         <row r="345">
           <cell r="A345">
-            <v>1703</v>
+            <v>1403</v>
           </cell>
         </row>
         <row r="346">
           <cell r="A346">
-            <v>1704</v>
+            <v>1404</v>
           </cell>
         </row>
         <row r="347">
           <cell r="A347">
-            <v>1705</v>
+            <v>1405</v>
           </cell>
         </row>
         <row r="348">
           <cell r="A348">
-            <v>1706</v>
+            <v>1406</v>
           </cell>
         </row>
         <row r="349">
           <cell r="A349">
-            <v>1707</v>
+            <v>1407</v>
           </cell>
         </row>
         <row r="350">
           <cell r="A350">
-            <v>1708</v>
+            <v>1408</v>
           </cell>
         </row>
         <row r="351">
           <cell r="A351">
-            <v>1709</v>
+            <v>1409</v>
           </cell>
         </row>
         <row r="352">
           <cell r="A352">
-            <v>1710</v>
+            <v>1410</v>
           </cell>
         </row>
         <row r="353">
           <cell r="A353">
-            <v>1711</v>
+            <v>1411</v>
           </cell>
         </row>
         <row r="354">
           <cell r="A354">
-            <v>1712</v>
+            <v>1412</v>
           </cell>
         </row>
         <row r="355">
           <cell r="A355">
-            <v>1713</v>
+            <v>1413</v>
           </cell>
         </row>
         <row r="356">
           <cell r="A356">
-            <v>1714</v>
+            <v>1414</v>
           </cell>
         </row>
         <row r="357">
           <cell r="A357">
-            <v>1715</v>
+            <v>1415</v>
           </cell>
         </row>
         <row r="358">
           <cell r="A358">
-            <v>1716</v>
+            <v>1416</v>
           </cell>
         </row>
         <row r="359">
           <cell r="A359">
-            <v>1717</v>
+            <v>1417</v>
           </cell>
         </row>
         <row r="360">
           <cell r="A360">
-            <v>1718</v>
+            <v>1418</v>
           </cell>
         </row>
         <row r="361">
           <cell r="A361">
-            <v>1719</v>
+            <v>1419</v>
           </cell>
         </row>
         <row r="362">
           <cell r="A362">
-            <v>1720</v>
+            <v>1420</v>
           </cell>
         </row>
         <row r="363">
           <cell r="A363">
-            <v>1721</v>
+            <v>1421</v>
           </cell>
         </row>
         <row r="364">
           <cell r="A364">
-            <v>1722</v>
+            <v>1422</v>
           </cell>
         </row>
         <row r="365">
           <cell r="A365">
-            <v>1723</v>
+            <v>1423</v>
           </cell>
         </row>
         <row r="366">
           <cell r="A366">
-            <v>1724</v>
+            <v>1424</v>
           </cell>
         </row>
         <row r="367">
           <cell r="A367">
-            <v>1725</v>
+            <v>1425</v>
           </cell>
         </row>
         <row r="368">
           <cell r="A368">
-            <v>1726</v>
+            <v>1426</v>
           </cell>
         </row>
         <row r="369">
           <cell r="A369">
-            <v>1727</v>
+            <v>1427</v>
           </cell>
         </row>
         <row r="370">
           <cell r="A370">
-            <v>1728</v>
+            <v>1428</v>
           </cell>
         </row>
         <row r="371">
           <cell r="A371">
-            <v>1729</v>
+            <v>1429</v>
           </cell>
         </row>
         <row r="372">
           <cell r="A372">
-            <v>1730</v>
+            <v>1430</v>
           </cell>
         </row>
         <row r="373">
           <cell r="A373">
-            <v>1731</v>
+            <v>1431</v>
           </cell>
         </row>
         <row r="374">
           <cell r="A374">
-            <v>1732</v>
+            <v>1432</v>
           </cell>
         </row>
         <row r="375">
           <cell r="A375">
-            <v>1733</v>
+            <v>1433</v>
           </cell>
         </row>
         <row r="376">
           <cell r="A376">
-            <v>1734</v>
+            <v>1434</v>
           </cell>
         </row>
         <row r="377">
           <cell r="A377">
-            <v>1735</v>
+            <v>1435</v>
           </cell>
         </row>
         <row r="378">
           <cell r="A378">
-            <v>1736</v>
+            <v>1436</v>
           </cell>
         </row>
         <row r="379">
           <cell r="A379">
-            <v>1737</v>
+            <v>1437</v>
           </cell>
         </row>
         <row r="380">
           <cell r="A380">
-            <v>1738</v>
+            <v>1438</v>
           </cell>
         </row>
         <row r="381">
           <cell r="A381">
-            <v>1739</v>
+            <v>1439</v>
           </cell>
         </row>
         <row r="382">
           <cell r="A382">
-            <v>1740</v>
+            <v>1440</v>
           </cell>
         </row>
         <row r="383">
           <cell r="A383">
-            <v>1741</v>
+            <v>1441</v>
           </cell>
         </row>
         <row r="384">
           <cell r="A384">
-            <v>1742</v>
+            <v>1442</v>
           </cell>
         </row>
         <row r="385">
           <cell r="A385">
-            <v>1743</v>
+            <v>1443</v>
           </cell>
         </row>
         <row r="386">
           <cell r="A386">
-            <v>1744</v>
+            <v>1444</v>
           </cell>
         </row>
         <row r="387">
           <cell r="A387">
-            <v>1745</v>
+            <v>1445</v>
           </cell>
         </row>
         <row r="388">
           <cell r="A388">
-            <v>1746</v>
+            <v>1446</v>
           </cell>
         </row>
         <row r="389">
           <cell r="A389">
-            <v>1747</v>
+            <v>1447</v>
           </cell>
         </row>
         <row r="390">
           <cell r="A390">
-            <v>1748</v>
+            <v>1448</v>
           </cell>
         </row>
         <row r="391">
           <cell r="A391">
-            <v>1749</v>
+            <v>1449</v>
           </cell>
         </row>
         <row r="392">
           <cell r="A392">
-            <v>1750</v>
+            <v>1450</v>
           </cell>
         </row>
         <row r="393">
           <cell r="A393">
-            <v>1751</v>
+            <v>1451</v>
           </cell>
         </row>
         <row r="394">
           <cell r="A394">
-            <v>1752</v>
+            <v>1452</v>
           </cell>
         </row>
         <row r="395">
           <cell r="A395">
-            <v>1753</v>
+            <v>1453</v>
           </cell>
         </row>
         <row r="396">
           <cell r="A396">
-            <v>1754</v>
+            <v>1454</v>
           </cell>
         </row>
         <row r="397">
           <cell r="A397">
-            <v>1755</v>
+            <v>1455</v>
           </cell>
         </row>
         <row r="398">
           <cell r="A398">
-            <v>1756</v>
+            <v>1456</v>
           </cell>
         </row>
         <row r="399">
           <cell r="A399">
-            <v>1757</v>
+            <v>1457</v>
           </cell>
         </row>
         <row r="400">
           <cell r="A400">
-            <v>1758</v>
+            <v>1458</v>
           </cell>
         </row>
         <row r="401">
           <cell r="A401">
-            <v>1759</v>
+            <v>1459</v>
           </cell>
         </row>
         <row r="402">
           <cell r="A402">
-            <v>1760</v>
+            <v>1460</v>
           </cell>
         </row>
         <row r="403">
           <cell r="A403">
-            <v>1761</v>
+            <v>1461</v>
           </cell>
         </row>
         <row r="404">
           <cell r="A404">
-            <v>1762</v>
+            <v>1462</v>
           </cell>
         </row>
         <row r="405">
           <cell r="A405">
-            <v>1763</v>
+            <v>1463</v>
           </cell>
         </row>
         <row r="406">
           <cell r="A406">
-            <v>1764</v>
+            <v>1464</v>
           </cell>
         </row>
         <row r="407">
           <cell r="A407">
-            <v>1765</v>
+            <v>1465</v>
           </cell>
         </row>
         <row r="408">
           <cell r="A408">
-            <v>1766</v>
+            <v>1466</v>
           </cell>
         </row>
         <row r="409">
           <cell r="A409">
-            <v>1767</v>
+            <v>1467</v>
           </cell>
         </row>
         <row r="410">
           <cell r="A410">
-            <v>1768</v>
+            <v>1468</v>
           </cell>
         </row>
         <row r="411">
           <cell r="A411">
-            <v>1769</v>
+            <v>1469</v>
           </cell>
         </row>
         <row r="412">
           <cell r="A412">
-            <v>1770</v>
+            <v>1470</v>
           </cell>
         </row>
         <row r="413">
           <cell r="A413">
-            <v>1771</v>
+            <v>1471</v>
           </cell>
         </row>
         <row r="414">
           <cell r="A414">
-            <v>1772</v>
+            <v>1472</v>
           </cell>
         </row>
         <row r="415">
           <cell r="A415">
-            <v>1773</v>
+            <v>1473</v>
           </cell>
         </row>
         <row r="416">
           <cell r="A416">
-            <v>1774</v>
+            <v>1474</v>
           </cell>
         </row>
         <row r="417">
           <cell r="A417">
-            <v>1775</v>
+            <v>1475</v>
           </cell>
         </row>
         <row r="418">
           <cell r="A418">
-            <v>1776</v>
+            <v>1476</v>
           </cell>
         </row>
         <row r="419">
           <cell r="A419">
-            <v>1777</v>
+            <v>1477</v>
           </cell>
         </row>
         <row r="420">
           <cell r="A420">
-            <v>1778</v>
+            <v>1478</v>
           </cell>
         </row>
         <row r="421">
           <cell r="A421">
-            <v>1779</v>
+            <v>1479</v>
           </cell>
         </row>
         <row r="422">
           <cell r="A422">
-            <v>1780</v>
+            <v>1480</v>
           </cell>
         </row>
         <row r="423">
           <cell r="A423">
-            <v>1781</v>
+            <v>1481</v>
           </cell>
         </row>
         <row r="424">
           <cell r="A424">
-            <v>1782</v>
+            <v>1482</v>
           </cell>
         </row>
         <row r="425">
           <cell r="A425">
-            <v>1783</v>
+            <v>1483</v>
           </cell>
         </row>
         <row r="426">
           <cell r="A426">
-            <v>1784</v>
+            <v>1484</v>
           </cell>
         </row>
         <row r="427">
           <cell r="A427">
-            <v>1785</v>
+            <v>1485</v>
           </cell>
         </row>
         <row r="428">
           <cell r="A428">
-            <v>1786</v>
+            <v>1486</v>
           </cell>
         </row>
         <row r="429">
           <cell r="A429">
-            <v>1787</v>
+            <v>1487</v>
           </cell>
         </row>
         <row r="430">
           <cell r="A430">
-            <v>1788</v>
+            <v>1488</v>
           </cell>
         </row>
         <row r="431">
           <cell r="A431">
-            <v>1789</v>
+            <v>1489</v>
           </cell>
         </row>
         <row r="432">
           <cell r="A432">
-            <v>1790</v>
+            <v>1490</v>
           </cell>
         </row>
         <row r="433">
           <cell r="A433">
-            <v>1791</v>
+            <v>1491</v>
           </cell>
         </row>
         <row r="434">
           <cell r="A434">
-            <v>1792</v>
+            <v>1492</v>
           </cell>
         </row>
         <row r="435">
           <cell r="A435">
-            <v>1793</v>
+            <v>1493</v>
           </cell>
         </row>
         <row r="436">
           <cell r="A436">
-            <v>1794</v>
+            <v>1494</v>
           </cell>
         </row>
         <row r="437">
           <cell r="A437">
-            <v>1795</v>
+            <v>1495</v>
           </cell>
         </row>
         <row r="438">
           <cell r="A438">
-            <v>1796</v>
+            <v>1496</v>
           </cell>
         </row>
         <row r="439">
           <cell r="A439">
-            <v>1797</v>
+            <v>1497</v>
           </cell>
         </row>
         <row r="440">
           <cell r="A440">
-            <v>1798</v>
+            <v>1498</v>
           </cell>
         </row>
         <row r="441">
           <cell r="A441">
-            <v>1799</v>
+            <v>1499</v>
           </cell>
         </row>
         <row r="442">
           <cell r="A442">
-            <v>1800</v>
+            <v>1500</v>
           </cell>
         </row>
         <row r="443">
           <cell r="A443">
-            <v>1801</v>
+            <v>1501</v>
           </cell>
         </row>
         <row r="444">
           <cell r="A444">
-            <v>1802</v>
+            <v>1502</v>
           </cell>
         </row>
         <row r="445">
           <cell r="A445">
-            <v>1803</v>
+            <v>1503</v>
           </cell>
         </row>
         <row r="446">
           <cell r="A446">
-            <v>1804</v>
+            <v>1504</v>
           </cell>
         </row>
         <row r="447">
           <cell r="A447">
-            <v>1805</v>
+            <v>1505</v>
           </cell>
         </row>
         <row r="448">
           <cell r="A448">
-            <v>1806</v>
+            <v>1506</v>
           </cell>
         </row>
         <row r="449">
           <cell r="A449">
-            <v>1807</v>
+            <v>1507</v>
           </cell>
         </row>
         <row r="450">
           <cell r="A450">
-            <v>1808</v>
+            <v>1508</v>
           </cell>
         </row>
         <row r="451">
           <cell r="A451">
-            <v>1809</v>
+            <v>1509</v>
           </cell>
         </row>
         <row r="452">
           <cell r="A452">
-            <v>1810</v>
+            <v>1510</v>
           </cell>
         </row>
         <row r="453">
           <cell r="A453">
-            <v>1811</v>
+            <v>1511</v>
           </cell>
         </row>
         <row r="454">
           <cell r="A454">
-            <v>1812</v>
+            <v>1512</v>
           </cell>
         </row>
         <row r="455">
           <cell r="A455">
-            <v>1813</v>
+            <v>1513</v>
           </cell>
         </row>
         <row r="456">
           <cell r="A456">
-            <v>1814</v>
+            <v>1514</v>
           </cell>
         </row>
         <row r="457">
           <cell r="A457">
-            <v>1815</v>
+            <v>1515</v>
           </cell>
         </row>
         <row r="458">
           <cell r="A458">
-            <v>1816</v>
+            <v>1516</v>
           </cell>
         </row>
         <row r="459">
           <cell r="A459">
-            <v>1817</v>
+            <v>1517</v>
           </cell>
         </row>
         <row r="460">
           <cell r="A460">
-            <v>1818</v>
+            <v>1518</v>
           </cell>
         </row>
         <row r="461">
           <cell r="A461">
-            <v>1819</v>
+            <v>1519</v>
           </cell>
         </row>
         <row r="462">
           <cell r="A462">
-            <v>1820</v>
+            <v>1520</v>
           </cell>
         </row>
         <row r="463">
           <cell r="A463">
-            <v>1821</v>
+            <v>1521</v>
           </cell>
         </row>
         <row r="464">
           <cell r="A464">
-            <v>1822</v>
+            <v>1522</v>
           </cell>
         </row>
         <row r="465">
           <cell r="A465">
-            <v>1823</v>
+            <v>1523</v>
           </cell>
         </row>
         <row r="466">
           <cell r="A466">
-            <v>1824</v>
+            <v>1524</v>
           </cell>
         </row>
         <row r="467">
           <cell r="A467">
-            <v>1825</v>
+            <v>1525</v>
           </cell>
         </row>
         <row r="468">
           <cell r="A468">
-            <v>1826</v>
+            <v>1526</v>
           </cell>
         </row>
         <row r="469">
           <cell r="A469">
-            <v>1827</v>
+            <v>1527</v>
           </cell>
         </row>
         <row r="470">
           <cell r="A470">
-            <v>1828</v>
+            <v>1528</v>
           </cell>
         </row>
         <row r="471">
           <cell r="A471">
-            <v>1829</v>
+            <v>1529</v>
           </cell>
         </row>
         <row r="472">
           <cell r="A472">
-            <v>1830</v>
+            <v>1530</v>
           </cell>
         </row>
         <row r="473">
           <cell r="A473">
-            <v>1831</v>
+            <v>1531</v>
           </cell>
         </row>
         <row r="474">
           <cell r="A474">
-            <v>1832</v>
+            <v>1532</v>
           </cell>
         </row>
         <row r="475">
           <cell r="A475">
-            <v>1833</v>
+            <v>1533</v>
           </cell>
         </row>
         <row r="476">
           <cell r="A476">
-            <v>1834</v>
+            <v>1534</v>
           </cell>
         </row>
         <row r="477">
           <cell r="A477">
-            <v>1835</v>
+            <v>1535</v>
           </cell>
         </row>
         <row r="478">
           <cell r="A478">
-            <v>1836</v>
+            <v>1536</v>
           </cell>
         </row>
         <row r="479">
           <cell r="A479">
-            <v>1837</v>
+            <v>1537</v>
           </cell>
         </row>
         <row r="480">
           <cell r="A480">
-            <v>1838</v>
+            <v>1538</v>
           </cell>
         </row>
         <row r="481">
           <cell r="A481">
-            <v>1839</v>
+            <v>1539</v>
           </cell>
         </row>
         <row r="482">
           <cell r="A482">
-            <v>1840</v>
+            <v>1540</v>
           </cell>
         </row>
         <row r="483">
           <cell r="A483">
-            <v>1841</v>
+            <v>1541</v>
           </cell>
         </row>
         <row r="484">
           <cell r="A484">
-            <v>1842</v>
+            <v>1542</v>
           </cell>
         </row>
         <row r="485">
           <cell r="A485">
-            <v>1843</v>
+            <v>1543</v>
           </cell>
         </row>
         <row r="486">
           <cell r="A486">
-            <v>1844</v>
+            <v>1544</v>
           </cell>
         </row>
         <row r="487">
           <cell r="A487">
-            <v>1845</v>
+            <v>1545</v>
           </cell>
         </row>
         <row r="488">
           <cell r="A488">
-            <v>1846</v>
+            <v>1546</v>
           </cell>
         </row>
         <row r="489">
           <cell r="A489">
-            <v>1847</v>
+            <v>1547</v>
           </cell>
         </row>
         <row r="490">
           <cell r="A490">
-            <v>1848</v>
+            <v>1548</v>
           </cell>
         </row>
         <row r="491">
           <cell r="A491">
-            <v>1849</v>
+            <v>1549</v>
           </cell>
         </row>
         <row r="492">
           <cell r="A492">
-            <v>1850</v>
+            <v>1550</v>
           </cell>
         </row>
         <row r="493">
           <cell r="A493">
-            <v>1851</v>
+            <v>1551</v>
           </cell>
         </row>
         <row r="494">
           <cell r="A494">
-            <v>1852</v>
+            <v>1552</v>
           </cell>
         </row>
         <row r="495">
           <cell r="A495">
-            <v>1853</v>
+            <v>1553</v>
           </cell>
         </row>
         <row r="496">
           <cell r="A496">
-            <v>1854</v>
+            <v>1554</v>
           </cell>
         </row>
         <row r="497">
           <cell r="A497">
-            <v>1855</v>
+            <v>1555</v>
           </cell>
         </row>
         <row r="498">
           <cell r="A498">
-            <v>1856</v>
+            <v>1556</v>
           </cell>
         </row>
         <row r="499">
           <cell r="A499">
-            <v>1857</v>
+            <v>1557</v>
           </cell>
         </row>
         <row r="500">
           <cell r="A500">
-            <v>1858</v>
+            <v>1558</v>
           </cell>
         </row>
         <row r="501">
           <cell r="A501">
-            <v>1859</v>
+            <v>1559</v>
           </cell>
         </row>
         <row r="502">
           <cell r="A502">
-            <v>1860</v>
+            <v>1560</v>
           </cell>
         </row>
         <row r="503">
           <cell r="A503">
-            <v>1861</v>
+            <v>1561</v>
           </cell>
         </row>
         <row r="504">
           <cell r="A504">
-            <v>1862</v>
+            <v>1562</v>
           </cell>
         </row>
         <row r="505">
           <cell r="A505">
-            <v>1863</v>
+            <v>1563</v>
           </cell>
         </row>
         <row r="506">
           <cell r="A506">
-            <v>1864</v>
+            <v>1564</v>
           </cell>
         </row>
         <row r="507">
           <cell r="A507">
-            <v>1865</v>
+            <v>1565</v>
           </cell>
         </row>
         <row r="508">
           <cell r="A508">
-            <v>1866</v>
+            <v>1566</v>
           </cell>
         </row>
         <row r="509">
           <cell r="A509">
-            <v>1867</v>
+            <v>1567</v>
           </cell>
         </row>
         <row r="510">
           <cell r="A510">
-            <v>1868</v>
+            <v>1568</v>
           </cell>
         </row>
         <row r="511">
           <cell r="A511">
-            <v>1869</v>
+            <v>1569</v>
           </cell>
         </row>
         <row r="512">
           <cell r="A512">
-            <v>1870</v>
+            <v>1570</v>
           </cell>
         </row>
         <row r="513">
           <cell r="A513">
-            <v>1871</v>
+            <v>1571</v>
           </cell>
         </row>
         <row r="514">
           <cell r="A514">
-            <v>1872</v>
+            <v>1572</v>
           </cell>
         </row>
         <row r="515">
           <cell r="A515">
-            <v>1873</v>
+            <v>1573</v>
           </cell>
         </row>
         <row r="516">
           <cell r="A516">
-            <v>1874</v>
+            <v>1574</v>
           </cell>
         </row>
         <row r="517">
           <cell r="A517">
-            <v>1875</v>
+            <v>1575</v>
           </cell>
         </row>
         <row r="518">
           <cell r="A518">
-            <v>1876</v>
+            <v>1576</v>
           </cell>
         </row>
         <row r="519">
           <cell r="A519">
-            <v>1877</v>
+            <v>1577</v>
           </cell>
         </row>
         <row r="520">
           <cell r="A520">
-            <v>1878</v>
+            <v>1578</v>
           </cell>
         </row>
         <row r="521">
           <cell r="A521">
-            <v>1879</v>
+            <v>1579</v>
           </cell>
         </row>
         <row r="522">
           <cell r="A522">
-            <v>1880</v>
+            <v>1580</v>
           </cell>
         </row>
         <row r="523">
           <cell r="A523">
-            <v>1881</v>
+            <v>1581</v>
           </cell>
         </row>
         <row r="524">
           <cell r="A524">
-            <v>1882</v>
+            <v>1582</v>
           </cell>
         </row>
         <row r="525">
           <cell r="A525">
-            <v>1883</v>
+            <v>1583</v>
           </cell>
         </row>
         <row r="526">
           <cell r="A526">
-            <v>1884</v>
+            <v>1584</v>
           </cell>
         </row>
         <row r="527">
           <cell r="A527">
-            <v>1885</v>
+            <v>1585</v>
           </cell>
         </row>
         <row r="528">
           <cell r="A528">
-            <v>1886</v>
+            <v>1586</v>
           </cell>
         </row>
         <row r="529">
           <cell r="A529">
-            <v>1887</v>
+            <v>1587</v>
           </cell>
         </row>
         <row r="530">
           <cell r="A530">
-            <v>1888</v>
+            <v>1588</v>
           </cell>
         </row>
         <row r="531">
           <cell r="A531">
-            <v>1889</v>
+            <v>1589</v>
           </cell>
         </row>
         <row r="532">
           <cell r="A532">
-            <v>1890</v>
+            <v>1590</v>
           </cell>
         </row>
         <row r="533">
           <cell r="A533">
-            <v>1891</v>
+            <v>1591</v>
           </cell>
         </row>
         <row r="534">
           <cell r="A534">
-            <v>1892</v>
+            <v>1592</v>
           </cell>
         </row>
         <row r="535">
           <cell r="A535">
-            <v>1893</v>
+            <v>1593</v>
           </cell>
         </row>
         <row r="536">
           <cell r="A536">
-            <v>1894</v>
+            <v>1594</v>
           </cell>
         </row>
         <row r="537">
           <cell r="A537">
-            <v>1895</v>
+            <v>1595</v>
           </cell>
         </row>
         <row r="538">
           <cell r="A538">
-            <v>1896</v>
+            <v>1596</v>
           </cell>
         </row>
         <row r="539">
           <cell r="A539">
-            <v>1897</v>
+            <v>1597</v>
           </cell>
         </row>
         <row r="540">
           <cell r="A540">
-            <v>1898</v>
+            <v>1598</v>
           </cell>
         </row>
         <row r="541">
           <cell r="A541">
-            <v>1899</v>
+            <v>1599</v>
           </cell>
         </row>
         <row r="542">
           <cell r="A542">
-            <v>1900</v>
+            <v>1600</v>
           </cell>
         </row>
         <row r="543">
           <cell r="A543">
-            <v>1901</v>
+            <v>1601</v>
           </cell>
         </row>
         <row r="544">
           <cell r="A544">
-            <v>1902</v>
+            <v>1602</v>
           </cell>
         </row>
         <row r="545">
           <cell r="A545">
-            <v>1903</v>
+            <v>1603</v>
           </cell>
         </row>
         <row r="546">
           <cell r="A546">
-            <v>1904</v>
+            <v>1604</v>
           </cell>
         </row>
         <row r="547">
           <cell r="A547">
-            <v>1905</v>
+            <v>1605</v>
           </cell>
         </row>
         <row r="548">
           <cell r="A548">
-            <v>1906</v>
+            <v>1606</v>
           </cell>
         </row>
         <row r="549">
           <cell r="A549">
-            <v>1907</v>
+            <v>1607</v>
           </cell>
         </row>
         <row r="550">
           <cell r="A550">
-            <v>1908</v>
+            <v>1608</v>
           </cell>
         </row>
         <row r="551">
           <cell r="A551">
-            <v>1909</v>
+            <v>1609</v>
           </cell>
         </row>
         <row r="552">
           <cell r="A552">
-            <v>1910</v>
+            <v>1610</v>
           </cell>
         </row>
         <row r="553">
           <cell r="A553">
-            <v>1911</v>
+            <v>1611</v>
           </cell>
         </row>
         <row r="554">
           <cell r="A554">
-            <v>1912</v>
+            <v>1612</v>
           </cell>
         </row>
         <row r="555">
           <cell r="A555">
-            <v>1913</v>
+            <v>1613</v>
           </cell>
         </row>
         <row r="556">
           <cell r="A556">
-            <v>1914</v>
+            <v>1614</v>
           </cell>
         </row>
         <row r="557">
           <cell r="A557">
-            <v>1915</v>
+            <v>1615</v>
           </cell>
         </row>
         <row r="558">
           <cell r="A558">
-            <v>1916</v>
+            <v>1616</v>
           </cell>
         </row>
         <row r="559">
           <cell r="A559">
-            <v>1917</v>
+            <v>1617</v>
           </cell>
         </row>
         <row r="560">
           <cell r="A560">
-            <v>1918</v>
+            <v>1618</v>
           </cell>
         </row>
         <row r="561">
           <cell r="A561">
-            <v>1919</v>
+            <v>1619</v>
           </cell>
         </row>
         <row r="562">
           <cell r="A562">
-            <v>1920</v>
+            <v>1620</v>
           </cell>
         </row>
         <row r="563">
           <cell r="A563">
-            <v>1921</v>
+            <v>1621</v>
           </cell>
         </row>
         <row r="564">
           <cell r="A564">
-            <v>1922</v>
+            <v>1622</v>
           </cell>
         </row>
         <row r="565">
           <cell r="A565">
-            <v>1923</v>
+            <v>1623</v>
           </cell>
         </row>
         <row r="566">
           <cell r="A566">
-            <v>1924</v>
+            <v>1624</v>
           </cell>
         </row>
         <row r="567">
           <cell r="A567">
-            <v>1925</v>
+            <v>1625</v>
           </cell>
         </row>
         <row r="568">
           <cell r="A568">
-            <v>1926</v>
+            <v>1626</v>
           </cell>
         </row>
         <row r="569">
           <cell r="A569">
-            <v>1927</v>
+            <v>1627</v>
           </cell>
         </row>
         <row r="570">
           <cell r="A570">
-            <v>1928</v>
+            <v>1628</v>
           </cell>
         </row>
         <row r="571">
           <cell r="A571">
-            <v>1929</v>
+            <v>1629</v>
           </cell>
         </row>
         <row r="572">
           <cell r="A572">
-            <v>1930</v>
+            <v>1630</v>
           </cell>
         </row>
         <row r="573">
           <cell r="A573">
-            <v>1931</v>
+            <v>1631</v>
           </cell>
         </row>
         <row r="574">
           <cell r="A574">
-            <v>1932</v>
+            <v>1632</v>
           </cell>
         </row>
         <row r="575">
           <cell r="A575">
-            <v>1933</v>
+            <v>1633</v>
           </cell>
         </row>
         <row r="576">
           <cell r="A576">
-            <v>1934</v>
+            <v>1634</v>
           </cell>
         </row>
         <row r="577">
           <cell r="A577">
-            <v>1935</v>
+            <v>1635</v>
           </cell>
         </row>
         <row r="578">
           <cell r="A578">
-            <v>1936</v>
+            <v>1636</v>
           </cell>
         </row>
         <row r="579">
           <cell r="A579">
-            <v>1937</v>
+            <v>1637</v>
           </cell>
         </row>
         <row r="580">
           <cell r="A580">
-            <v>1938</v>
+            <v>1638</v>
           </cell>
         </row>
         <row r="581">
           <cell r="A581">
-            <v>1939</v>
+            <v>1639</v>
           </cell>
         </row>
         <row r="582">
           <cell r="A582">
-            <v>1940</v>
+            <v>1640</v>
           </cell>
         </row>
         <row r="583">
           <cell r="A583">
-            <v>1941</v>
+            <v>1641</v>
           </cell>
         </row>
         <row r="584">
           <cell r="A584">
-            <v>1942</v>
+            <v>1642</v>
           </cell>
         </row>
         <row r="585">
           <cell r="A585">
-            <v>1943</v>
+            <v>1643</v>
           </cell>
         </row>
         <row r="586">
           <cell r="A586">
-            <v>1944</v>
+            <v>1644</v>
           </cell>
         </row>
         <row r="587">
           <cell r="A587">
-            <v>1945</v>
+            <v>1645</v>
           </cell>
         </row>
         <row r="588">
           <cell r="A588">
-            <v>1946</v>
+            <v>1646</v>
           </cell>
         </row>
         <row r="589">
           <cell r="A589">
-            <v>1947</v>
+            <v>1647</v>
           </cell>
         </row>
         <row r="590">
           <cell r="A590">
-            <v>1948</v>
+            <v>1648</v>
           </cell>
         </row>
         <row r="591">
           <cell r="A591">
-            <v>1949</v>
+            <v>1649</v>
           </cell>
         </row>
         <row r="592">
           <cell r="A592">
-            <v>1950</v>
+            <v>1650</v>
           </cell>
         </row>
         <row r="593">
           <cell r="A593">
-            <v>1951</v>
+            <v>1651</v>
           </cell>
         </row>
         <row r="594">
           <cell r="A594">
-            <v>1952</v>
+            <v>1652</v>
           </cell>
         </row>
         <row r="595">
           <cell r="A595">
-            <v>1953</v>
+            <v>1653</v>
           </cell>
         </row>
         <row r="596">
           <cell r="A596">
-            <v>1954</v>
+            <v>1654</v>
           </cell>
         </row>
         <row r="597">
           <cell r="A597">
-            <v>1955</v>
+            <v>1655</v>
           </cell>
         </row>
         <row r="598">
           <cell r="A598">
-            <v>1956</v>
+            <v>1656</v>
           </cell>
         </row>
         <row r="599">
           <cell r="A599">
-            <v>1957</v>
+            <v>1657</v>
           </cell>
         </row>
         <row r="600">
           <cell r="A600">
-            <v>1958</v>
+            <v>1658</v>
           </cell>
         </row>
         <row r="601">
           <cell r="A601">
-            <v>1959</v>
+            <v>1659</v>
           </cell>
         </row>
         <row r="602">
           <cell r="A602">
-            <v>1960</v>
+            <v>1660</v>
           </cell>
         </row>
         <row r="603">
           <cell r="A603">
-            <v>1961</v>
+            <v>1661</v>
           </cell>
         </row>
         <row r="604">
           <cell r="A604">
-            <v>1962</v>
+            <v>1662</v>
           </cell>
         </row>
         <row r="605">
           <cell r="A605">
-            <v>1963</v>
+            <v>1663</v>
           </cell>
         </row>
         <row r="606">
           <cell r="A606">
-            <v>1964</v>
+            <v>1664</v>
           </cell>
         </row>
         <row r="607">
           <cell r="A607">
-            <v>1965</v>
+            <v>1665</v>
           </cell>
         </row>
         <row r="608">
           <cell r="A608">
-            <v>1966</v>
+            <v>1666</v>
           </cell>
         </row>
         <row r="609">
           <cell r="A609">
-            <v>1967</v>
+            <v>1667</v>
           </cell>
         </row>
         <row r="610">
           <cell r="A610">
-            <v>1968</v>
+            <v>1668</v>
           </cell>
         </row>
         <row r="611">
           <cell r="A611">
-            <v>1969</v>
+            <v>1669</v>
           </cell>
         </row>
         <row r="612">
           <cell r="A612">
-            <v>1970</v>
+            <v>1670</v>
           </cell>
         </row>
         <row r="613">
           <cell r="A613">
-            <v>1971</v>
+            <v>1671</v>
           </cell>
         </row>
         <row r="614">
           <cell r="A614">
-            <v>1972</v>
+            <v>1672</v>
           </cell>
         </row>
         <row r="615">
           <cell r="A615">
-            <v>1973</v>
+            <v>1673</v>
           </cell>
         </row>
         <row r="616">
           <cell r="A616">
-            <v>1974</v>
+            <v>1674</v>
           </cell>
         </row>
         <row r="617">
           <cell r="A617">
-            <v>1975</v>
+            <v>1675</v>
           </cell>
         </row>
         <row r="618">
           <cell r="A618">
-            <v>1976</v>
+            <v>1676</v>
           </cell>
         </row>
         <row r="619">
           <cell r="A619">
-            <v>1977</v>
+            <v>1677</v>
           </cell>
         </row>
         <row r="620">
           <cell r="A620">
-            <v>1978</v>
+            <v>1678</v>
           </cell>
         </row>
         <row r="621">
           <cell r="A621">
-            <v>1979</v>
+            <v>1679</v>
           </cell>
         </row>
         <row r="622">
           <cell r="A622">
-            <v>1980</v>
+            <v>1680</v>
           </cell>
         </row>
         <row r="623">
           <cell r="A623">
-            <v>1981</v>
+            <v>1681</v>
           </cell>
         </row>
         <row r="624">
           <cell r="A624">
-            <v>1982</v>
+            <v>1682</v>
           </cell>
         </row>
         <row r="625">
           <cell r="A625">
-            <v>1983</v>
+            <v>1683</v>
           </cell>
         </row>
         <row r="626">
           <cell r="A626">
-            <v>1984</v>
+            <v>1684</v>
           </cell>
         </row>
         <row r="627">
           <cell r="A627">
-            <v>1985</v>
+            <v>1685</v>
           </cell>
         </row>
         <row r="628">
           <cell r="A628">
-            <v>1986</v>
+            <v>1686</v>
           </cell>
         </row>
         <row r="629">
           <cell r="A629">
-            <v>1987</v>
+            <v>1687</v>
           </cell>
         </row>
         <row r="630">
           <cell r="A630">
-            <v>1988</v>
+            <v>1688</v>
           </cell>
         </row>
         <row r="631">
           <cell r="A631">
-            <v>1989</v>
+            <v>1689</v>
           </cell>
         </row>
         <row r="632">
           <cell r="A632">
-            <v>1990</v>
+            <v>1690</v>
           </cell>
         </row>
         <row r="633">
           <cell r="A633">
-            <v>1991</v>
+            <v>1691</v>
           </cell>
         </row>
         <row r="634">
           <cell r="A634">
-            <v>1992</v>
+            <v>1692</v>
           </cell>
         </row>
         <row r="635">
           <cell r="A635">
-            <v>1993</v>
+            <v>1693</v>
           </cell>
         </row>
         <row r="636">
           <cell r="A636">
-            <v>1994</v>
+            <v>1694</v>
           </cell>
         </row>
         <row r="637">
           <cell r="A637">
-            <v>1995</v>
+            <v>1695</v>
           </cell>
         </row>
         <row r="638">
           <cell r="A638">
-            <v>1996</v>
+            <v>1696</v>
           </cell>
         </row>
         <row r="639">
           <cell r="A639">
-            <v>1997</v>
+            <v>1697</v>
           </cell>
         </row>
         <row r="640">
           <cell r="A640">
-            <v>1998</v>
+            <v>1698</v>
           </cell>
         </row>
         <row r="641">
           <cell r="A641">
-            <v>1999</v>
+            <v>1699</v>
           </cell>
         </row>
         <row r="642">
           <cell r="A642">
-            <v>2000</v>
+            <v>1700</v>
           </cell>
         </row>
         <row r="643">
           <cell r="A643">
-            <v>2001</v>
+            <v>1701</v>
           </cell>
         </row>
         <row r="644">
           <cell r="A644">
-            <v>2002</v>
+            <v>1702</v>
           </cell>
         </row>
         <row r="645">
           <cell r="A645">
-            <v>2003</v>
+            <v>1703</v>
           </cell>
         </row>
         <row r="646">
           <cell r="A646">
-            <v>2004</v>
+            <v>1704</v>
           </cell>
         </row>
         <row r="647">
           <cell r="A647">
-            <v>2005</v>
+            <v>1705</v>
           </cell>
         </row>
         <row r="648">
           <cell r="A648">
-            <v>2006</v>
+            <v>1706</v>
           </cell>
         </row>
         <row r="649">
           <cell r="A649">
-            <v>2007</v>
+            <v>1707</v>
           </cell>
         </row>
         <row r="650">
           <cell r="A650">
-            <v>2008</v>
+            <v>1708</v>
           </cell>
         </row>
         <row r="651">
           <cell r="A651">
-            <v>2009</v>
+            <v>1709</v>
           </cell>
         </row>
         <row r="652">
           <cell r="A652">
-            <v>2010</v>
+            <v>1710</v>
           </cell>
         </row>
         <row r="653">
           <cell r="A653">
-            <v>2011</v>
+            <v>1711</v>
           </cell>
         </row>
         <row r="654">
           <cell r="A654">
-            <v>2012</v>
+            <v>1712</v>
           </cell>
         </row>
         <row r="655">
           <cell r="A655">
-            <v>2013</v>
+            <v>1713</v>
           </cell>
         </row>
         <row r="656">
           <cell r="A656">
-            <v>2014</v>
+            <v>1714</v>
           </cell>
         </row>
         <row r="657">
           <cell r="A657">
-            <v>2015</v>
+            <v>1715</v>
           </cell>
         </row>
         <row r="658">
           <cell r="A658">
-            <v>2016</v>
+            <v>1716</v>
           </cell>
         </row>
         <row r="659">
           <cell r="A659">
-            <v>2017</v>
+            <v>1717</v>
           </cell>
         </row>
         <row r="660">
           <cell r="A660">
-            <v>2018</v>
+            <v>1718</v>
           </cell>
         </row>
         <row r="661">
           <cell r="A661">
-            <v>2019</v>
+            <v>1719</v>
           </cell>
         </row>
         <row r="662">
           <cell r="A662">
-            <v>2020</v>
+            <v>1720</v>
           </cell>
         </row>
         <row r="663">
           <cell r="A663">
-            <v>2021</v>
+            <v>1721</v>
           </cell>
         </row>
         <row r="664">
           <cell r="A664">
-            <v>2022</v>
+            <v>1722</v>
           </cell>
         </row>
         <row r="665">
           <cell r="A665">
-            <v>2023</v>
+            <v>1723</v>
           </cell>
         </row>
         <row r="666">
           <cell r="A666">
-            <v>2024</v>
+            <v>1724</v>
           </cell>
         </row>
         <row r="667">
           <cell r="A667">
-            <v>2025</v>
+            <v>1725</v>
           </cell>
         </row>
         <row r="668">
           <cell r="A668">
-            <v>2026</v>
+            <v>1726</v>
           </cell>
         </row>
         <row r="669">
           <cell r="A669">
-            <v>2027</v>
+            <v>1727</v>
           </cell>
         </row>
         <row r="670">
           <cell r="A670">
-            <v>2028</v>
+            <v>1728</v>
           </cell>
         </row>
         <row r="671">
           <cell r="A671">
-            <v>2029</v>
+            <v>1729</v>
           </cell>
         </row>
         <row r="672">
           <cell r="A672">
-            <v>2030</v>
+            <v>1730</v>
           </cell>
         </row>
         <row r="673">
           <cell r="A673">
-            <v>2031</v>
+            <v>1731</v>
           </cell>
         </row>
         <row r="674">
           <cell r="A674">
-            <v>2032</v>
+            <v>1732</v>
           </cell>
         </row>
         <row r="675">
           <cell r="A675">
-            <v>2033</v>
+            <v>1733</v>
           </cell>
         </row>
         <row r="676">
           <cell r="A676">
-            <v>2034</v>
+            <v>1734</v>
           </cell>
         </row>
         <row r="677">
           <cell r="A677">
-            <v>2035</v>
+            <v>1735</v>
           </cell>
         </row>
         <row r="678">
           <cell r="A678">
-            <v>2036</v>
+            <v>1736</v>
           </cell>
         </row>
         <row r="679">
           <cell r="A679">
-            <v>2037</v>
+            <v>1737</v>
           </cell>
         </row>
         <row r="680">
           <cell r="A680">
-            <v>2038</v>
+            <v>1738</v>
           </cell>
         </row>
         <row r="681">
           <cell r="A681">
-            <v>2039</v>
+            <v>1739</v>
           </cell>
         </row>
         <row r="682">
           <cell r="A682">
-            <v>2040</v>
+            <v>1740</v>
           </cell>
         </row>
         <row r="683">
           <cell r="A683">
-            <v>2041</v>
+            <v>1741</v>
           </cell>
         </row>
         <row r="684">
           <cell r="A684">
-            <v>2042</v>
+            <v>1742</v>
           </cell>
         </row>
         <row r="685">
           <cell r="A685">
-            <v>2043</v>
+            <v>1743</v>
           </cell>
         </row>
         <row r="686">
           <cell r="A686">
-            <v>2044</v>
+            <v>1744</v>
           </cell>
         </row>
         <row r="687">
           <cell r="A687">
-            <v>2045</v>
+            <v>1745</v>
           </cell>
         </row>
         <row r="688">
           <cell r="A688">
-            <v>2046</v>
+            <v>1746</v>
           </cell>
         </row>
         <row r="689">
           <cell r="A689">
-            <v>2047</v>
+            <v>1747</v>
           </cell>
         </row>
         <row r="690">
           <cell r="A690">
-            <v>2048</v>
+            <v>1748</v>
           </cell>
         </row>
         <row r="691">
           <cell r="A691">
-            <v>2049</v>
+            <v>1749</v>
           </cell>
         </row>
         <row r="692">
           <cell r="A692">
-            <v>2050</v>
+            <v>1750</v>
           </cell>
         </row>
         <row r="693">
           <cell r="A693">
-            <v>2051</v>
+            <v>1751</v>
           </cell>
         </row>
         <row r="694">
           <cell r="A694">
-            <v>2052</v>
+            <v>1752</v>
           </cell>
         </row>
         <row r="695">
           <cell r="A695">
-            <v>2053</v>
+            <v>1753</v>
           </cell>
         </row>
         <row r="696">
           <cell r="A696">
-            <v>2054</v>
+            <v>1754</v>
           </cell>
         </row>
         <row r="697">
           <cell r="A697">
-            <v>2055</v>
+            <v>1755</v>
           </cell>
         </row>
         <row r="698">
           <cell r="A698">
-            <v>2056</v>
+            <v>1756</v>
           </cell>
         </row>
         <row r="699">
           <cell r="A699">
-            <v>2057</v>
+            <v>1757</v>
           </cell>
         </row>
         <row r="700">
           <cell r="A700">
-            <v>2058</v>
+            <v>1758</v>
           </cell>
         </row>
         <row r="701">
           <cell r="A701">
-            <v>2059</v>
+            <v>1759</v>
           </cell>
         </row>
         <row r="702">
           <cell r="A702">
-            <v>2060</v>
+            <v>1760</v>
           </cell>
         </row>
         <row r="703">
           <cell r="A703">
-            <v>2061</v>
+            <v>1761</v>
           </cell>
         </row>
         <row r="704">
           <cell r="A704">
-            <v>2062</v>
+            <v>1762</v>
           </cell>
         </row>
         <row r="705">
           <cell r="A705">
-            <v>2063</v>
+            <v>1763</v>
           </cell>
         </row>
         <row r="706">
           <cell r="A706">
-            <v>2064</v>
+            <v>1764</v>
           </cell>
         </row>
         <row r="707">
           <cell r="A707">
-            <v>2065</v>
+            <v>1765</v>
           </cell>
         </row>
         <row r="708">
           <cell r="A708">
-            <v>2066</v>
+            <v>1766</v>
           </cell>
         </row>
         <row r="709">
           <cell r="A709">
-            <v>2067</v>
+            <v>1767</v>
           </cell>
         </row>
         <row r="710">
           <cell r="A710">
-            <v>2068</v>
+            <v>1768</v>
           </cell>
         </row>
         <row r="711">
           <cell r="A711">
-            <v>2069</v>
+            <v>1769</v>
           </cell>
         </row>
         <row r="712">
           <cell r="A712">
-            <v>2070</v>
+            <v>1770</v>
           </cell>
         </row>
         <row r="713">
           <cell r="A713">
-            <v>2071</v>
+            <v>1771</v>
           </cell>
         </row>
         <row r="714">
           <cell r="A714">
-            <v>2072</v>
+            <v>1772</v>
           </cell>
         </row>
         <row r="715">
           <cell r="A715">
-            <v>2073</v>
+            <v>1773</v>
           </cell>
         </row>
         <row r="716">
           <cell r="A716">
-            <v>2074</v>
+            <v>1774</v>
           </cell>
         </row>
         <row r="717">
           <cell r="A717">
-            <v>2075</v>
+            <v>1775</v>
           </cell>
         </row>
         <row r="718">
           <cell r="A718">
-            <v>2076</v>
+            <v>1776</v>
           </cell>
         </row>
         <row r="719">
           <cell r="A719">
-            <v>2077</v>
+            <v>1777</v>
           </cell>
         </row>
         <row r="720">
           <cell r="A720">
-            <v>2078</v>
+            <v>1778</v>
           </cell>
         </row>
         <row r="721">
           <cell r="A721">
-            <v>2079</v>
+            <v>1779</v>
           </cell>
         </row>
         <row r="722">
           <cell r="A722">
-            <v>2080</v>
+            <v>1780</v>
           </cell>
         </row>
         <row r="723">
           <cell r="A723">
-            <v>2081</v>
+            <v>1781</v>
           </cell>
         </row>
         <row r="724">
           <cell r="A724">
-            <v>2082</v>
+            <v>1782</v>
           </cell>
         </row>
         <row r="725">
           <cell r="A725">
-            <v>2083</v>
+            <v>1783</v>
           </cell>
         </row>
         <row r="726">
           <cell r="A726">
-            <v>2084</v>
+            <v>1784</v>
           </cell>
         </row>
         <row r="727">
           <cell r="A727">
-            <v>2085</v>
+            <v>1785</v>
           </cell>
         </row>
         <row r="728">
           <cell r="A728">
-            <v>2086</v>
+            <v>1786</v>
           </cell>
         </row>
         <row r="729">
           <cell r="A729">
-            <v>2087</v>
+            <v>1787</v>
           </cell>
         </row>
         <row r="730">
           <cell r="A730">
-            <v>2088</v>
+            <v>1788</v>
           </cell>
         </row>
         <row r="731">
           <cell r="A731">
-            <v>2089</v>
+            <v>1789</v>
           </cell>
         </row>
         <row r="732">
           <cell r="A732">
-            <v>2090</v>
+            <v>1790</v>
           </cell>
         </row>
         <row r="733">
           <cell r="A733">
-            <v>2091</v>
+            <v>1791</v>
           </cell>
         </row>
         <row r="734">
           <cell r="A734">
-            <v>2092</v>
+            <v>1792</v>
           </cell>
         </row>
         <row r="735">
           <cell r="A735">
-            <v>2093</v>
+            <v>1793</v>
           </cell>
         </row>
         <row r="736">
           <cell r="A736">
-            <v>2094</v>
+            <v>1794</v>
           </cell>
         </row>
         <row r="737">
           <cell r="A737">
-            <v>2095</v>
+            <v>1795</v>
           </cell>
         </row>
         <row r="738">
           <cell r="A738">
-            <v>2096</v>
+            <v>1796</v>
           </cell>
         </row>
         <row r="739">
           <cell r="A739">
-            <v>2097</v>
+            <v>1797</v>
           </cell>
         </row>
         <row r="740">
           <cell r="A740">
-            <v>2098</v>
+            <v>1798</v>
           </cell>
         </row>
         <row r="741">
           <cell r="A741">
-            <v>2099</v>
+            <v>1799</v>
           </cell>
         </row>
         <row r="742">
           <cell r="A742">
-            <v>2100</v>
+            <v>1800</v>
           </cell>
         </row>
         <row r="743">
           <cell r="A743">
-            <v>2101</v>
+            <v>1801</v>
           </cell>
         </row>
         <row r="744">
           <cell r="A744">
-            <v>2102</v>
+            <v>1802</v>
           </cell>
         </row>
         <row r="745">
           <cell r="A745">
-            <v>2103</v>
+            <v>1803</v>
           </cell>
         </row>
         <row r="746">
           <cell r="A746">
-            <v>2104</v>
+            <v>1804</v>
           </cell>
         </row>
         <row r="747">
           <cell r="A747">
-            <v>2105</v>
+            <v>1805</v>
           </cell>
         </row>
         <row r="748">
           <cell r="A748">
-            <v>2106</v>
+            <v>1806</v>
           </cell>
         </row>
         <row r="749">
           <cell r="A749">
-            <v>2107</v>
+            <v>1807</v>
           </cell>
         </row>
         <row r="750">
           <cell r="A750">
-            <v>2108</v>
+            <v>1808</v>
           </cell>
         </row>
         <row r="751">
           <cell r="A751">
-            <v>2109</v>
+            <v>1809</v>
           </cell>
         </row>
         <row r="752">
           <cell r="A752">
-            <v>2110</v>
+            <v>1810</v>
           </cell>
         </row>
         <row r="753">
           <cell r="A753">
-            <v>2111</v>
+            <v>1811</v>
           </cell>
         </row>
         <row r="754">
           <cell r="A754">
-            <v>2112</v>
+            <v>1812</v>
           </cell>
         </row>
         <row r="755">
           <cell r="A755">
-            <v>2113</v>
+            <v>1813</v>
           </cell>
         </row>
         <row r="756">
           <cell r="A756">
-            <v>2114</v>
+            <v>1814</v>
           </cell>
         </row>
         <row r="757">
           <cell r="A757">
-            <v>2115</v>
+            <v>1815</v>
           </cell>
         </row>
         <row r="758">
           <cell r="A758">
-            <v>2116</v>
+            <v>1816</v>
           </cell>
         </row>
         <row r="759">
           <cell r="A759">
-            <v>2117</v>
+            <v>1817</v>
           </cell>
         </row>
         <row r="760">
           <cell r="A760">
-            <v>2118</v>
+            <v>1818</v>
           </cell>
         </row>
         <row r="761">
           <cell r="A761">
-            <v>2119</v>
+            <v>1819</v>
           </cell>
         </row>
         <row r="762">
           <cell r="A762">
-            <v>2120</v>
+            <v>1820</v>
           </cell>
         </row>
         <row r="763">
           <cell r="A763">
-            <v>2121</v>
+            <v>1821</v>
           </cell>
         </row>
         <row r="764">
           <cell r="A764">
-            <v>2122</v>
+            <v>1822</v>
           </cell>
         </row>
         <row r="765">
           <cell r="A765">
-            <v>2123</v>
+            <v>1823</v>
           </cell>
         </row>
         <row r="766">
           <cell r="A766">
-            <v>2124</v>
+            <v>1824</v>
           </cell>
         </row>
         <row r="767">
           <cell r="A767">
-            <v>2125</v>
+            <v>1825</v>
           </cell>
         </row>
         <row r="768">
           <cell r="A768">
-            <v>2126</v>
+            <v>1826</v>
           </cell>
         </row>
         <row r="769">
           <cell r="A769">
-            <v>2127</v>
+            <v>1827</v>
           </cell>
         </row>
         <row r="770">
           <cell r="A770">
-            <v>2128</v>
+            <v>1828</v>
           </cell>
         </row>
         <row r="771">
           <cell r="A771">
-            <v>2129</v>
+            <v>1829</v>
           </cell>
         </row>
         <row r="772">
           <cell r="A772">
-            <v>2130</v>
+            <v>1830</v>
           </cell>
         </row>
         <row r="773">
           <cell r="A773">
-            <v>2131</v>
+            <v>1831</v>
           </cell>
         </row>
         <row r="774">
           <cell r="A774">
-            <v>2132</v>
+            <v>1832</v>
           </cell>
         </row>
         <row r="775">
           <cell r="A775">
-            <v>2133</v>
+            <v>1833</v>
           </cell>
         </row>
         <row r="776">
           <cell r="A776">
-            <v>2134</v>
+            <v>1834</v>
           </cell>
         </row>
         <row r="777">
           <cell r="A777">
-            <v>2135</v>
+            <v>1835</v>
           </cell>
         </row>
         <row r="778">
           <cell r="A778">
-            <v>2136</v>
+            <v>1836</v>
           </cell>
         </row>
         <row r="779">
           <cell r="A779">
-            <v>2137</v>
+            <v>1837</v>
           </cell>
         </row>
         <row r="780">
           <cell r="A780">
-            <v>2138</v>
+            <v>1838</v>
           </cell>
         </row>
         <row r="781">
           <cell r="A781">
-            <v>2139</v>
+            <v>1839</v>
           </cell>
         </row>
         <row r="782">
           <cell r="A782">
-            <v>2140</v>
+            <v>1840</v>
           </cell>
         </row>
         <row r="783">
           <cell r="A783">
-            <v>2141</v>
+            <v>1841</v>
           </cell>
         </row>
         <row r="784">
           <cell r="A784">
-            <v>2142</v>
+            <v>1842</v>
           </cell>
         </row>
         <row r="785">
           <cell r="A785">
-            <v>2143</v>
+            <v>1843</v>
           </cell>
         </row>
         <row r="786">
           <cell r="A786">
-            <v>2144</v>
+            <v>1844</v>
           </cell>
         </row>
         <row r="787">
           <cell r="A787">
-            <v>2145</v>
+            <v>1845</v>
           </cell>
         </row>
         <row r="788">
           <cell r="A788">
-            <v>2146</v>
+            <v>1846</v>
           </cell>
         </row>
         <row r="789">
           <cell r="A789">
-            <v>2147</v>
+            <v>1847</v>
           </cell>
         </row>
         <row r="790">
           <cell r="A790">
-            <v>2148</v>
+            <v>1848</v>
           </cell>
         </row>
         <row r="791">
           <cell r="A791">
-            <v>2149</v>
+            <v>1849</v>
           </cell>
         </row>
         <row r="792">
           <cell r="A792">
-            <v>2150</v>
+            <v>1850</v>
           </cell>
         </row>
         <row r="793">
           <cell r="A793">
-            <v>2151</v>
+            <v>1851</v>
           </cell>
         </row>
         <row r="794">
           <cell r="A794">
-            <v>2152</v>
+            <v>1852</v>
           </cell>
         </row>
         <row r="795">
           <cell r="A795">
-            <v>2153</v>
+            <v>1853</v>
           </cell>
         </row>
         <row r="796">
           <cell r="A796">
-            <v>2154</v>
+            <v>1854</v>
           </cell>
         </row>
         <row r="797">
           <cell r="A797">
-            <v>2155</v>
+            <v>1855</v>
           </cell>
         </row>
         <row r="798">
           <cell r="A798">
-            <v>2156</v>
+            <v>1856</v>
           </cell>
         </row>
         <row r="799">
           <cell r="A799">
-            <v>2157</v>
+            <v>1857</v>
           </cell>
         </row>
         <row r="800">
           <cell r="A800">
-            <v>2158</v>
+            <v>1858</v>
           </cell>
         </row>
         <row r="801">
           <cell r="A801">
-            <v>2159</v>
+            <v>1859</v>
           </cell>
         </row>
         <row r="802">
           <cell r="A802">
-            <v>2160</v>
+            <v>1860</v>
           </cell>
         </row>
         <row r="803">
           <cell r="A803">
-            <v>2161</v>
+            <v>1861</v>
           </cell>
         </row>
         <row r="804">
           <cell r="A804">
-            <v>2162</v>
+            <v>1862</v>
           </cell>
         </row>
         <row r="805">
           <cell r="A805">
-            <v>2163</v>
+            <v>1863</v>
           </cell>
         </row>
         <row r="806">
           <cell r="A806">
-            <v>2164</v>
+            <v>1864</v>
           </cell>
         </row>
         <row r="807">
           <cell r="A807">
-            <v>2165</v>
+            <v>1865</v>
           </cell>
         </row>
         <row r="808">
           <cell r="A808">
-            <v>2166</v>
+            <v>1866</v>
           </cell>
         </row>
         <row r="809">
           <cell r="A809">
-            <v>2167</v>
+            <v>1867</v>
           </cell>
         </row>
         <row r="810">
           <cell r="A810">
-            <v>2168</v>
+            <v>1868</v>
           </cell>
         </row>
         <row r="811">
           <cell r="A811">
-            <v>2169</v>
+            <v>1869</v>
           </cell>
         </row>
         <row r="812">
           <cell r="A812">
-            <v>2170</v>
+            <v>1870</v>
           </cell>
         </row>
         <row r="813">
           <cell r="A813">
-            <v>2171</v>
+            <v>1871</v>
           </cell>
         </row>
         <row r="814">
           <cell r="A814">
-            <v>2172</v>
+            <v>1872</v>
           </cell>
         </row>
         <row r="815">
           <cell r="A815">
-            <v>2173</v>
+            <v>1873</v>
           </cell>
         </row>
         <row r="816">
           <cell r="A816">
-            <v>2174</v>
+            <v>1874</v>
           </cell>
         </row>
         <row r="817">
           <cell r="A817">
-            <v>2175</v>
+            <v>1875</v>
           </cell>
         </row>
         <row r="818">
           <cell r="A818">
-            <v>2176</v>
+            <v>1876</v>
           </cell>
         </row>
         <row r="819">
           <cell r="A819">
-            <v>2177</v>
+            <v>1877</v>
           </cell>
         </row>
         <row r="820">
           <cell r="A820">
-            <v>2178</v>
+            <v>1878</v>
           </cell>
         </row>
         <row r="821">
           <cell r="A821">
-            <v>2179</v>
+            <v>1879</v>
           </cell>
         </row>
         <row r="822">
           <cell r="A822">
-            <v>2180</v>
+            <v>1880</v>
           </cell>
         </row>
         <row r="823">
           <cell r="A823">
-            <v>2181</v>
+            <v>1881</v>
           </cell>
         </row>
         <row r="824">
           <cell r="A824">
-            <v>2182</v>
+            <v>1882</v>
           </cell>
         </row>
         <row r="825">
           <cell r="A825">
-            <v>2183</v>
+            <v>1883</v>
           </cell>
         </row>
         <row r="826">
           <cell r="A826">
-            <v>2184</v>
+            <v>1884</v>
           </cell>
         </row>
         <row r="827">
           <cell r="A827">
-            <v>2185</v>
+            <v>1885</v>
           </cell>
         </row>
         <row r="828">
           <cell r="A828">
-            <v>2186</v>
+            <v>1886</v>
           </cell>
         </row>
         <row r="829">
           <cell r="A829">
-            <v>2187</v>
+            <v>1887</v>
           </cell>
         </row>
         <row r="830">
           <cell r="A830">
-            <v>2188</v>
+            <v>1888</v>
           </cell>
         </row>
         <row r="831">
           <cell r="A831">
-            <v>2189</v>
+            <v>1889</v>
           </cell>
         </row>
       </sheetData>
@@ -8766,21 +8760,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="22.4017094017094" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.4017094017094" style="3"/>
-    <col min="2" max="2" width="33.7948717948718" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="22.4017094017094" style="3"/>
+    <col min="1" max="1" width="22.4047619047619" style="3"/>
+    <col min="2" max="2" width="33.7936507936508" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="22.4047619047619" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
@@ -8940,24 +8934,24 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.9316239316239" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.9285714285714" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.3333333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.0940170940171" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.0952380952381" style="3" customWidth="1"/>
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" spans="1:5">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="7" customFormat="1" spans="1:5">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="3"/>
@@ -9101,69 +9095,69 @@
   <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6.46153846153846" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.5982905982906" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.4615384615385" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.8034188034188" style="3" customWidth="1"/>
-    <col min="5" max="5" width="44.5299145299145" style="3" customWidth="1"/>
-    <col min="6" max="7" width="12.1965811965812" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.6068376068376" style="3" customWidth="1"/>
-    <col min="9" max="10" width="12.1965811965812" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.5952380952381" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.4603174603175" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.8015873015873" style="3" customWidth="1"/>
+    <col min="5" max="5" width="44.531746031746" style="3" customWidth="1"/>
+    <col min="6" max="7" width="12.1984126984127" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.6031746031746" style="3" customWidth="1"/>
+    <col min="9" max="10" width="12.1984126984127" style="3" customWidth="1"/>
     <col min="11" max="11" width="16.6666666666667" style="3" customWidth="1"/>
-    <col min="12" max="16" width="12.1965811965812" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.06837606837607" style="3"/>
+    <col min="12" max="16" width="12.1984126984127" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9.07142857142857" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" spans="1:17">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="7" customFormat="1" spans="1:17">
+      <c r="A1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="7" t="s">
         <v>41</v>
       </c>
     </row>
@@ -9438,7 +9432,7 @@
       <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -9467,12 +9461,12 @@
   <dimension ref="A1:G100"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.7606837606838" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.0940170940171" style="2" customWidth="1"/>
-    <col min="3" max="3" width="212.162393162393" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.3931623931624" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.2905982905983" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.4358974358974" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.7619047619048" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.0952380952381" style="2" customWidth="1"/>
+    <col min="3" max="3" width="212.15873015873" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.3968253968254" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.2936507936508" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.4365079365079" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
@@ -9545,7 +9539,7 @@
       <c r="B5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D5" s="4">
@@ -9556,10 +9550,10 @@
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D6" s="4">
@@ -9570,10 +9564,10 @@
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D7" s="4">
@@ -9587,7 +9581,7 @@
       <c r="B8" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D8" s="4">
@@ -9598,10 +9592,10 @@
       <c r="A9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="4">
@@ -9612,10 +9606,10 @@
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D10" s="4">
@@ -9629,7 +9623,7 @@
       <c r="B11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D11" s="4">
@@ -9640,10 +9634,10 @@
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D12" s="4">
@@ -9654,10 +9648,10 @@
       <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="4">
@@ -9755,7 +9749,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -9769,7 +9763,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -9783,7 +9777,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -9797,7 +9791,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -9811,7 +9805,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -9825,7 +9819,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -9929,7 +9923,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -9943,7 +9937,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -9957,7 +9951,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -9971,7 +9965,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -9985,7 +9979,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -9999,7 +9993,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -10103,7 +10097,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -10117,7 +10111,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -10131,7 +10125,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -10145,7 +10139,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -10159,7 +10153,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -10173,7 +10167,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -10193,7 +10187,7 @@
       <c r="B50" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="6">
         <v>500506</v>
       </c>
       <c r="D50" s="4">
@@ -10207,7 +10201,7 @@
       <c r="B51" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="6">
         <v>501507</v>
       </c>
       <c r="D51" s="4">
@@ -10221,7 +10215,7 @@
       <c r="B52" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="6">
         <v>502508</v>
       </c>
       <c r="D52" s="4">
@@ -10235,7 +10229,7 @@
       <c r="B53" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="6">
         <v>503509</v>
       </c>
       <c r="D53" s="4">
@@ -10249,7 +10243,7 @@
       <c r="B54" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="6">
         <v>504510</v>
       </c>
       <c r="D54" s="4">
@@ -10263,7 +10257,7 @@
       <c r="B55" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="6">
         <v>505511</v>
       </c>
       <c r="D55" s="4">
@@ -10277,7 +10271,7 @@
       <c r="B56" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="6">
         <v>500506</v>
       </c>
       <c r="D56" s="4">
@@ -10291,7 +10285,7 @@
       <c r="B57" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="6">
         <v>501507</v>
       </c>
       <c r="D57" s="4">
@@ -10305,7 +10299,7 @@
       <c r="B58" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="6">
         <v>502508</v>
       </c>
       <c r="D58" s="4">
@@ -10319,7 +10313,7 @@
       <c r="B59" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="6">
         <v>503509</v>
       </c>
       <c r="D59" s="4">
@@ -10333,7 +10327,7 @@
       <c r="B60" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="6">
         <v>504510</v>
       </c>
       <c r="D60" s="4">
@@ -10347,7 +10341,7 @@
       <c r="B61" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="6">
         <v>505511</v>
       </c>
       <c r="D61" s="4">
@@ -10361,7 +10355,7 @@
       <c r="B62" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="6">
         <v>500506</v>
       </c>
       <c r="D62" s="4">
@@ -10375,7 +10369,7 @@
       <c r="B63" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C63" s="8">
+      <c r="C63" s="6">
         <v>501507</v>
       </c>
       <c r="D63" s="4">
@@ -10389,7 +10383,7 @@
       <c r="B64" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="6">
         <v>502508</v>
       </c>
       <c r="D64" s="4">
@@ -10403,7 +10397,7 @@
       <c r="B65" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="6">
         <v>503509</v>
       </c>
       <c r="D65" s="4">
@@ -10417,7 +10411,7 @@
       <c r="B66" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="6">
         <v>504510</v>
       </c>
       <c r="D66" s="4">
@@ -10431,7 +10425,7 @@
       <c r="B67" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="6">
         <v>505511</v>
       </c>
       <c r="D67" s="4">
@@ -10445,7 +10439,7 @@
       <c r="B68" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="6">
         <v>500506</v>
       </c>
       <c r="D68" s="4">
@@ -10459,7 +10453,7 @@
       <c r="B69" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="6">
         <v>501507</v>
       </c>
       <c r="D69" s="4">
@@ -10473,7 +10467,7 @@
       <c r="B70" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="6">
         <v>502508</v>
       </c>
       <c r="D70" s="4">
@@ -10487,7 +10481,7 @@
       <c r="B71" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="6">
         <v>503509</v>
       </c>
       <c r="D71" s="4">
@@ -10501,7 +10495,7 @@
       <c r="B72" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="6">
         <v>504510</v>
       </c>
       <c r="D72" s="4">
@@ -10515,7 +10509,7 @@
       <c r="B73" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C73" s="8">
+      <c r="C73" s="6">
         <v>505511</v>
       </c>
       <c r="D73" s="4">
@@ -10531,14 +10525,14 @@
       </c>
       <c r="C74" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
-        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+        <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
       <c r="D74" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B75" s="4" t="s">
@@ -10546,14 +10540,14 @@
       </c>
       <c r="C75" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
-        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+        <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
       <c r="D75" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B76" s="4" t="s">
@@ -10561,14 +10555,14 @@
       </c>
       <c r="C76" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
-        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+        <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
       <c r="D76" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B77" s="4" t="s">
@@ -10576,14 +10570,14 @@
       </c>
       <c r="C77" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
-        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+        <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
       <c r="D77" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B78" s="4" t="s">
@@ -10591,14 +10585,14 @@
       </c>
       <c r="C78" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
-        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+        <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
       <c r="D78" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B79" s="4" t="s">
@@ -10606,7 +10600,7 @@
       </c>
       <c r="C79" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
-        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+        <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
       <c r="D79" s="4">
         <v>1</v>
@@ -10621,7 +10615,7 @@
       </c>
       <c r="C80" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
-        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+        <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
       <c r="D80" s="4">
         <v>1</v>
@@ -10636,7 +10630,7 @@
       </c>
       <c r="C81" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
-        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+        <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
       <c r="D81" s="4">
         <v>1</v>
@@ -10651,7 +10645,7 @@
       </c>
       <c r="C82" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
-        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+        <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
       <c r="D82" s="4">
         <v>1</v>
@@ -10666,7 +10660,7 @@
       </c>
       <c r="C83" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
-        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+        <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
       <c r="D83" s="4">
         <v>1</v>
@@ -10681,7 +10675,7 @@
       </c>
       <c r="C84" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
-        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+        <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
       <c r="D84" s="4">
         <v>1</v>
@@ -10696,7 +10690,7 @@
       </c>
       <c r="C85" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
-        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+        <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
       <c r="D85" s="4">
         <v>1</v>
@@ -10711,7 +10705,7 @@
       </c>
       <c r="C86" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
-        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+        <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
       <c r="D86" s="4">
         <v>1</v>
@@ -10726,7 +10720,7 @@
       </c>
       <c r="C87" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
-        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+        <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
       <c r="D87" s="4">
         <v>1</v>
@@ -10741,7 +10735,7 @@
       </c>
       <c r="C88" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
-        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+        <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
       <c r="D88" s="4">
         <v>1</v>
@@ -10756,7 +10750,7 @@
       </c>
       <c r="C89" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
-        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+        <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
       <c r="D89" s="4">
         <v>1</v>
@@ -10771,7 +10765,7 @@
       </c>
       <c r="C90" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
-        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+        <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
       <c r="D90" s="4">
         <v>1</v>
@@ -10786,7 +10780,7 @@
       </c>
       <c r="C91" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
-        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+        <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
       <c r="D91" s="4">
         <v>1</v>
@@ -10801,7 +10795,7 @@
       </c>
       <c r="C92" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
-        <v>1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544,1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614</v>
+        <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
       <c r="D92" s="4">
         <v>1</v>
@@ -10816,7 +10810,7 @@
       </c>
       <c r="C93" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
-        <v>1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659,1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729</v>
+        <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
       <c r="D93" s="4">
         <v>1</v>
@@ -10831,7 +10825,7 @@
       </c>
       <c r="C94" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
-        <v>1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774,1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844</v>
+        <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
       <c r="D94" s="4">
         <v>1</v>
@@ -10846,7 +10840,7 @@
       </c>
       <c r="C95" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
-        <v>1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889,1890,1891,1892,1893,1894,1895,1896,1897,1898,1899,1900,1901,1902,1903,1904,1905,1906,1907,1908,1909,1910,1911,1912,1913,1914,1915,1916,1917,1918,1919,1920,1921,1922,1923,1924,1925,1926,1927,1928,1929,1930,1931,1932,1933,1934,1935,1936,1937,1938,1939,1940,1941,1942,1943,1944,1945,1946,1947,1948,1949,1950,1951,1952,1953,1954,1955,1956,1957,1958,1959</v>
+        <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
       <c r="D95" s="4">
         <v>1</v>
@@ -10861,7 +10855,7 @@
       </c>
       <c r="C96" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
-        <v>1960,1961,1962,1963,1964,1965,1966,1967,1968,1969,1970,1971,1972,1973,1974,1975,1976,1977,1978,1979,1980,1981,1982,1983,1984,1985,1986,1987,1988,1989,1990,1991,1992,1993,1994,1995,1996,1997,1998,1999,2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045,2046,2047,2048,2049,2050,2051,2052,2053,2054,2055,2056,2057,2058,2059,2060,2061,2062,2063,2064,2065,2066,2067,2068,2069,2070,2071,2072,2073,2074</v>
+        <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
       <c r="D96" s="4">
         <v>1</v>
@@ -10876,7 +10870,7 @@
       </c>
       <c r="C97" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
-        <v>2075,2076,2077,2078,2079,2080,2081,2082,2083,2084,2085,2086,2087,2088,2089,2090,2091,2092,2093,2094,2095,2096,2097,2098,2099,2100,2101,2102,2103,2104,2105,2106,2107,2108,2109,2110,2111,2112,2113,2114,2115,2116,2117,2118,2119,2120,2121,2122,2123,2124,2125,2126,2127,2128,2129,2130,2131,2132,2133,2134,2135,2136,2137,2138,2139,2140,2141,2142,2143,2144,2145,2146,2147,2148,2149,2150,2151,2152,2153,2154,2155,2156,2157,2158,2159,2160,2161,2162,2163,2164,2165,2166,2167,2168,2169,2170,2171,2172,2173,2174,2175,2176,2177,2178,2179,2180,2181,2182,2183,2184,2185,2186,2187,2188,2189</v>
+        <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
       <c r="D97" s="4">
         <v>1</v>

--- a/config/鸿合_配置_v2.0.xlsx
+++ b/config/鸿合_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="20752" windowHeight="9555" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="207">
   <si>
     <t>key</t>
   </si>
@@ -247,6 +247,12 @@
     <t>interface</t>
   </si>
   <si>
+    <t>requestInterval</t>
+  </si>
+  <si>
+    <t>maxGap</t>
+  </si>
+  <si>
     <t>ModbusTCP</t>
   </si>
   <si>
@@ -268,16 +274,16 @@
     <t>./config/BMS_鸿合国轩.xlsx</t>
   </si>
   <si>
-    <t>192.168.1.104</t>
-  </si>
-  <si>
-    <t>192.168.1.105</t>
-  </si>
-  <si>
-    <t>192.168.1.106</t>
-  </si>
-  <si>
-    <t>192.168.1.107</t>
+    <t>192.168.0.6</t>
+  </si>
+  <si>
+    <t>192.168.0.7</t>
+  </si>
+  <si>
+    <t>192.168.0.8</t>
+  </si>
+  <si>
+    <t>192.168.0.9</t>
   </si>
   <si>
     <t>IEC104</t>
@@ -286,7 +292,7 @@
     <t>./config/测控柜_鸿合.xlsx</t>
   </si>
   <si>
-    <t>192.168.1.108</t>
+    <t>192.168.0.5</t>
   </si>
   <si>
     <t>device_id</t>
@@ -484,19 +490,37 @@
     <t>/pds/bank/0/cell/0/yc</t>
   </si>
   <si>
+    <t>500,506</t>
+  </si>
+  <si>
     <t>/pds/bank/0/cell/1/yc</t>
   </si>
   <si>
+    <t>501,507</t>
+  </si>
+  <si>
     <t>/pds/bank/0/cell/2/yc</t>
   </si>
   <si>
+    <t>502,508</t>
+  </si>
+  <si>
     <t>/pds/bank/0/cell/3/yc</t>
   </si>
   <si>
+    <t>503,509</t>
+  </si>
+  <si>
     <t>/pds/bank/0/cell/4/yc</t>
   </si>
   <si>
+    <t>504,510</t>
+  </si>
+  <si>
     <t>/pds/bank/0/cell/5/yc</t>
+  </si>
+  <si>
+    <t>505,511</t>
   </si>
   <si>
     <t>/pds/bank/1/cell/0/yc</t>
@@ -644,7 +668,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,9 +680,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -669,20 +692,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1166,144 +1175,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1312,20 +1318,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -8760,164 +8763,164 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="22.4070796460177" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.4047619047619" style="3"/>
-    <col min="2" max="2" width="33.7936507936508" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="22.4047619047619" style="3"/>
+    <col min="1" max="1" width="22.4070796460177" style="2"/>
+    <col min="2" max="2" width="33.7964601769912" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="22.4070796460177" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+    <row r="1" ht="15.75" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>9091</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>1883</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>9092</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -8932,153 +8935,153 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.9285714285714" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.3333333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.0952380952381" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="6.46017699115044" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.929203539823" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.3362831858407" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.0973451327434" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:5">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9092,360 +9095,392 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.5952380952381" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.4603174603175" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.8015873015873" style="3" customWidth="1"/>
-    <col min="5" max="5" width="44.531746031746" style="3" customWidth="1"/>
-    <col min="6" max="7" width="12.1984126984127" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.6031746031746" style="3" customWidth="1"/>
-    <col min="9" max="10" width="12.1984126984127" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.6666666666667" style="3" customWidth="1"/>
-    <col min="12" max="16" width="12.1984126984127" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.07142857142857" style="3"/>
+    <col min="1" max="1" width="6.46017699115044" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5929203539823" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.4601769911504" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.8053097345133" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44.5309734513274" style="2" customWidth="1"/>
+    <col min="6" max="7" width="12.1946902654867" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.6017699115044" style="2" customWidth="1"/>
+    <col min="9" max="10" width="12.1946902654867" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.6637168141593" style="2" customWidth="1"/>
+    <col min="12" max="16" width="12.1946902654867" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.07079646017699" style="2"/>
+    <col min="18" max="18" width="17.4513274336283" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9.07079646017699" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:17">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:19">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="3">
+      <c r="R1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="2">
         <f>devices!A2</f>
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="D2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="2">
         <v>1000</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>1000</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="3">
+      <c r="H2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="2">
         <v>502</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="3">
+      <c r="R2" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="2">
         <f>devices!A3</f>
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="D3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
         <v>1000</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>1000</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="3">
+      <c r="H3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="2">
         <v>502</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="3">
+      <c r="R3" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="2">
         <f>devices!A4</f>
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="D4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="2">
         <v>1000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>1000</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="3">
+      <c r="H4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="2">
         <v>502</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="3">
+      <c r="R4" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="2">
         <f>devices!A5</f>
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="D5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2">
         <v>1000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>1000</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="H5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="2">
         <v>502</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="3">
+      <c r="R5" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="2">
         <f>devices!A6</f>
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="D6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2">
         <v>1000</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" s="3">
+      <c r="G6" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="2">
         <v>502</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="3">
+      <c r="S6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="2">
         <f>devices!A7</f>
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="D7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="2">
         <v>1000</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="3">
+      <c r="G7" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="2">
         <v>502</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="3">
+      <c r="S7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="2">
         <f>devices!A8</f>
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="2">
         <v>1000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="G8" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="2">
         <v>502</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="3">
+      <c r="S8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="2">
         <f>devices!A9</f>
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="2">
         <v>1000</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="G9" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="2">
         <v>502</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="3">
+      <c r="S9" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="3">
-        <v>502</v>
+      <c r="E10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2404</v>
       </c>
     </row>
   </sheetData>
@@ -9459,1465 +9494,1465 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G100"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.11504424778761" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.7619047619048" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.0952380952381" style="2" customWidth="1"/>
-    <col min="3" max="3" width="212.15873015873" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.3968253968254" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.2936507936508" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.4365079365079" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.11111111111111" style="2"/>
+    <col min="1" max="1" width="11.7610619469027" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.0973451327434" style="2" customWidth="1"/>
+    <col min="3" max="3" width="212.159292035398" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.3982300884956" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.2920353982301" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.4336283185841" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.11504424778761" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>88</v>
+      <c r="B2" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)</f>
         <v>58,59,60,61,62,63,64,65,66,67,68,69,70,71</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
         <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
         <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018,2019,2020,2021,2022,2023,2024,2025,2026,2027,2028,2029</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="B5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D8" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    <row r="9" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D9" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="5" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row r="11" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="D13" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-    </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)</f>
         <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
         <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
         <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)</f>
         <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
         <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
         <v>2000,2001,2002,2003,2004,2005,2006,2007,2008,2009,2010,2011,2012,2013,2014,2015,2016,2017,2018</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="B20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D23" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="4" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D24" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="5" t="s">
+    <row r="25" spans="1:4">
+      <c r="A25" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="B25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-    </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C26" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
         <v>100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
         <v>139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
         <v>178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C29" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
         <v>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,249,250,251,252,253,254,255</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C30" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
         <v>256,257,258,259,260,261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,281,282,283,284,285,286,287,288,289,290,291,292,293,294</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C31" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
         <v>295,296,297,298,299,300,301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D32" s="4">
+      <c r="B32" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="4">
+      <c r="B33" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" s="4">
+      <c r="B34" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" s="4">
+      <c r="B35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="4">
+      <c r="B36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D36" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D37" s="4">
+      <c r="B37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C38" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
         <v>100,101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C39" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
         <v>139,140,141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C40" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
         <v>178,179,180,181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C41" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
         <v>217,218,219,220,221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,241,242,243,244,245,246,247,248,249,250,251,252,253,254,255</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C42" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
         <v>256,257,258,259,260,261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,281,282,283,284,285,286,287,288,289,290,291,292,293,294</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C43" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
         <v>295,296,297,298,299,300,301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320,321,322,323,324,325,326,327,328,329,330,331,332,333</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="4">
+      <c r="B44" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D45" s="4">
+      <c r="B45" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D46" s="4">
+      <c r="B46" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D46" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D47" s="4">
+      <c r="B47" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D47" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D48" s="4">
+      <c r="B48" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D49" s="4">
+      <c r="B49" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" s="6">
-        <v>500506</v>
-      </c>
-      <c r="D50" s="4">
+        <v>150</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D50" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C51" s="6">
-        <v>501507</v>
-      </c>
-      <c r="D51" s="4">
+        <v>152</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="6">
-        <v>502508</v>
-      </c>
-      <c r="D52" s="4">
+        <v>154</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="6">
-        <v>503509</v>
-      </c>
-      <c r="D53" s="4">
+      <c r="D56" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="3" t="s">
+    <row r="57" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D65" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C54" s="6">
-        <v>504510</v>
-      </c>
-      <c r="D54" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C55" s="6">
-        <v>505511</v>
-      </c>
-      <c r="D55" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C56" s="6">
-        <v>500506</v>
-      </c>
-      <c r="D56" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C57" s="6">
-        <v>501507</v>
-      </c>
-      <c r="D57" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C58" s="6">
-        <v>502508</v>
-      </c>
-      <c r="D58" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C59" s="6">
-        <v>503509</v>
-      </c>
-      <c r="D59" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C60" s="6">
-        <v>504510</v>
-      </c>
-      <c r="D60" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C61" s="6">
-        <v>505511</v>
-      </c>
-      <c r="D61" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C62" s="6">
-        <v>500506</v>
-      </c>
-      <c r="D62" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C63" s="6">
-        <v>501507</v>
-      </c>
-      <c r="D63" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C64" s="6">
-        <v>502508</v>
-      </c>
-      <c r="D64" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="6">
-        <v>503509</v>
-      </c>
-      <c r="D65" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" s="6">
-        <v>504510</v>
-      </c>
-      <c r="D66" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C67" s="6">
-        <v>505511</v>
-      </c>
-      <c r="D67" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C68" s="6">
-        <v>500506</v>
-      </c>
-      <c r="D68" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C69" s="6">
-        <v>501507</v>
-      </c>
-      <c r="D69" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C70" s="6">
-        <v>502508</v>
-      </c>
-      <c r="D70" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C71" s="6">
-        <v>503509</v>
-      </c>
-      <c r="D71" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C72" s="6">
-        <v>504510</v>
-      </c>
-      <c r="D72" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C73" s="6">
-        <v>505511</v>
-      </c>
-      <c r="D73" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="B74" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C74" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
         <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C75" s="4" t="str">
+      <c r="B75" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C75" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
         <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C76" s="4" t="str">
+      <c r="B76" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C76" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
         <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C77" s="4" t="str">
+      <c r="B77" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
         <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C78" s="4" t="str">
+      <c r="B78" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C78" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
         <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C79" s="4" t="str">
+      <c r="B79" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C79" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
         <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C80" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
         <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C81" s="4" t="str">
+      <c r="B81" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
         <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C82" s="4" t="str">
+      <c r="B82" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C82" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
         <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C83" s="4" t="str">
+      <c r="B83" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
         <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C84" s="4" t="str">
+      <c r="B84" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C84" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
         <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C85" s="4" t="str">
+      <c r="B85" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
         <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C86" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
         <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B87" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C87" s="4" t="str">
+      <c r="B87" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
         <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C88" s="4" t="str">
+      <c r="B88" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
         <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D88" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B89" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C89" s="4" t="str">
+      <c r="B89" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
         <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
-      <c r="D89" s="4">
+      <c r="D89" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C90" s="4" t="str">
+      <c r="B90" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C90" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
         <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C91" s="4" t="str">
+      <c r="B91" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
         <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C92" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
         <v>1200,1201,1202,1203,1204,1205,1206,1207,1208,1209,1210,1211,1212,1213,1214,1215,1216,1217,1218,1219,1220,1221,1222,1223,1224,1225,1226,1227,1228,1229,1230,1231,1232,1233,1234,1235,1236,1237,1238,1239,1240,1241,1242,1243,1244,1245,1246,1247,1248,1249,1250,1251,1252,1253,1254,1255,1256,1257,1258,1259,1260,1261,1262,1263,1264,1265,1266,1267,1268,1269,1270,1271,1272,1273,1274,1275,1276,1277,1278,1279,1280,1281,1282,1283,1284,1285,1286,1287,1288,1289,1290,1291,1292,1293,1294,1295,1296,1297,1298,1299,1300,1301,1302,1303,1304,1305,1306,1307,1308,1309,1310,1311,1312,1313,1314</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B93" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C93" s="4" t="str">
+      <c r="B93" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
         <v>1315,1316,1317,1318,1319,1320,1321,1322,1323,1324,1325,1326,1327,1328,1329,1330,1331,1332,1333,1334,1335,1336,1337,1338,1339,1340,1341,1342,1343,1344,1345,1346,1347,1348,1349,1350,1351,1352,1353,1354,1355,1356,1357,1358,1359,1360,1361,1362,1363,1364,1365,1366,1367,1368,1369,1370,1371,1372,1373,1374,1375,1376,1377,1378,1379,1380,1381,1382,1383,1384,1385,1386,1387,1388,1389,1390,1391,1392,1393,1394,1395,1396,1397,1398,1399,1400,1401,1402,1403,1404,1405,1406,1407,1408,1409,1410,1411,1412,1413,1414,1415,1416,1417,1418,1419,1420,1421,1422,1423,1424,1425,1426,1427,1428,1429</v>
       </c>
-      <c r="D93" s="4">
+      <c r="D93" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B94" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C94" s="4" t="str">
+      <c r="B94" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
         <v>1430,1431,1432,1433,1434,1435,1436,1437,1438,1439,1440,1441,1442,1443,1444,1445,1446,1447,1448,1449,1450,1451,1452,1453,1454,1455,1456,1457,1458,1459,1460,1461,1462,1463,1464,1465,1466,1467,1468,1469,1470,1471,1472,1473,1474,1475,1476,1477,1478,1479,1480,1481,1482,1483,1484,1485,1486,1487,1488,1489,1490,1491,1492,1493,1494,1495,1496,1497,1498,1499,1500,1501,1502,1503,1504,1505,1506,1507,1508,1509,1510,1511,1512,1513,1514,1515,1516,1517,1518,1519,1520,1521,1522,1523,1524,1525,1526,1527,1528,1529,1530,1531,1532,1533,1534,1535,1536,1537,1538,1539,1540,1541,1542,1543,1544</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C95" s="4" t="str">
+      <c r="B95" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C95" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
         <v>1545,1546,1547,1548,1549,1550,1551,1552,1553,1554,1555,1556,1557,1558,1559,1560,1561,1562,1563,1564,1565,1566,1567,1568,1569,1570,1571,1572,1573,1574,1575,1576,1577,1578,1579,1580,1581,1582,1583,1584,1585,1586,1587,1588,1589,1590,1591,1592,1593,1594,1595,1596,1597,1598,1599,1600,1601,1602,1603,1604,1605,1606,1607,1608,1609,1610,1611,1612,1613,1614,1615,1616,1617,1618,1619,1620,1621,1622,1623,1624,1625,1626,1627,1628,1629,1630,1631,1632,1633,1634,1635,1636,1637,1638,1639,1640,1641,1642,1643,1644,1645,1646,1647,1648,1649,1650,1651,1652,1653,1654,1655,1656,1657,1658,1659</v>
       </c>
-      <c r="D95" s="4">
+      <c r="D95" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C96" s="4" t="str">
+      <c r="B96" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C96" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
         <v>1660,1661,1662,1663,1664,1665,1666,1667,1668,1669,1670,1671,1672,1673,1674,1675,1676,1677,1678,1679,1680,1681,1682,1683,1684,1685,1686,1687,1688,1689,1690,1691,1692,1693,1694,1695,1696,1697,1698,1699,1700,1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712,1713,1714,1715,1716,1717,1718,1719,1720,1721,1722,1723,1724,1725,1726,1727,1728,1729,1730,1731,1732,1733,1734,1735,1736,1737,1738,1739,1740,1741,1742,1743,1744,1745,1746,1747,1748,1749,1750,1751,1752,1753,1754,1755,1756,1757,1758,1759,1760,1761,1762,1763,1764,1765,1766,1767,1768,1769,1770,1771,1772,1773,1774</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C97" s="4" t="str">
+      <c r="B97" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C97" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
         <v>1775,1776,1777,1778,1779,1780,1781,1782,1783,1784,1785,1786,1787,1788,1789,1790,1791,1792,1793,1794,1795,1796,1797,1798,1799,1800,1801,1802,1803,1804,1805,1806,1807,1808,1809,1810,1811,1812,1813,1814,1815,1816,1817,1818,1819,1820,1821,1822,1823,1824,1825,1826,1827,1828,1829,1830,1831,1832,1833,1834,1835,1836,1837,1838,1839,1840,1841,1842,1843,1844,1845,1846,1847,1848,1849,1850,1851,1852,1853,1854,1855,1856,1857,1858,1859,1860,1861,1862,1863,1864,1865,1866,1867,1868,1869,1870,1871,1872,1873,1874,1875,1876,1877,1878,1879,1880,1881,1882,1883,1884,1885,1886,1887,1888,1889</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C98" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$120)</f>
         <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C99" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$200)</f>
         <v>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,101,102,103,104,105,106,107,108,109,110,111,112,113</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C100" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥控!$A$2:$A$120)</f>
         <v>3000,3001,3002,3003</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="3">
         <v>1</v>
       </c>
     </row>

--- a/config/鸿合_配置_v2.0.xlsx
+++ b/config/鸿合_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555" activeTab="2"/>
+    <workbookView windowWidth="18519" windowHeight="11218" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="205">
   <si>
     <t>key</t>
   </si>
@@ -319,9 +319,6 @@
     <t>/pds/pcs/1/yx</t>
   </si>
   <si>
-    <t>58,59,60,61,62,63,64,65,66,67,68,69,70,71</t>
-  </si>
-  <si>
     <t>/pds/pcs/1/yc</t>
   </si>
   <si>
@@ -371,9 +368,6 @@
   </si>
   <si>
     <t>/pds/bank/2/yx</t>
-  </si>
-  <si>
-    <t>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</t>
   </si>
   <si>
     <t>/pds/bank/2/yc</t>
@@ -8763,14 +8757,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="22.4070796460177" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.4070796460177" style="2"/>
-    <col min="2" max="2" width="33.7964601769912" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="22.4070796460177" style="2"/>
+    <col min="1" max="1" width="22.4047619047619" style="2"/>
+    <col min="2" max="2" width="33.7936507936508" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="22.4047619047619" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8935,16 +8929,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46017699115044" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.929203539823" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.3362831858407" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.0973451327434" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.9285714285714" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.3333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.0952380952381" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -9096,24 +9090,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6.46017699115044" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.5929203539823" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.4601769911504" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.8053097345133" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.5309734513274" style="2" customWidth="1"/>
-    <col min="6" max="7" width="12.1946902654867" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.6017699115044" style="2" customWidth="1"/>
-    <col min="9" max="10" width="12.1946902654867" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.6637168141593" style="2" customWidth="1"/>
-    <col min="12" max="16" width="12.1946902654867" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.07079646017699" style="2"/>
-    <col min="18" max="18" width="17.4513274336283" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9.07079646017699" style="2"/>
+    <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5952380952381" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.4603174603175" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.8015873015873" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44.531746031746" style="2" customWidth="1"/>
+    <col min="6" max="7" width="12.1984126984127" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.6031746031746" style="2" customWidth="1"/>
+    <col min="9" max="10" width="12.1984126984127" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.6666666666667" style="2" customWidth="1"/>
+    <col min="12" max="16" width="12.1984126984127" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.07142857142857" style="2"/>
+    <col min="18" max="18" width="17.452380952381" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9.07142857142857" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:19">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -9494,18 +9488,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G100"/>
-  <sheetFormatPr defaultColWidth="9.11504424778761" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.7610619469027" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.0973451327434" style="2" customWidth="1"/>
-    <col min="3" max="3" width="212.159292035398" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.3982300884956" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.2920353982301" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.4336283185841" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.11504424778761" style="2"/>
+    <col min="1" max="1" width="11.7619047619048" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.0952380952381" style="2" customWidth="1"/>
+    <col min="3" max="3" width="212.15873015873" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.3968253968254" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.2936507936508" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.4365079365079" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.75" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -9530,8 +9524,8 @@
         <v>90</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)</f>
-        <v>58,59,60,61,62,63,64,65,66,67,68,69,70,71</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
+        <v>58,59,60,61,62,63,64,65,66,67,68,69,70,71,65535</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -9574,8 +9568,9 @@
       <c r="B5" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>94</v>
+      <c r="C5" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
+        <v>58,59,60,61,62,63,64,65,66,67,68,69,70,71,65535</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -9586,10 +9581,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -9600,10 +9595,10 @@
         <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -9614,10 +9609,11 @@
         <v>46</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
+        <v>58,59,60,61,62,63,64,65,66,67,68,69,70,71,65535</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -9628,10 +9624,10 @@
         <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -9642,10 +9638,10 @@
         <v>46</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -9656,10 +9652,11 @@
         <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
+        <v>58,59,60,61,62,63,64,65,66,67,68,69,70,71,65535</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -9670,10 +9667,10 @@
         <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -9684,10 +9681,10 @@
         <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -9698,11 +9695,11 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)</f>
-        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617,65535</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -9713,7 +9710,7 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C15" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
@@ -9728,7 +9725,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
@@ -9743,11 +9740,11 @@
         <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)</f>
-        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617,65535</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -9758,7 +9755,7 @@
         <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
@@ -9773,7 +9770,7 @@
         <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
@@ -9788,10 +9785,11 @@
         <v>52</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617,65535</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -9802,10 +9800,10 @@
         <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -9816,10 +9814,10 @@
         <v>52</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -9830,10 +9828,11 @@
         <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,1044,1045,1046,1047,1048,1049,1050,1051,1052,1053,1054,1055,1056,1057,1058,1059,1060,1061,1062,1063,1064,1065,1066,1067,1068,1069,1070,1071,1072,1073,1074,1075,1076,1077,1078,1079,1080,1081,1082,1083,1084,1085,1086,1087,1088,1089,1090,1091,1092,1093,1094,1095,1096,1097,1098,1099,1100,1101,1102,1103,1104,1105,1106,1107,1108,1109,1110,1111,1112,1113,1114,1115,1116,1117,1118,1119,1120,1121,1122,1123,1124,1125,1126,1127,1128,1129,1130,1131,1132,1133,1134,1135,1136,1137,1138,1139,600,601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617,65535</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
@@ -9844,10 +9843,10 @@
         <v>53</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
@@ -9858,10 +9857,10 @@
         <v>53</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -9872,7 +9871,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C26" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
@@ -9887,7 +9886,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C27" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
@@ -9902,7 +9901,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
@@ -9917,7 +9916,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
@@ -9932,7 +9931,7 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C30" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
@@ -9947,7 +9946,7 @@
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C31" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
@@ -9962,10 +9961,10 @@
         <v>51</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -9976,10 +9975,10 @@
         <v>51</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
@@ -9990,10 +9989,10 @@
         <v>51</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -10004,10 +10003,10 @@
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -10018,10 +10017,10 @@
         <v>51</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -10032,10 +10031,10 @@
         <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -10046,7 +10045,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
@@ -10061,7 +10060,7 @@
         <v>52</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C39" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
@@ -10076,7 +10075,7 @@
         <v>52</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C40" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
@@ -10091,7 +10090,7 @@
         <v>52</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C41" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
@@ -10106,7 +10105,7 @@
         <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C42" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
@@ -10121,7 +10120,7 @@
         <v>52</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C43" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
@@ -10136,10 +10135,10 @@
         <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -10150,10 +10149,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -10164,10 +10163,10 @@
         <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -10178,10 +10177,10 @@
         <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -10192,10 +10191,10 @@
         <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -10206,10 +10205,10 @@
         <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -10220,10 +10219,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -10234,10 +10233,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -10248,10 +10247,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -10262,10 +10261,10 @@
         <v>48</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -10276,10 +10275,10 @@
         <v>48</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
@@ -10290,10 +10289,10 @@
         <v>48</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D55" s="3">
         <v>1</v>
@@ -10304,10 +10303,10 @@
         <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -10318,10 +10317,10 @@
         <v>51</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -10332,10 +10331,10 @@
         <v>51</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D58" s="3">
         <v>1</v>
@@ -10346,10 +10345,10 @@
         <v>51</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
@@ -10360,10 +10359,10 @@
         <v>51</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
@@ -10374,10 +10373,10 @@
         <v>51</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
@@ -10388,10 +10387,10 @@
         <v>52</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -10402,10 +10401,10 @@
         <v>52</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D63" s="3">
         <v>1</v>
@@ -10416,10 +10415,10 @@
         <v>52</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
@@ -10430,10 +10429,10 @@
         <v>52</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
@@ -10444,10 +10443,10 @@
         <v>52</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D66" s="3">
         <v>1</v>
@@ -10458,10 +10457,10 @@
         <v>52</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D67" s="3">
         <v>1</v>
@@ -10472,10 +10471,10 @@
         <v>53</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -10486,10 +10485,10 @@
         <v>53</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D69" s="3">
         <v>1</v>
@@ -10500,10 +10499,10 @@
         <v>53</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
@@ -10514,10 +10513,10 @@
         <v>53</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
@@ -10528,10 +10527,10 @@
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
@@ -10542,10 +10541,10 @@
         <v>53</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
@@ -10556,7 +10555,7 @@
         <v>48</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C74" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10571,7 +10570,7 @@
         <v>48</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C75" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10586,7 +10585,7 @@
         <v>48</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C76" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10601,7 +10600,7 @@
         <v>48</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C77" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10616,7 +10615,7 @@
         <v>48</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C78" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10631,7 +10630,7 @@
         <v>48</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C79" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10646,7 +10645,7 @@
         <v>51</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C80" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10661,7 +10660,7 @@
         <v>51</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C81" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10676,7 +10675,7 @@
         <v>51</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C82" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10691,7 +10690,7 @@
         <v>51</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C83" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10706,7 +10705,7 @@
         <v>51</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C84" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10721,7 +10720,7 @@
         <v>51</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C85" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10736,7 +10735,7 @@
         <v>52</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C86" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10751,7 +10750,7 @@
         <v>52</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C87" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10766,7 +10765,7 @@
         <v>52</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C88" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10781,7 +10780,7 @@
         <v>52</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C89" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10796,7 +10795,7 @@
         <v>52</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C90" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10811,7 +10810,7 @@
         <v>52</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C91" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10826,7 +10825,7 @@
         <v>53</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C92" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10841,7 +10840,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C93" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10856,7 +10855,7 @@
         <v>53</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C94" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10871,7 +10870,7 @@
         <v>53</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C95" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10886,7 +10885,7 @@
         <v>53</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C96" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10901,7 +10900,7 @@
         <v>53</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C97" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10916,11 +10915,11 @@
         <v>54</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C98" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$120)</f>
-        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$120)&amp;",65535"</f>
+        <v>1000,1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014,1015,1016,1017,1018,1019,1020,1021,1022,1023,1024,1025,1026,1027,1028,1029,1030,1031,1032,1033,1034,1035,1036,1037,1038,1039,1040,1041,1042,1043,65535</v>
       </c>
       <c r="D98" s="3">
         <v>1</v>
@@ -10931,7 +10930,7 @@
         <v>54</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C99" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$200)</f>
@@ -10946,7 +10945,7 @@
         <v>54</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C100" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥控!$A$2:$A$120)</f>

--- a/config/鸿合_配置_v2.0.xlsx
+++ b/config/鸿合_配置_v2.0.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18519" windowHeight="11218" activeTab="3"/>
+    <workbookView windowWidth="18569" windowHeight="10825" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="204">
   <si>
     <t>key</t>
   </si>
@@ -253,6 +253,9 @@
     <t>maxGap</t>
   </si>
   <si>
+    <t>pcs</t>
+  </si>
+  <si>
     <t>ModbusTCP</t>
   </si>
   <si>
@@ -262,37 +265,31 @@
     <t>192.168.0.1</t>
   </si>
   <si>
+    <t>bms</t>
+  </si>
+  <si>
     <t>192.168.0.2</t>
   </si>
   <si>
+    <t>tms</t>
+  </si>
+  <si>
     <t>192.168.0.3</t>
   </si>
   <si>
+    <t>dehum</t>
+  </si>
+  <si>
     <t>192.168.0.4</t>
   </si>
   <si>
+    <t>fire</t>
+  </si>
+  <si>
     <t>./config/BMS_鸿合国轩.xlsx</t>
   </si>
   <si>
     <t>192.168.0.6</t>
-  </si>
-  <si>
-    <t>192.168.0.7</t>
-  </si>
-  <si>
-    <t>192.168.0.8</t>
-  </si>
-  <si>
-    <t>192.168.0.9</t>
-  </si>
-  <si>
-    <t>IEC104</t>
-  </si>
-  <si>
-    <t>./config/测控柜_鸿合.xlsx</t>
-  </si>
-  <si>
-    <t>192.168.0.5</t>
   </si>
   <si>
     <t>device_id</t>
@@ -1299,7 +1296,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1317,9 +1314,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9089,8 +9083,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.5952380952381" style="2" customWidth="1"/>
@@ -9172,16 +9166,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2" s="2">
         <v>1000</v>
@@ -9190,7 +9184,7 @@
         <v>1000</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2" s="2">
         <v>502</v>
@@ -9208,16 +9202,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="2">
         <v>1000</v>
@@ -9226,7 +9220,7 @@
         <v>1000</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2">
         <v>502</v>
@@ -9244,16 +9238,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2">
         <v>1000</v>
@@ -9262,7 +9256,7 @@
         <v>1000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I4" s="2">
         <v>502</v>
@@ -9280,16 +9274,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" s="2">
         <v>1000</v>
@@ -9298,7 +9292,7 @@
         <v>1000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I5" s="2">
         <v>502</v>
@@ -9316,16 +9310,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F6" s="2">
         <v>1000</v>
@@ -9334,7 +9328,7 @@
         <v>5000</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2">
         <v>502</v>
@@ -9344,137 +9338,6 @@
       </c>
       <c r="S6" s="2">
         <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="2">
-        <f>devices!A7</f>
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G7" s="2">
-        <v>5000</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="2">
-        <v>502</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="S7" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="2">
-        <f>devices!A8</f>
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5000</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I8" s="2">
-        <v>502</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-      <c r="S8" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="2">
-        <f>devices!A9</f>
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G9" s="2">
-        <v>5000</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="2">
-        <v>502</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1</v>
-      </c>
-      <c r="S9" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="2">
-        <v>2404</v>
       </c>
     </row>
   </sheetData>
@@ -9501,16 +9364,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -9521,7 +9384,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9536,7 +9399,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
@@ -9551,7 +9414,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
@@ -9566,7 +9429,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9581,10 +9444,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -9595,10 +9458,10 @@
         <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -9609,7 +9472,7 @@
         <v>46</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9624,10 +9487,10 @@
         <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -9638,10 +9501,10 @@
         <v>46</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -9652,7 +9515,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9667,10 +9530,10 @@
         <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -9681,10 +9544,10 @@
         <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -9695,7 +9558,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9710,7 +9573,7 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
@@ -9725,7 +9588,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
@@ -9740,7 +9603,7 @@
         <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9755,7 +9618,7 @@
         <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
@@ -9770,7 +9633,7 @@
         <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
@@ -9785,7 +9648,7 @@
         <v>52</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9800,10 +9663,10 @@
         <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -9814,10 +9677,10 @@
         <v>52</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -9828,7 +9691,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9843,10 +9706,10 @@
         <v>53</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
@@ -9857,10 +9720,10 @@
         <v>53</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -9871,7 +9734,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C26" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
@@ -9886,7 +9749,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
@@ -9901,7 +9764,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
@@ -9916,7 +9779,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C29" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
@@ -9931,7 +9794,7 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C30" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
@@ -9946,7 +9809,7 @@
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C31" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
@@ -9961,10 +9824,10 @@
         <v>51</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -9975,10 +9838,10 @@
         <v>51</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
@@ -9989,10 +9852,10 @@
         <v>51</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -10003,10 +9866,10 @@
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -10017,10 +9880,10 @@
         <v>51</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -10031,10 +9894,10 @@
         <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -10045,7 +9908,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
@@ -10060,7 +9923,7 @@
         <v>52</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C39" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
@@ -10075,7 +9938,7 @@
         <v>52</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C40" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
@@ -10090,7 +9953,7 @@
         <v>52</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C41" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
@@ -10105,7 +9968,7 @@
         <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C42" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
@@ -10120,7 +9983,7 @@
         <v>52</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C43" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
@@ -10135,10 +9998,10 @@
         <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -10149,10 +10012,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -10163,10 +10026,10 @@
         <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -10177,10 +10040,10 @@
         <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -10191,10 +10054,10 @@
         <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -10205,10 +10068,10 @@
         <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>135</v>
+        <v>146</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -10219,10 +10082,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -10233,10 +10096,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -10247,10 +10110,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -10261,10 +10124,10 @@
         <v>48</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -10275,10 +10138,10 @@
         <v>48</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
@@ -10289,10 +10152,10 @@
         <v>48</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="D55" s="3">
         <v>1</v>
@@ -10303,10 +10166,10 @@
         <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -10317,10 +10180,10 @@
         <v>51</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -10331,10 +10194,10 @@
         <v>51</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D58" s="3">
         <v>1</v>
@@ -10345,10 +10208,10 @@
         <v>51</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
@@ -10359,10 +10222,10 @@
         <v>51</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
@@ -10373,10 +10236,10 @@
         <v>51</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
@@ -10387,10 +10250,10 @@
         <v>52</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -10401,10 +10264,10 @@
         <v>52</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D63" s="3">
         <v>1</v>
@@ -10415,10 +10278,10 @@
         <v>52</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
@@ -10429,10 +10292,10 @@
         <v>52</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
@@ -10443,10 +10306,10 @@
         <v>52</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D66" s="3">
         <v>1</v>
@@ -10457,10 +10320,10 @@
         <v>52</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D67" s="3">
         <v>1</v>
@@ -10471,10 +10334,10 @@
         <v>53</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -10485,10 +10348,10 @@
         <v>53</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D69" s="3">
         <v>1</v>
@@ -10499,10 +10362,10 @@
         <v>53</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
@@ -10513,10 +10376,10 @@
         <v>53</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
@@ -10527,10 +10390,10 @@
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
@@ -10541,10 +10404,10 @@
         <v>53</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
@@ -10555,7 +10418,7 @@
         <v>48</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C74" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10570,7 +10433,7 @@
         <v>48</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C75" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10585,7 +10448,7 @@
         <v>48</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C76" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10600,7 +10463,7 @@
         <v>48</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C77" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10615,7 +10478,7 @@
         <v>48</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C78" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10630,7 +10493,7 @@
         <v>48</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C79" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10645,7 +10508,7 @@
         <v>51</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10660,7 +10523,7 @@
         <v>51</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C81" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10675,7 +10538,7 @@
         <v>51</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C82" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10690,7 +10553,7 @@
         <v>51</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C83" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10705,7 +10568,7 @@
         <v>51</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C84" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10720,7 +10583,7 @@
         <v>51</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C85" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10735,7 +10598,7 @@
         <v>52</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C86" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10750,7 +10613,7 @@
         <v>52</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C87" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10765,7 +10628,7 @@
         <v>52</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C88" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10780,7 +10643,7 @@
         <v>52</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C89" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10795,7 +10658,7 @@
         <v>52</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C90" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10810,7 +10673,7 @@
         <v>52</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C91" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10825,7 +10688,7 @@
         <v>53</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C92" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10840,7 +10703,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C93" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10855,7 +10718,7 @@
         <v>53</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C94" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10870,7 +10733,7 @@
         <v>53</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C95" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10885,7 +10748,7 @@
         <v>53</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C96" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10900,7 +10763,7 @@
         <v>53</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C97" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10915,7 +10778,7 @@
         <v>54</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C98" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$120)&amp;",65535"</f>
@@ -10930,7 +10793,7 @@
         <v>54</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C99" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$200)</f>
@@ -10945,7 +10808,7 @@
         <v>54</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C100" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥控!$A$2:$A$120)</f>

--- a/config/鸿合_配置_v2.0.xlsx
+++ b/config/鸿合_配置_v2.0.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="200">
   <si>
     <t>key</t>
   </si>
@@ -253,9 +253,6 @@
     <t>maxGap</t>
   </si>
   <si>
-    <t>pcs</t>
-  </si>
-  <si>
     <t>ModbusTCP</t>
   </si>
   <si>
@@ -265,19 +262,10 @@
     <t>192.168.0.1</t>
   </si>
   <si>
-    <t>bms</t>
-  </si>
-  <si>
     <t>192.168.0.2</t>
   </si>
   <si>
-    <t>tms</t>
-  </si>
-  <si>
     <t>192.168.0.3</t>
-  </si>
-  <si>
-    <t>dehum</t>
   </si>
   <si>
     <t>192.168.0.4</t>
@@ -9166,16 +9154,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="F2" s="2">
         <v>1000</v>
@@ -9184,7 +9172,7 @@
         <v>1000</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I2" s="2">
         <v>502</v>
@@ -9202,16 +9190,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="F3" s="2">
         <v>1000</v>
@@ -9220,7 +9208,7 @@
         <v>1000</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I3" s="2">
         <v>502</v>
@@ -9238,16 +9226,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="F4" s="2">
         <v>1000</v>
@@ -9256,7 +9244,7 @@
         <v>1000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2">
         <v>502</v>
@@ -9274,16 +9262,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="F5" s="2">
         <v>1000</v>
@@ -9292,7 +9280,7 @@
         <v>1000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2">
         <v>502</v>
@@ -9310,16 +9298,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F6" s="2">
         <v>1000</v>
@@ -9328,7 +9316,7 @@
         <v>5000</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I6" s="2">
         <v>502</v>
@@ -9364,16 +9352,16 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -9384,7 +9372,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9399,7 +9387,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$2:$A$55)</f>
@@ -9414,7 +9402,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥调!$A$2:$A$31)</f>
@@ -9429,7 +9417,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C5" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9444,10 +9432,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -9458,10 +9446,10 @@
         <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -9472,7 +9460,7 @@
         <v>46</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9487,10 +9475,10 @@
         <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -9501,10 +9489,10 @@
         <v>46</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -9515,7 +9503,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[1]遥测!$A$56:$A$71)&amp;",65535"</f>
@@ -9530,10 +9518,10 @@
         <v>47</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -9544,10 +9532,10 @@
         <v>47</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -9558,7 +9546,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C14" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9573,7 +9561,7 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C15" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
@@ -9588,7 +9576,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
@@ -9603,7 +9591,7 @@
         <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9618,7 +9606,7 @@
         <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$2:$A$53)</f>
@@ -9633,7 +9621,7 @@
         <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥调!$A$2:$A$20)</f>
@@ -9648,7 +9636,7 @@
         <v>52</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C20" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9663,10 +9651,10 @@
         <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
@@ -9677,10 +9665,10 @@
         <v>52</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -9691,7 +9679,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C23" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$2:$A$141,[3]遥测!$A$300:$A$317)&amp;",65535"</f>
@@ -9706,10 +9694,10 @@
         <v>53</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
@@ -9720,10 +9708,10 @@
         <v>53</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -9734,7 +9722,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C26" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
@@ -9749,7 +9737,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C27" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
@@ -9764,7 +9752,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
@@ -9779,7 +9767,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C29" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
@@ -9794,7 +9782,7 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C30" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
@@ -9809,7 +9797,7 @@
         <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C31" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
@@ -9824,10 +9812,10 @@
         <v>51</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
@@ -9838,10 +9826,10 @@
         <v>51</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
@@ -9852,10 +9840,10 @@
         <v>51</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D34" s="3">
         <v>1</v>
@@ -9866,10 +9854,10 @@
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
@@ -9880,10 +9868,10 @@
         <v>51</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -9894,10 +9882,10 @@
         <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
@@ -9908,7 +9896,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C38" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$54:$A$92)</f>
@@ -9923,7 +9911,7 @@
         <v>52</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C39" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$93:$A$131)</f>
@@ -9938,7 +9926,7 @@
         <v>52</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C40" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$132:$A$170)</f>
@@ -9953,7 +9941,7 @@
         <v>52</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C41" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$171:$A$209)</f>
@@ -9968,7 +9956,7 @@
         <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C42" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$210:$A$248)</f>
@@ -9983,7 +9971,7 @@
         <v>52</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C43" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥测!$A$249:$A$287)</f>
@@ -9998,10 +9986,10 @@
         <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
@@ -10012,10 +10000,10 @@
         <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
@@ -10026,10 +10014,10 @@
         <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -10040,10 +10028,10 @@
         <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
@@ -10054,10 +10042,10 @@
         <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -10068,10 +10056,10 @@
         <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -10082,10 +10070,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -10096,10 +10084,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -10110,10 +10098,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -10124,10 +10112,10 @@
         <v>48</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -10138,10 +10126,10 @@
         <v>48</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
@@ -10152,10 +10140,10 @@
         <v>48</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D55" s="3">
         <v>1</v>
@@ -10166,10 +10154,10 @@
         <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -10180,10 +10168,10 @@
         <v>51</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -10194,10 +10182,10 @@
         <v>51</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D58" s="3">
         <v>1</v>
@@ -10208,10 +10196,10 @@
         <v>51</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
@@ -10222,10 +10210,10 @@
         <v>51</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
@@ -10236,10 +10224,10 @@
         <v>51</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
@@ -10250,10 +10238,10 @@
         <v>52</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -10264,10 +10252,10 @@
         <v>52</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D63" s="3">
         <v>1</v>
@@ -10278,10 +10266,10 @@
         <v>52</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
@@ -10292,10 +10280,10 @@
         <v>52</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
@@ -10306,10 +10294,10 @@
         <v>52</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D66" s="3">
         <v>1</v>
@@ -10320,10 +10308,10 @@
         <v>52</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D67" s="3">
         <v>1</v>
@@ -10334,10 +10322,10 @@
         <v>53</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -10348,10 +10336,10 @@
         <v>53</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D69" s="3">
         <v>1</v>
@@ -10362,10 +10350,10 @@
         <v>53</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
@@ -10376,10 +10364,10 @@
         <v>53</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
@@ -10390,10 +10378,10 @@
         <v>53</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
@@ -10404,10 +10392,10 @@
         <v>53</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
@@ -10418,7 +10406,7 @@
         <v>48</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C74" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10433,7 +10421,7 @@
         <v>48</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C75" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10448,7 +10436,7 @@
         <v>48</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C76" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10463,7 +10451,7 @@
         <v>48</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C77" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10478,7 +10466,7 @@
         <v>48</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C78" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10493,7 +10481,7 @@
         <v>48</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C79" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10508,7 +10496,7 @@
         <v>51</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C80" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10523,7 +10511,7 @@
         <v>51</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C81" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10538,7 +10526,7 @@
         <v>51</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C82" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10553,7 +10541,7 @@
         <v>51</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C83" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10568,7 +10556,7 @@
         <v>51</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C84" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10583,7 +10571,7 @@
         <v>51</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C85" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10598,7 +10586,7 @@
         <v>52</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C86" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10613,7 +10601,7 @@
         <v>52</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C87" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10628,7 +10616,7 @@
         <v>52</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C88" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10643,7 +10631,7 @@
         <v>52</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C89" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10658,7 +10646,7 @@
         <v>52</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C90" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10673,7 +10661,7 @@
         <v>52</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C91" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10688,7 +10676,7 @@
         <v>53</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C92" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$142:$A$256)</f>
@@ -10703,7 +10691,7 @@
         <v>53</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C93" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$257:$A$371)</f>
@@ -10718,7 +10706,7 @@
         <v>53</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C94" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$372:$A$486)</f>
@@ -10733,7 +10721,7 @@
         <v>53</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C95" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$487:$A$601)</f>
@@ -10748,7 +10736,7 @@
         <v>53</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C96" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$602:$A$716)</f>
@@ -10763,7 +10751,7 @@
         <v>53</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C97" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[3]遥信!$A$717:$A$831)</f>
@@ -10778,7 +10766,7 @@
         <v>54</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C98" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥信!$A$2:$A$120)&amp;",65535"</f>
@@ -10793,7 +10781,7 @@
         <v>54</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C99" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥测!$A$2:$A$200)</f>
@@ -10808,7 +10796,7 @@
         <v>54</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C100" s="2" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,[2]遥控!$A$2:$A$120)</f>
